--- a/data/dupl_sample.xlsx
+++ b/data/dupl_sample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/janabusa/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74BE7017-EA18-494F-A33C-E5BCBAC78625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67155FA1-827B-9A40-B35B-E8CE8583B7B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19440" tabRatio="205" xr2:uid="{B654635F-ACD3-1A4D-8D5D-C270B619768D}"/>
   </bookViews>
@@ -367,10 +367,10 @@
     <t>Alkire</t>
   </si>
   <si>
-    <t>as</t>
+    <t>o</t>
   </si>
   <si>
-    <t>fgh</t>
+    <t>awe</t>
   </si>
 </sst>
 </file>
@@ -413,10 +413,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -818,6 +820,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40126374-5BB8-B544-8023-843744AF278C}">
   <dimension ref="A1:H1004"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="6" max="6" width="11.5" style="4"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B1" s="1" t="s">
@@ -832,7 +837,7 @@
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -858,8 +863,8 @@
       <c r="E2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
-        <v>116</v>
+      <c r="F2" s="4">
+        <v>12</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>11</v>
@@ -884,8 +889,8 @@
       <c r="E3" t="s">
         <v>10</v>
       </c>
-      <c r="F3">
-        <v>32.5</v>
+      <c r="F3" s="4">
+        <v>32</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>11</v>
@@ -910,6 +915,9 @@
       <c r="E4" t="s">
         <v>14</v>
       </c>
+      <c r="F4" s="4">
+        <v>12</v>
+      </c>
       <c r="G4" t="s">
         <v>15</v>
       </c>
@@ -933,7 +941,7 @@
       <c r="E5" t="s">
         <v>19</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="4">
         <v>36</v>
       </c>
       <c r="G5" t="s">
@@ -959,7 +967,7 @@
       <c r="E6" t="s">
         <v>10</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="4">
         <v>25</v>
       </c>
       <c r="G6" s="2" t="s">
@@ -985,7 +993,7 @@
       <c r="E7" t="s">
         <v>10</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="4">
         <v>58</v>
       </c>
       <c r="G7" t="s">
@@ -1011,8 +1019,8 @@
       <c r="E8" t="s">
         <v>10</v>
       </c>
-      <c r="F8">
-        <v>24</v>
+      <c r="F8" s="4">
+        <v>12</v>
       </c>
       <c r="G8" t="s">
         <v>20</v>
@@ -1037,7 +1045,7 @@
       <c r="E9" t="s">
         <v>14</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="4">
         <v>56</v>
       </c>
       <c r="G9" s="2" t="s">
@@ -1063,7 +1071,7 @@
       <c r="E10" t="s">
         <v>10</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="4">
         <v>27</v>
       </c>
       <c r="G10" t="s">
@@ -1089,7 +1097,7 @@
       <c r="E11" t="s">
         <v>10</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="4">
         <v>40</v>
       </c>
       <c r="G11" t="s">
@@ -1115,7 +1123,7 @@
       <c r="E12" t="s">
         <v>14</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="4">
         <v>28</v>
       </c>
       <c r="G12" t="s">
@@ -1141,7 +1149,7 @@
       <c r="E13" t="s">
         <v>14</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="4">
         <v>39</v>
       </c>
       <c r="G13" t="s">
@@ -1167,7 +1175,7 @@
       <c r="E14" t="s">
         <v>19</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="4">
         <v>38</v>
       </c>
       <c r="G14" s="2" t="s">
@@ -1193,7 +1201,7 @@
       <c r="E15" t="s">
         <v>14</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="4">
         <v>32</v>
       </c>
       <c r="G15" t="s">
@@ -1219,7 +1227,7 @@
       <c r="E16" t="s">
         <v>14</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="4">
         <v>26</v>
       </c>
       <c r="G16" t="s">
@@ -1245,8 +1253,8 @@
       <c r="E17" t="s">
         <v>14</v>
       </c>
-      <c r="F17">
-        <v>31</v>
+      <c r="F17" s="4" t="s">
+        <v>116</v>
       </c>
       <c r="G17" t="s">
         <v>15</v>
@@ -1271,7 +1279,7 @@
       <c r="E18" t="s">
         <v>19</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="4">
         <v>24</v>
       </c>
       <c r="G18" t="s">
@@ -1297,7 +1305,7 @@
       <c r="E19" t="s">
         <v>19</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="4">
         <v>39</v>
       </c>
       <c r="G19" s="2" t="s">
@@ -1323,8 +1331,8 @@
       <c r="E20" t="s">
         <v>14</v>
       </c>
-      <c r="F20">
-        <v>28</v>
+      <c r="F20" s="4" t="s">
+        <v>115</v>
       </c>
       <c r="G20" t="s">
         <v>15</v>
@@ -1349,7 +1357,7 @@
       <c r="E21" t="s">
         <v>19</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="4">
         <v>26</v>
       </c>
       <c r="G21" t="s">
@@ -1375,8 +1383,8 @@
       <c r="E22" t="s">
         <v>19</v>
       </c>
-      <c r="F22">
-        <v>46</v>
+      <c r="F22" s="4">
+        <v>12</v>
       </c>
       <c r="G22" t="s">
         <v>20</v>
@@ -1401,7 +1409,7 @@
       <c r="E23" t="s">
         <v>10</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="4">
         <v>37</v>
       </c>
       <c r="G23" s="2" t="s">
@@ -1427,7 +1435,7 @@
       <c r="E24" t="s">
         <v>10</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="4">
         <v>52</v>
       </c>
       <c r="G24" t="s">
@@ -1453,7 +1461,7 @@
       <c r="E25" t="s">
         <v>14</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="4">
         <v>46</v>
       </c>
       <c r="G25" t="s">
@@ -1479,7 +1487,7 @@
       <c r="E26" t="s">
         <v>19</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="4">
         <v>42</v>
       </c>
       <c r="G26" t="s">
@@ -1505,9 +1513,6 @@
       <c r="E27" t="s">
         <v>19</v>
       </c>
-      <c r="F27" t="s">
-        <v>115</v>
-      </c>
       <c r="G27" s="2" t="s">
         <v>11</v>
       </c>
@@ -1531,7 +1536,7 @@
       <c r="E28" t="s">
         <v>14</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="4">
         <v>28</v>
       </c>
       <c r="G28" t="s">
@@ -1557,7 +1562,7 @@
       <c r="E29" t="s">
         <v>10</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="4">
         <v>29</v>
       </c>
       <c r="G29" t="s">
@@ -1583,7 +1588,7 @@
       <c r="E30" t="s">
         <v>19</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="4">
         <v>23</v>
       </c>
       <c r="G30" s="2" t="s">
@@ -1609,7 +1614,7 @@
       <c r="E31" t="s">
         <v>10</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="4">
         <v>41</v>
       </c>
       <c r="G31" t="s">
@@ -1635,7 +1640,7 @@
       <c r="E32" t="s">
         <v>14</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="4">
         <v>28</v>
       </c>
       <c r="G32" t="s">
@@ -1661,7 +1666,7 @@
       <c r="E33" t="s">
         <v>14</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="4">
         <v>37</v>
       </c>
       <c r="G33" s="2" t="s">
@@ -1687,7 +1692,7 @@
       <c r="E34" t="s">
         <v>14</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="4">
         <v>34</v>
       </c>
       <c r="G34" t="s">
@@ -1713,7 +1718,7 @@
       <c r="E35" t="s">
         <v>14</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="4">
         <v>26</v>
       </c>
       <c r="G35" t="s">
@@ -1739,7 +1744,7 @@
       <c r="E36" t="s">
         <v>19</v>
       </c>
-      <c r="F36">
+      <c r="F36" s="4">
         <v>35</v>
       </c>
       <c r="G36" t="s">
@@ -1765,7 +1770,7 @@
       <c r="E37" t="s">
         <v>10</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="4">
         <v>36</v>
       </c>
       <c r="G37" t="s">
@@ -1791,7 +1796,7 @@
       <c r="E38" t="s">
         <v>10</v>
       </c>
-      <c r="F38">
+      <c r="F38" s="4">
         <v>29</v>
       </c>
       <c r="G38" s="2" t="s">
@@ -1817,9 +1822,6 @@
       <c r="E39" t="s">
         <v>19</v>
       </c>
-      <c r="F39">
-        <v>27</v>
-      </c>
       <c r="G39" t="s">
         <v>15</v>
       </c>
@@ -1843,7 +1845,7 @@
       <c r="E40" t="s">
         <v>10</v>
       </c>
-      <c r="F40">
+      <c r="F40" s="4">
         <v>25</v>
       </c>
       <c r="G40" t="s">
@@ -1869,7 +1871,7 @@
       <c r="E41" t="s">
         <v>10</v>
       </c>
-      <c r="F41">
+      <c r="F41" s="4">
         <v>36</v>
       </c>
       <c r="G41" t="s">
@@ -1895,7 +1897,7 @@
       <c r="E42" t="s">
         <v>10</v>
       </c>
-      <c r="F42">
+      <c r="F42" s="4">
         <v>37</v>
       </c>
       <c r="G42" s="2" t="s">
@@ -1921,7 +1923,7 @@
       <c r="E43" t="s">
         <v>10</v>
       </c>
-      <c r="F43">
+      <c r="F43" s="4">
         <v>26</v>
       </c>
       <c r="G43" t="s">
@@ -1947,7 +1949,7 @@
       <c r="E44" t="s">
         <v>10</v>
       </c>
-      <c r="F44">
+      <c r="F44" s="4">
         <v>37</v>
       </c>
       <c r="G44" t="s">
@@ -1973,9 +1975,6 @@
       <c r="E45" t="s">
         <v>19</v>
       </c>
-      <c r="F45">
-        <v>24</v>
-      </c>
       <c r="G45" s="2" t="s">
         <v>11</v>
       </c>
@@ -1999,7 +1998,7 @@
       <c r="E46" t="s">
         <v>10</v>
       </c>
-      <c r="F46">
+      <c r="F46" s="4">
         <v>39</v>
       </c>
       <c r="G46" t="s">
@@ -2025,7 +2024,7 @@
       <c r="E47" t="s">
         <v>10</v>
       </c>
-      <c r="F47">
+      <c r="F47" s="4">
         <v>26</v>
       </c>
       <c r="G47" t="s">
@@ -2051,7 +2050,7 @@
       <c r="E48" t="s">
         <v>10</v>
       </c>
-      <c r="F48">
+      <c r="F48" s="4">
         <v>34</v>
       </c>
       <c r="G48" s="2" t="s">
@@ -2077,7 +2076,7 @@
       <c r="E49" t="s">
         <v>10</v>
       </c>
-      <c r="F49">
+      <c r="F49" s="4">
         <v>28</v>
       </c>
       <c r="G49" t="s">
@@ -2103,7 +2102,7 @@
       <c r="E50" t="s">
         <v>10</v>
       </c>
-      <c r="F50">
+      <c r="F50" s="4">
         <v>32</v>
       </c>
       <c r="G50" t="s">
@@ -2129,7 +2128,7 @@
       <c r="E51" t="s">
         <v>10</v>
       </c>
-      <c r="F51">
+      <c r="F51" s="4">
         <v>39</v>
       </c>
       <c r="G51" s="2" t="s">
@@ -2155,7 +2154,7 @@
       <c r="E52" t="s">
         <v>10</v>
       </c>
-      <c r="F52">
+      <c r="F52" s="4">
         <v>29</v>
       </c>
       <c r="G52" t="s">
@@ -2181,7 +2180,7 @@
       <c r="E53" t="s">
         <v>10</v>
       </c>
-      <c r="F53">
+      <c r="F53" s="4">
         <v>32</v>
       </c>
       <c r="G53" s="2" t="s">
@@ -2207,7 +2206,7 @@
       <c r="E54" t="s">
         <v>14</v>
       </c>
-      <c r="F54">
+      <c r="F54" s="4">
         <v>25</v>
       </c>
       <c r="G54" t="s">
@@ -2233,7 +2232,7 @@
       <c r="E55" t="s">
         <v>19</v>
       </c>
-      <c r="F55">
+      <c r="F55" s="4">
         <v>36</v>
       </c>
       <c r="G55" t="s">
@@ -2259,7 +2258,7 @@
       <c r="E56" t="s">
         <v>10</v>
       </c>
-      <c r="F56">
+      <c r="F56" s="4">
         <v>25</v>
       </c>
       <c r="G56" s="2" t="s">
@@ -2285,7 +2284,7 @@
       <c r="E57" t="s">
         <v>10</v>
       </c>
-      <c r="F57">
+      <c r="F57" s="4">
         <v>58</v>
       </c>
       <c r="G57" t="s">
@@ -2311,7 +2310,7 @@
       <c r="E58" t="s">
         <v>10</v>
       </c>
-      <c r="F58">
+      <c r="F58" s="4">
         <v>24</v>
       </c>
       <c r="G58" t="s">
@@ -2337,7 +2336,7 @@
       <c r="E59" t="s">
         <v>14</v>
       </c>
-      <c r="F59">
+      <c r="F59" s="4">
         <v>56</v>
       </c>
       <c r="G59" s="2" t="s">
@@ -2363,7 +2362,7 @@
       <c r="E60" t="s">
         <v>10</v>
       </c>
-      <c r="F60">
+      <c r="F60" s="4">
         <v>27</v>
       </c>
       <c r="G60" t="s">
@@ -2389,7 +2388,7 @@
       <c r="E61" t="s">
         <v>10</v>
       </c>
-      <c r="F61">
+      <c r="F61" s="4">
         <v>40</v>
       </c>
       <c r="G61" t="s">
@@ -2415,7 +2414,7 @@
       <c r="E62" t="s">
         <v>14</v>
       </c>
-      <c r="F62">
+      <c r="F62" s="4">
         <v>28</v>
       </c>
       <c r="G62" t="s">
@@ -2441,7 +2440,7 @@
       <c r="E63" t="s">
         <v>14</v>
       </c>
-      <c r="F63">
+      <c r="F63" s="4">
         <v>39</v>
       </c>
       <c r="G63" t="s">
@@ -2467,7 +2466,7 @@
       <c r="E64" t="s">
         <v>19</v>
       </c>
-      <c r="F64">
+      <c r="F64" s="4">
         <v>38</v>
       </c>
       <c r="G64" s="2" t="s">
@@ -2493,7 +2492,7 @@
       <c r="E65" t="s">
         <v>14</v>
       </c>
-      <c r="F65">
+      <c r="F65" s="4">
         <v>32</v>
       </c>
       <c r="G65" t="s">
@@ -2519,7 +2518,7 @@
       <c r="E66" t="s">
         <v>14</v>
       </c>
-      <c r="F66">
+      <c r="F66" s="4">
         <v>26</v>
       </c>
       <c r="G66" t="s">
@@ -2545,7 +2544,7 @@
       <c r="E67" t="s">
         <v>14</v>
       </c>
-      <c r="F67">
+      <c r="F67" s="4">
         <v>31</v>
       </c>
       <c r="G67" t="s">
@@ -2571,7 +2570,7 @@
       <c r="E68" t="s">
         <v>19</v>
       </c>
-      <c r="F68">
+      <c r="F68" s="4">
         <v>24</v>
       </c>
       <c r="G68" t="s">
@@ -2597,7 +2596,7 @@
       <c r="E69" t="s">
         <v>19</v>
       </c>
-      <c r="F69">
+      <c r="F69" s="4">
         <v>39</v>
       </c>
       <c r="G69" s="2" t="s">
@@ -2623,7 +2622,7 @@
       <c r="E70" t="s">
         <v>14</v>
       </c>
-      <c r="F70">
+      <c r="F70" s="4">
         <v>28</v>
       </c>
       <c r="G70" t="s">
@@ -2649,7 +2648,7 @@
       <c r="E71" t="s">
         <v>19</v>
       </c>
-      <c r="F71">
+      <c r="F71" s="4">
         <v>26</v>
       </c>
       <c r="G71" t="s">
@@ -2675,7 +2674,7 @@
       <c r="E72" t="s">
         <v>19</v>
       </c>
-      <c r="F72">
+      <c r="F72" s="4">
         <v>46</v>
       </c>
       <c r="G72" t="s">
@@ -2701,7 +2700,7 @@
       <c r="E73" t="s">
         <v>10</v>
       </c>
-      <c r="F73">
+      <c r="F73" s="4">
         <v>37</v>
       </c>
       <c r="G73" s="2" t="s">
@@ -2727,7 +2726,7 @@
       <c r="E74" t="s">
         <v>10</v>
       </c>
-      <c r="F74">
+      <c r="F74" s="4">
         <v>52</v>
       </c>
       <c r="G74" t="s">
@@ -2753,7 +2752,7 @@
       <c r="E75" t="s">
         <v>14</v>
       </c>
-      <c r="F75">
+      <c r="F75" s="4">
         <v>46</v>
       </c>
       <c r="G75" t="s">
@@ -2779,7 +2778,7 @@
       <c r="E76" t="s">
         <v>19</v>
       </c>
-      <c r="F76">
+      <c r="F76" s="4">
         <v>42</v>
       </c>
       <c r="G76" t="s">
@@ -2805,7 +2804,7 @@
       <c r="E77" t="s">
         <v>19</v>
       </c>
-      <c r="F77">
+      <c r="F77" s="4">
         <v>21</v>
       </c>
       <c r="G77" s="2" t="s">
@@ -2831,7 +2830,7 @@
       <c r="E78" t="s">
         <v>14</v>
       </c>
-      <c r="F78">
+      <c r="F78" s="4">
         <v>28</v>
       </c>
       <c r="G78" t="s">
@@ -2857,7 +2856,7 @@
       <c r="E79" t="s">
         <v>10</v>
       </c>
-      <c r="F79">
+      <c r="F79" s="4">
         <v>29</v>
       </c>
       <c r="G79" t="s">
@@ -2883,7 +2882,7 @@
       <c r="E80" t="s">
         <v>19</v>
       </c>
-      <c r="F80">
+      <c r="F80" s="4">
         <v>23</v>
       </c>
       <c r="G80" s="2" t="s">
@@ -2909,7 +2908,7 @@
       <c r="E81" t="s">
         <v>10</v>
       </c>
-      <c r="F81">
+      <c r="F81" s="4">
         <v>41</v>
       </c>
       <c r="G81" t="s">
@@ -2935,7 +2934,7 @@
       <c r="E82" t="s">
         <v>14</v>
       </c>
-      <c r="F82">
+      <c r="F82" s="4">
         <v>28</v>
       </c>
       <c r="G82" t="s">
@@ -2961,7 +2960,7 @@
       <c r="E83" t="s">
         <v>14</v>
       </c>
-      <c r="F83">
+      <c r="F83" s="4">
         <v>37</v>
       </c>
       <c r="G83" s="2" t="s">
@@ -2987,7 +2986,7 @@
       <c r="E84" t="s">
         <v>14</v>
       </c>
-      <c r="F84">
+      <c r="F84" s="4">
         <v>34</v>
       </c>
       <c r="G84" t="s">
@@ -3013,7 +3012,7 @@
       <c r="E85" t="s">
         <v>14</v>
       </c>
-      <c r="F85">
+      <c r="F85" s="4">
         <v>26</v>
       </c>
       <c r="G85" t="s">
@@ -3039,7 +3038,7 @@
       <c r="E86" t="s">
         <v>19</v>
       </c>
-      <c r="F86">
+      <c r="F86" s="4">
         <v>35</v>
       </c>
       <c r="G86" t="s">
@@ -3065,7 +3064,7 @@
       <c r="E87" t="s">
         <v>10</v>
       </c>
-      <c r="F87">
+      <c r="F87" s="4">
         <v>36</v>
       </c>
       <c r="G87" t="s">
@@ -3091,7 +3090,7 @@
       <c r="E88" t="s">
         <v>10</v>
       </c>
-      <c r="F88">
+      <c r="F88" s="4">
         <v>29</v>
       </c>
       <c r="G88" s="2" t="s">
@@ -3117,7 +3116,7 @@
       <c r="E89" t="s">
         <v>19</v>
       </c>
-      <c r="F89">
+      <c r="F89" s="4">
         <v>27</v>
       </c>
       <c r="G89" t="s">
@@ -3143,7 +3142,7 @@
       <c r="E90" t="s">
         <v>10</v>
       </c>
-      <c r="F90">
+      <c r="F90" s="4">
         <v>25</v>
       </c>
       <c r="G90" t="s">
@@ -3169,7 +3168,7 @@
       <c r="E91" t="s">
         <v>10</v>
       </c>
-      <c r="F91">
+      <c r="F91" s="4">
         <v>36</v>
       </c>
       <c r="G91" t="s">
@@ -3195,7 +3194,7 @@
       <c r="E92" t="s">
         <v>10</v>
       </c>
-      <c r="F92">
+      <c r="F92" s="4">
         <v>37</v>
       </c>
       <c r="G92" s="2" t="s">
@@ -3221,7 +3220,7 @@
       <c r="E93" t="s">
         <v>10</v>
       </c>
-      <c r="F93">
+      <c r="F93" s="4">
         <v>26</v>
       </c>
       <c r="G93" t="s">
@@ -3247,7 +3246,7 @@
       <c r="E94" t="s">
         <v>10</v>
       </c>
-      <c r="F94">
+      <c r="F94" s="4">
         <v>37</v>
       </c>
       <c r="G94" t="s">
@@ -3273,7 +3272,7 @@
       <c r="E95" t="s">
         <v>19</v>
       </c>
-      <c r="F95">
+      <c r="F95" s="4">
         <v>24</v>
       </c>
       <c r="G95" s="2" t="s">
@@ -3299,7 +3298,7 @@
       <c r="E96" t="s">
         <v>10</v>
       </c>
-      <c r="F96">
+      <c r="F96" s="4">
         <v>39</v>
       </c>
       <c r="G96" t="s">
@@ -3325,7 +3324,7 @@
       <c r="E97" t="s">
         <v>10</v>
       </c>
-      <c r="F97">
+      <c r="F97" s="4">
         <v>26</v>
       </c>
       <c r="G97" t="s">
@@ -3351,7 +3350,7 @@
       <c r="E98" t="s">
         <v>10</v>
       </c>
-      <c r="F98">
+      <c r="F98" s="4">
         <v>34</v>
       </c>
       <c r="G98" s="2" t="s">
@@ -3377,7 +3376,7 @@
       <c r="E99" t="s">
         <v>10</v>
       </c>
-      <c r="F99">
+      <c r="F99" s="4">
         <v>28</v>
       </c>
       <c r="G99" t="s">
@@ -3403,7 +3402,7 @@
       <c r="E100" t="s">
         <v>10</v>
       </c>
-      <c r="F100">
+      <c r="F100" s="4">
         <v>32</v>
       </c>
       <c r="G100" t="s">
@@ -3429,7 +3428,7 @@
       <c r="E101" t="s">
         <v>10</v>
       </c>
-      <c r="F101">
+      <c r="F101" s="4">
         <v>39</v>
       </c>
       <c r="G101" s="2" t="s">
@@ -3455,7 +3454,7 @@
       <c r="E102" t="s">
         <v>10</v>
       </c>
-      <c r="F102">
+      <c r="F102" s="4">
         <v>29</v>
       </c>
       <c r="G102" t="s">
@@ -3481,7 +3480,7 @@
       <c r="E103" t="s">
         <v>10</v>
       </c>
-      <c r="F103">
+      <c r="F103" s="4">
         <v>32</v>
       </c>
       <c r="G103" s="2" t="s">
@@ -3507,7 +3506,7 @@
       <c r="E104" t="s">
         <v>14</v>
       </c>
-      <c r="F104">
+      <c r="F104" s="4">
         <v>25</v>
       </c>
       <c r="G104" t="s">
@@ -3533,7 +3532,7 @@
       <c r="E105" t="s">
         <v>19</v>
       </c>
-      <c r="F105">
+      <c r="F105" s="4">
         <v>36</v>
       </c>
       <c r="G105" t="s">
@@ -3559,7 +3558,7 @@
       <c r="E106" t="s">
         <v>10</v>
       </c>
-      <c r="F106">
+      <c r="F106" s="4">
         <v>25</v>
       </c>
       <c r="G106" s="2" t="s">
@@ -3585,7 +3584,7 @@
       <c r="E107" t="s">
         <v>10</v>
       </c>
-      <c r="F107">
+      <c r="F107" s="4">
         <v>58</v>
       </c>
       <c r="G107" t="s">
@@ -3611,7 +3610,7 @@
       <c r="E108" t="s">
         <v>10</v>
       </c>
-      <c r="F108">
+      <c r="F108" s="4">
         <v>24</v>
       </c>
       <c r="G108" t="s">
@@ -3637,7 +3636,7 @@
       <c r="E109" t="s">
         <v>14</v>
       </c>
-      <c r="F109">
+      <c r="F109" s="4">
         <v>56</v>
       </c>
       <c r="G109" s="2" t="s">
@@ -3663,7 +3662,7 @@
       <c r="E110" t="s">
         <v>10</v>
       </c>
-      <c r="F110">
+      <c r="F110" s="4">
         <v>27</v>
       </c>
       <c r="G110" t="s">
@@ -3689,7 +3688,7 @@
       <c r="E111" t="s">
         <v>10</v>
       </c>
-      <c r="F111">
+      <c r="F111" s="4">
         <v>40</v>
       </c>
       <c r="G111" t="s">
@@ -3715,7 +3714,7 @@
       <c r="E112" t="s">
         <v>14</v>
       </c>
-      <c r="F112">
+      <c r="F112" s="4">
         <v>28</v>
       </c>
       <c r="G112" t="s">
@@ -3741,7 +3740,7 @@
       <c r="E113" t="s">
         <v>14</v>
       </c>
-      <c r="F113">
+      <c r="F113" s="4">
         <v>39</v>
       </c>
       <c r="G113" t="s">
@@ -3767,7 +3766,7 @@
       <c r="E114" t="s">
         <v>19</v>
       </c>
-      <c r="F114">
+      <c r="F114" s="4">
         <v>38</v>
       </c>
       <c r="G114" s="2" t="s">
@@ -3793,7 +3792,7 @@
       <c r="E115" t="s">
         <v>14</v>
       </c>
-      <c r="F115">
+      <c r="F115" s="4">
         <v>32</v>
       </c>
       <c r="G115" t="s">
@@ -3819,7 +3818,7 @@
       <c r="E116" t="s">
         <v>14</v>
       </c>
-      <c r="F116">
+      <c r="F116" s="4">
         <v>26</v>
       </c>
       <c r="G116" t="s">
@@ -3845,7 +3844,7 @@
       <c r="E117" t="s">
         <v>14</v>
       </c>
-      <c r="F117">
+      <c r="F117" s="4">
         <v>31</v>
       </c>
       <c r="G117" t="s">
@@ -3871,7 +3870,7 @@
       <c r="E118" t="s">
         <v>19</v>
       </c>
-      <c r="F118">
+      <c r="F118" s="4">
         <v>24</v>
       </c>
       <c r="G118" t="s">
@@ -3897,7 +3896,7 @@
       <c r="E119" t="s">
         <v>19</v>
       </c>
-      <c r="F119">
+      <c r="F119" s="4">
         <v>39</v>
       </c>
       <c r="G119" s="2" t="s">
@@ -3923,7 +3922,7 @@
       <c r="E120" t="s">
         <v>14</v>
       </c>
-      <c r="F120">
+      <c r="F120" s="4">
         <v>28</v>
       </c>
       <c r="G120" t="s">
@@ -3949,7 +3948,7 @@
       <c r="E121" t="s">
         <v>19</v>
       </c>
-      <c r="F121">
+      <c r="F121" s="4">
         <v>26</v>
       </c>
       <c r="G121" t="s">
@@ -3975,7 +3974,7 @@
       <c r="E122" t="s">
         <v>19</v>
       </c>
-      <c r="F122">
+      <c r="F122" s="4">
         <v>46</v>
       </c>
       <c r="G122" t="s">
@@ -4001,7 +4000,7 @@
       <c r="E123" t="s">
         <v>10</v>
       </c>
-      <c r="F123">
+      <c r="F123" s="4">
         <v>37</v>
       </c>
       <c r="G123" s="2" t="s">
@@ -4027,7 +4026,7 @@
       <c r="E124" t="s">
         <v>10</v>
       </c>
-      <c r="F124">
+      <c r="F124" s="4">
         <v>52</v>
       </c>
       <c r="G124" t="s">
@@ -4053,7 +4052,7 @@
       <c r="E125" t="s">
         <v>14</v>
       </c>
-      <c r="F125">
+      <c r="F125" s="4">
         <v>46</v>
       </c>
       <c r="G125" t="s">
@@ -4079,7 +4078,7 @@
       <c r="E126" t="s">
         <v>19</v>
       </c>
-      <c r="F126">
+      <c r="F126" s="4">
         <v>42</v>
       </c>
       <c r="G126" t="s">
@@ -4105,7 +4104,7 @@
       <c r="E127" t="s">
         <v>19</v>
       </c>
-      <c r="F127">
+      <c r="F127" s="4">
         <v>21</v>
       </c>
       <c r="G127" s="2" t="s">
@@ -4131,7 +4130,7 @@
       <c r="E128" t="s">
         <v>14</v>
       </c>
-      <c r="F128">
+      <c r="F128" s="4">
         <v>28</v>
       </c>
       <c r="G128" t="s">
@@ -4157,7 +4156,7 @@
       <c r="E129" t="s">
         <v>10</v>
       </c>
-      <c r="F129">
+      <c r="F129" s="4">
         <v>29</v>
       </c>
       <c r="G129" t="s">
@@ -4183,7 +4182,7 @@
       <c r="E130" t="s">
         <v>19</v>
       </c>
-      <c r="F130">
+      <c r="F130" s="4">
         <v>23</v>
       </c>
       <c r="G130" s="2" t="s">
@@ -4209,7 +4208,7 @@
       <c r="E131" t="s">
         <v>10</v>
       </c>
-      <c r="F131">
+      <c r="F131" s="4">
         <v>41</v>
       </c>
       <c r="G131" t="s">
@@ -4235,7 +4234,7 @@
       <c r="E132" t="s">
         <v>14</v>
       </c>
-      <c r="F132">
+      <c r="F132" s="4">
         <v>28</v>
       </c>
       <c r="G132" t="s">
@@ -4261,7 +4260,7 @@
       <c r="E133" t="s">
         <v>14</v>
       </c>
-      <c r="F133">
+      <c r="F133" s="4">
         <v>37</v>
       </c>
       <c r="G133" s="2" t="s">
@@ -4287,7 +4286,7 @@
       <c r="E134" t="s">
         <v>14</v>
       </c>
-      <c r="F134">
+      <c r="F134" s="4">
         <v>34</v>
       </c>
       <c r="G134" t="s">
@@ -4313,7 +4312,7 @@
       <c r="E135" t="s">
         <v>14</v>
       </c>
-      <c r="F135">
+      <c r="F135" s="4">
         <v>26</v>
       </c>
       <c r="G135" t="s">
@@ -4339,7 +4338,7 @@
       <c r="E136" t="s">
         <v>19</v>
       </c>
-      <c r="F136">
+      <c r="F136" s="4">
         <v>35</v>
       </c>
       <c r="G136" t="s">
@@ -4365,7 +4364,7 @@
       <c r="E137" t="s">
         <v>10</v>
       </c>
-      <c r="F137">
+      <c r="F137" s="4">
         <v>36</v>
       </c>
       <c r="G137" t="s">
@@ -4391,7 +4390,7 @@
       <c r="E138" t="s">
         <v>10</v>
       </c>
-      <c r="F138">
+      <c r="F138" s="4">
         <v>29</v>
       </c>
       <c r="G138" s="2" t="s">
@@ -4417,7 +4416,7 @@
       <c r="E139" t="s">
         <v>19</v>
       </c>
-      <c r="F139">
+      <c r="F139" s="4">
         <v>27</v>
       </c>
       <c r="G139" t="s">
@@ -4443,7 +4442,7 @@
       <c r="E140" t="s">
         <v>10</v>
       </c>
-      <c r="F140">
+      <c r="F140" s="4">
         <v>25</v>
       </c>
       <c r="G140" t="s">
@@ -4469,7 +4468,7 @@
       <c r="E141" t="s">
         <v>10</v>
       </c>
-      <c r="F141">
+      <c r="F141" s="4">
         <v>36</v>
       </c>
       <c r="G141" t="s">
@@ -4495,7 +4494,7 @@
       <c r="E142" t="s">
         <v>10</v>
       </c>
-      <c r="F142">
+      <c r="F142" s="4">
         <v>37</v>
       </c>
       <c r="G142" s="2" t="s">
@@ -4521,7 +4520,7 @@
       <c r="E143" t="s">
         <v>10</v>
       </c>
-      <c r="F143">
+      <c r="F143" s="4">
         <v>26</v>
       </c>
       <c r="G143" t="s">
@@ -4547,7 +4546,7 @@
       <c r="E144" t="s">
         <v>10</v>
       </c>
-      <c r="F144">
+      <c r="F144" s="4">
         <v>37</v>
       </c>
       <c r="G144" t="s">
@@ -4573,7 +4572,7 @@
       <c r="E145" t="s">
         <v>19</v>
       </c>
-      <c r="F145">
+      <c r="F145" s="4">
         <v>24</v>
       </c>
       <c r="G145" s="2" t="s">
@@ -4599,7 +4598,7 @@
       <c r="E146" t="s">
         <v>10</v>
       </c>
-      <c r="F146">
+      <c r="F146" s="4">
         <v>39</v>
       </c>
       <c r="G146" t="s">
@@ -4625,7 +4624,7 @@
       <c r="E147" t="s">
         <v>10</v>
       </c>
-      <c r="F147">
+      <c r="F147" s="4">
         <v>26</v>
       </c>
       <c r="G147" t="s">
@@ -4651,7 +4650,7 @@
       <c r="E148" t="s">
         <v>10</v>
       </c>
-      <c r="F148">
+      <c r="F148" s="4">
         <v>34</v>
       </c>
       <c r="G148" s="2" t="s">
@@ -4677,7 +4676,7 @@
       <c r="E149" t="s">
         <v>10</v>
       </c>
-      <c r="F149">
+      <c r="F149" s="4">
         <v>28</v>
       </c>
       <c r="G149" t="s">
@@ -4703,7 +4702,7 @@
       <c r="E150" t="s">
         <v>10</v>
       </c>
-      <c r="F150">
+      <c r="F150" s="4">
         <v>32</v>
       </c>
       <c r="G150" t="s">
@@ -4729,7 +4728,7 @@
       <c r="E151" t="s">
         <v>10</v>
       </c>
-      <c r="F151">
+      <c r="F151" s="4">
         <v>39</v>
       </c>
       <c r="G151" s="2" t="s">
@@ -4755,7 +4754,7 @@
       <c r="E152" t="s">
         <v>10</v>
       </c>
-      <c r="F152">
+      <c r="F152" s="4">
         <v>29</v>
       </c>
       <c r="G152" t="s">
@@ -4781,7 +4780,7 @@
       <c r="E153" t="s">
         <v>10</v>
       </c>
-      <c r="F153">
+      <c r="F153" s="4">
         <v>32</v>
       </c>
       <c r="G153" s="2" t="s">
@@ -4807,7 +4806,7 @@
       <c r="E154" t="s">
         <v>14</v>
       </c>
-      <c r="F154">
+      <c r="F154" s="4">
         <v>25</v>
       </c>
       <c r="G154" t="s">
@@ -4833,7 +4832,7 @@
       <c r="E155" t="s">
         <v>19</v>
       </c>
-      <c r="F155">
+      <c r="F155" s="4">
         <v>36</v>
       </c>
       <c r="G155" t="s">
@@ -4859,7 +4858,7 @@
       <c r="E156" t="s">
         <v>10</v>
       </c>
-      <c r="F156">
+      <c r="F156" s="4">
         <v>25</v>
       </c>
       <c r="G156" s="2" t="s">
@@ -4885,7 +4884,7 @@
       <c r="E157" t="s">
         <v>10</v>
       </c>
-      <c r="F157">
+      <c r="F157" s="4">
         <v>58</v>
       </c>
       <c r="G157" t="s">
@@ -4911,7 +4910,7 @@
       <c r="E158" t="s">
         <v>10</v>
       </c>
-      <c r="F158">
+      <c r="F158" s="4">
         <v>24</v>
       </c>
       <c r="G158" t="s">
@@ -4937,7 +4936,7 @@
       <c r="E159" t="s">
         <v>14</v>
       </c>
-      <c r="F159">
+      <c r="F159" s="4">
         <v>56</v>
       </c>
       <c r="G159" s="2" t="s">
@@ -4963,7 +4962,7 @@
       <c r="E160" t="s">
         <v>10</v>
       </c>
-      <c r="F160">
+      <c r="F160" s="4">
         <v>27</v>
       </c>
       <c r="G160" t="s">
@@ -4989,7 +4988,7 @@
       <c r="E161" t="s">
         <v>10</v>
       </c>
-      <c r="F161">
+      <c r="F161" s="4">
         <v>40</v>
       </c>
       <c r="G161" t="s">
@@ -5015,7 +5014,7 @@
       <c r="E162" t="s">
         <v>14</v>
       </c>
-      <c r="F162">
+      <c r="F162" s="4">
         <v>28</v>
       </c>
       <c r="G162" t="s">
@@ -5041,7 +5040,7 @@
       <c r="E163" t="s">
         <v>14</v>
       </c>
-      <c r="F163">
+      <c r="F163" s="4">
         <v>39</v>
       </c>
       <c r="G163" t="s">
@@ -5067,7 +5066,7 @@
       <c r="E164" t="s">
         <v>19</v>
       </c>
-      <c r="F164">
+      <c r="F164" s="4">
         <v>38</v>
       </c>
       <c r="G164" s="2" t="s">
@@ -5093,7 +5092,7 @@
       <c r="E165" t="s">
         <v>14</v>
       </c>
-      <c r="F165">
+      <c r="F165" s="4">
         <v>32</v>
       </c>
       <c r="G165" t="s">
@@ -5119,7 +5118,7 @@
       <c r="E166" t="s">
         <v>14</v>
       </c>
-      <c r="F166">
+      <c r="F166" s="4">
         <v>26</v>
       </c>
       <c r="G166" t="s">
@@ -5145,7 +5144,7 @@
       <c r="E167" t="s">
         <v>14</v>
       </c>
-      <c r="F167">
+      <c r="F167" s="4">
         <v>31</v>
       </c>
       <c r="G167" t="s">
@@ -5171,7 +5170,7 @@
       <c r="E168" t="s">
         <v>19</v>
       </c>
-      <c r="F168">
+      <c r="F168" s="4">
         <v>24</v>
       </c>
       <c r="G168" t="s">
@@ -5197,7 +5196,7 @@
       <c r="E169" t="s">
         <v>19</v>
       </c>
-      <c r="F169">
+      <c r="F169" s="4">
         <v>39</v>
       </c>
       <c r="G169" s="2" t="s">
@@ -5223,7 +5222,7 @@
       <c r="E170" t="s">
         <v>14</v>
       </c>
-      <c r="F170">
+      <c r="F170" s="4">
         <v>28</v>
       </c>
       <c r="G170" t="s">
@@ -5249,7 +5248,7 @@
       <c r="E171" t="s">
         <v>19</v>
       </c>
-      <c r="F171">
+      <c r="F171" s="4">
         <v>26</v>
       </c>
       <c r="G171" t="s">
@@ -5275,7 +5274,7 @@
       <c r="E172" t="s">
         <v>19</v>
       </c>
-      <c r="F172">
+      <c r="F172" s="4">
         <v>46</v>
       </c>
       <c r="G172" t="s">
@@ -5301,7 +5300,7 @@
       <c r="E173" t="s">
         <v>10</v>
       </c>
-      <c r="F173">
+      <c r="F173" s="4">
         <v>37</v>
       </c>
       <c r="G173" s="2" t="s">
@@ -5327,7 +5326,7 @@
       <c r="E174" t="s">
         <v>10</v>
       </c>
-      <c r="F174">
+      <c r="F174" s="4">
         <v>52</v>
       </c>
       <c r="G174" t="s">
@@ -5353,7 +5352,7 @@
       <c r="E175" t="s">
         <v>14</v>
       </c>
-      <c r="F175">
+      <c r="F175" s="4">
         <v>46</v>
       </c>
       <c r="G175" t="s">
@@ -5379,7 +5378,7 @@
       <c r="E176" t="s">
         <v>19</v>
       </c>
-      <c r="F176">
+      <c r="F176" s="4">
         <v>42</v>
       </c>
       <c r="G176" t="s">
@@ -5405,7 +5404,7 @@
       <c r="E177" t="s">
         <v>19</v>
       </c>
-      <c r="F177">
+      <c r="F177" s="4">
         <v>21</v>
       </c>
       <c r="G177" s="2" t="s">
@@ -5431,7 +5430,7 @@
       <c r="E178" t="s">
         <v>14</v>
       </c>
-      <c r="F178">
+      <c r="F178" s="4">
         <v>28</v>
       </c>
       <c r="G178" t="s">
@@ -5457,7 +5456,7 @@
       <c r="E179" t="s">
         <v>10</v>
       </c>
-      <c r="F179">
+      <c r="F179" s="4">
         <v>29</v>
       </c>
       <c r="G179" t="s">
@@ -5483,7 +5482,7 @@
       <c r="E180" t="s">
         <v>19</v>
       </c>
-      <c r="F180">
+      <c r="F180" s="4">
         <v>23</v>
       </c>
       <c r="G180" s="2" t="s">
@@ -5509,7 +5508,7 @@
       <c r="E181" t="s">
         <v>10</v>
       </c>
-      <c r="F181">
+      <c r="F181" s="4">
         <v>41</v>
       </c>
       <c r="G181" t="s">
@@ -5535,7 +5534,7 @@
       <c r="E182" t="s">
         <v>14</v>
       </c>
-      <c r="F182">
+      <c r="F182" s="4">
         <v>28</v>
       </c>
       <c r="G182" t="s">
@@ -5561,7 +5560,7 @@
       <c r="E183" t="s">
         <v>14</v>
       </c>
-      <c r="F183">
+      <c r="F183" s="4">
         <v>37</v>
       </c>
       <c r="G183" s="2" t="s">
@@ -5587,7 +5586,7 @@
       <c r="E184" t="s">
         <v>14</v>
       </c>
-      <c r="F184">
+      <c r="F184" s="4">
         <v>34</v>
       </c>
       <c r="G184" t="s">
@@ -5613,7 +5612,7 @@
       <c r="E185" t="s">
         <v>14</v>
       </c>
-      <c r="F185">
+      <c r="F185" s="4">
         <v>26</v>
       </c>
       <c r="G185" t="s">
@@ -5639,7 +5638,7 @@
       <c r="E186" t="s">
         <v>19</v>
       </c>
-      <c r="F186">
+      <c r="F186" s="4">
         <v>35</v>
       </c>
       <c r="G186" t="s">
@@ -5665,7 +5664,7 @@
       <c r="E187" t="s">
         <v>10</v>
       </c>
-      <c r="F187">
+      <c r="F187" s="4">
         <v>36</v>
       </c>
       <c r="G187" t="s">
@@ -5691,7 +5690,7 @@
       <c r="E188" t="s">
         <v>10</v>
       </c>
-      <c r="F188">
+      <c r="F188" s="4">
         <v>29</v>
       </c>
       <c r="G188" s="2" t="s">
@@ -5717,7 +5716,7 @@
       <c r="E189" t="s">
         <v>19</v>
       </c>
-      <c r="F189">
+      <c r="F189" s="4">
         <v>27</v>
       </c>
       <c r="G189" t="s">
@@ -5743,7 +5742,7 @@
       <c r="E190" t="s">
         <v>10</v>
       </c>
-      <c r="F190">
+      <c r="F190" s="4">
         <v>25</v>
       </c>
       <c r="G190" t="s">
@@ -5769,7 +5768,7 @@
       <c r="E191" t="s">
         <v>10</v>
       </c>
-      <c r="F191">
+      <c r="F191" s="4">
         <v>36</v>
       </c>
       <c r="G191" t="s">
@@ -5795,7 +5794,7 @@
       <c r="E192" t="s">
         <v>10</v>
       </c>
-      <c r="F192">
+      <c r="F192" s="4">
         <v>37</v>
       </c>
       <c r="G192" s="2" t="s">
@@ -5821,7 +5820,7 @@
       <c r="E193" t="s">
         <v>10</v>
       </c>
-      <c r="F193">
+      <c r="F193" s="4">
         <v>26</v>
       </c>
       <c r="G193" t="s">
@@ -5847,7 +5846,7 @@
       <c r="E194" t="s">
         <v>10</v>
       </c>
-      <c r="F194">
+      <c r="F194" s="4">
         <v>37</v>
       </c>
       <c r="G194" t="s">
@@ -5873,7 +5872,7 @@
       <c r="E195" t="s">
         <v>19</v>
       </c>
-      <c r="F195">
+      <c r="F195" s="4">
         <v>24</v>
       </c>
       <c r="G195" s="2" t="s">
@@ -5899,7 +5898,7 @@
       <c r="E196" t="s">
         <v>10</v>
       </c>
-      <c r="F196">
+      <c r="F196" s="4">
         <v>39</v>
       </c>
       <c r="G196" t="s">
@@ -5925,7 +5924,7 @@
       <c r="E197" t="s">
         <v>10</v>
       </c>
-      <c r="F197">
+      <c r="F197" s="4">
         <v>26</v>
       </c>
       <c r="G197" t="s">
@@ -5951,7 +5950,7 @@
       <c r="E198" t="s">
         <v>10</v>
       </c>
-      <c r="F198">
+      <c r="F198" s="4">
         <v>34</v>
       </c>
       <c r="G198" s="2" t="s">
@@ -5977,7 +5976,7 @@
       <c r="E199" t="s">
         <v>10</v>
       </c>
-      <c r="F199">
+      <c r="F199" s="4">
         <v>28</v>
       </c>
       <c r="G199" t="s">
@@ -6003,7 +6002,7 @@
       <c r="E200" t="s">
         <v>10</v>
       </c>
-      <c r="F200">
+      <c r="F200" s="4">
         <v>32</v>
       </c>
       <c r="G200" t="s">
@@ -6029,7 +6028,7 @@
       <c r="E201" t="s">
         <v>10</v>
       </c>
-      <c r="F201">
+      <c r="F201" s="4">
         <v>39</v>
       </c>
       <c r="G201" s="2" t="s">
@@ -6055,7 +6054,7 @@
       <c r="E202" t="s">
         <v>10</v>
       </c>
-      <c r="F202">
+      <c r="F202" s="4">
         <v>29</v>
       </c>
       <c r="G202" t="s">
@@ -6081,7 +6080,7 @@
       <c r="E203" t="s">
         <v>10</v>
       </c>
-      <c r="F203">
+      <c r="F203" s="4">
         <v>32</v>
       </c>
       <c r="G203" s="2" t="s">
@@ -6107,7 +6106,7 @@
       <c r="E204" t="s">
         <v>14</v>
       </c>
-      <c r="F204">
+      <c r="F204" s="4">
         <v>25</v>
       </c>
       <c r="G204" t="s">
@@ -6133,7 +6132,7 @@
       <c r="E205" t="s">
         <v>19</v>
       </c>
-      <c r="F205">
+      <c r="F205" s="4">
         <v>36</v>
       </c>
       <c r="G205" t="s">
@@ -6159,7 +6158,7 @@
       <c r="E206" t="s">
         <v>10</v>
       </c>
-      <c r="F206">
+      <c r="F206" s="4">
         <v>25</v>
       </c>
       <c r="G206" s="2" t="s">
@@ -6185,7 +6184,7 @@
       <c r="E207" t="s">
         <v>10</v>
       </c>
-      <c r="F207">
+      <c r="F207" s="4">
         <v>58</v>
       </c>
       <c r="G207" t="s">
@@ -6211,7 +6210,7 @@
       <c r="E208" t="s">
         <v>10</v>
       </c>
-      <c r="F208">
+      <c r="F208" s="4">
         <v>24</v>
       </c>
       <c r="G208" t="s">
@@ -6237,7 +6236,7 @@
       <c r="E209" t="s">
         <v>14</v>
       </c>
-      <c r="F209">
+      <c r="F209" s="4">
         <v>56</v>
       </c>
       <c r="G209" s="2" t="s">
@@ -6263,7 +6262,7 @@
       <c r="E210" t="s">
         <v>10</v>
       </c>
-      <c r="F210">
+      <c r="F210" s="4">
         <v>27</v>
       </c>
       <c r="G210" t="s">
@@ -6289,7 +6288,7 @@
       <c r="E211" t="s">
         <v>10</v>
       </c>
-      <c r="F211">
+      <c r="F211" s="4">
         <v>40</v>
       </c>
       <c r="G211" t="s">
@@ -6315,7 +6314,7 @@
       <c r="E212" t="s">
         <v>14</v>
       </c>
-      <c r="F212">
+      <c r="F212" s="4">
         <v>28</v>
       </c>
       <c r="G212" t="s">
@@ -6341,7 +6340,7 @@
       <c r="E213" t="s">
         <v>14</v>
       </c>
-      <c r="F213">
+      <c r="F213" s="4">
         <v>39</v>
       </c>
       <c r="G213" t="s">
@@ -6367,7 +6366,7 @@
       <c r="E214" t="s">
         <v>19</v>
       </c>
-      <c r="F214">
+      <c r="F214" s="4">
         <v>38</v>
       </c>
       <c r="G214" s="2" t="s">
@@ -6393,7 +6392,7 @@
       <c r="E215" t="s">
         <v>14</v>
       </c>
-      <c r="F215">
+      <c r="F215" s="4">
         <v>32</v>
       </c>
       <c r="G215" t="s">
@@ -6419,7 +6418,7 @@
       <c r="E216" t="s">
         <v>14</v>
       </c>
-      <c r="F216">
+      <c r="F216" s="4">
         <v>26</v>
       </c>
       <c r="G216" t="s">
@@ -6445,7 +6444,7 @@
       <c r="E217" t="s">
         <v>14</v>
       </c>
-      <c r="F217">
+      <c r="F217" s="4">
         <v>31</v>
       </c>
       <c r="G217" t="s">
@@ -6471,7 +6470,7 @@
       <c r="E218" t="s">
         <v>19</v>
       </c>
-      <c r="F218">
+      <c r="F218" s="4">
         <v>24</v>
       </c>
       <c r="G218" t="s">
@@ -6497,7 +6496,7 @@
       <c r="E219" t="s">
         <v>19</v>
       </c>
-      <c r="F219">
+      <c r="F219" s="4">
         <v>39</v>
       </c>
       <c r="G219" s="2" t="s">
@@ -6523,7 +6522,7 @@
       <c r="E220" t="s">
         <v>14</v>
       </c>
-      <c r="F220">
+      <c r="F220" s="4">
         <v>28</v>
       </c>
       <c r="G220" t="s">
@@ -6549,7 +6548,7 @@
       <c r="E221" t="s">
         <v>19</v>
       </c>
-      <c r="F221">
+      <c r="F221" s="4">
         <v>26</v>
       </c>
       <c r="G221" t="s">
@@ -6575,7 +6574,7 @@
       <c r="E222" t="s">
         <v>19</v>
       </c>
-      <c r="F222">
+      <c r="F222" s="4">
         <v>46</v>
       </c>
       <c r="G222" t="s">
@@ -6601,7 +6600,7 @@
       <c r="E223" t="s">
         <v>10</v>
       </c>
-      <c r="F223">
+      <c r="F223" s="4">
         <v>37</v>
       </c>
       <c r="G223" s="2" t="s">
@@ -6627,7 +6626,7 @@
       <c r="E224" t="s">
         <v>10</v>
       </c>
-      <c r="F224">
+      <c r="F224" s="4">
         <v>52</v>
       </c>
       <c r="G224" t="s">
@@ -6653,7 +6652,7 @@
       <c r="E225" t="s">
         <v>14</v>
       </c>
-      <c r="F225">
+      <c r="F225" s="4">
         <v>46</v>
       </c>
       <c r="G225" t="s">
@@ -6679,7 +6678,7 @@
       <c r="E226" t="s">
         <v>19</v>
       </c>
-      <c r="F226">
+      <c r="F226" s="4">
         <v>42</v>
       </c>
       <c r="G226" t="s">
@@ -6705,7 +6704,7 @@
       <c r="E227" t="s">
         <v>19</v>
       </c>
-      <c r="F227">
+      <c r="F227" s="4">
         <v>21</v>
       </c>
       <c r="G227" s="2" t="s">
@@ -6731,7 +6730,7 @@
       <c r="E228" t="s">
         <v>14</v>
       </c>
-      <c r="F228">
+      <c r="F228" s="4">
         <v>28</v>
       </c>
       <c r="G228" t="s">
@@ -6757,7 +6756,7 @@
       <c r="E229" t="s">
         <v>10</v>
       </c>
-      <c r="F229">
+      <c r="F229" s="4">
         <v>29</v>
       </c>
       <c r="G229" t="s">
@@ -6783,7 +6782,7 @@
       <c r="E230" t="s">
         <v>19</v>
       </c>
-      <c r="F230">
+      <c r="F230" s="4">
         <v>23</v>
       </c>
       <c r="G230" s="2" t="s">
@@ -6809,7 +6808,7 @@
       <c r="E231" t="s">
         <v>10</v>
       </c>
-      <c r="F231">
+      <c r="F231" s="4">
         <v>41</v>
       </c>
       <c r="G231" t="s">
@@ -6835,7 +6834,7 @@
       <c r="E232" t="s">
         <v>14</v>
       </c>
-      <c r="F232">
+      <c r="F232" s="4">
         <v>28</v>
       </c>
       <c r="G232" t="s">
@@ -6861,7 +6860,7 @@
       <c r="E233" t="s">
         <v>14</v>
       </c>
-      <c r="F233">
+      <c r="F233" s="4">
         <v>37</v>
       </c>
       <c r="G233" s="2" t="s">
@@ -6887,7 +6886,7 @@
       <c r="E234" t="s">
         <v>14</v>
       </c>
-      <c r="F234">
+      <c r="F234" s="4">
         <v>34</v>
       </c>
       <c r="G234" t="s">
@@ -6913,7 +6912,7 @@
       <c r="E235" t="s">
         <v>14</v>
       </c>
-      <c r="F235">
+      <c r="F235" s="4">
         <v>26</v>
       </c>
       <c r="G235" t="s">
@@ -6939,7 +6938,7 @@
       <c r="E236" t="s">
         <v>19</v>
       </c>
-      <c r="F236">
+      <c r="F236" s="4">
         <v>35</v>
       </c>
       <c r="G236" t="s">
@@ -6965,7 +6964,7 @@
       <c r="E237" t="s">
         <v>10</v>
       </c>
-      <c r="F237">
+      <c r="F237" s="4">
         <v>36</v>
       </c>
       <c r="G237" t="s">
@@ -6991,7 +6990,7 @@
       <c r="E238" t="s">
         <v>10</v>
       </c>
-      <c r="F238">
+      <c r="F238" s="4">
         <v>29</v>
       </c>
       <c r="G238" s="2" t="s">
@@ -7017,7 +7016,7 @@
       <c r="E239" t="s">
         <v>19</v>
       </c>
-      <c r="F239">
+      <c r="F239" s="4">
         <v>27</v>
       </c>
       <c r="G239" t="s">
@@ -7043,7 +7042,7 @@
       <c r="E240" t="s">
         <v>10</v>
       </c>
-      <c r="F240">
+      <c r="F240" s="4">
         <v>25</v>
       </c>
       <c r="G240" t="s">
@@ -7069,7 +7068,7 @@
       <c r="E241" t="s">
         <v>10</v>
       </c>
-      <c r="F241">
+      <c r="F241" s="4">
         <v>36</v>
       </c>
       <c r="G241" t="s">
@@ -7095,7 +7094,7 @@
       <c r="E242" t="s">
         <v>10</v>
       </c>
-      <c r="F242">
+      <c r="F242" s="4">
         <v>37</v>
       </c>
       <c r="G242" s="2" t="s">
@@ -7121,7 +7120,7 @@
       <c r="E243" t="s">
         <v>10</v>
       </c>
-      <c r="F243">
+      <c r="F243" s="4">
         <v>26</v>
       </c>
       <c r="G243" t="s">
@@ -7147,7 +7146,7 @@
       <c r="E244" t="s">
         <v>10</v>
       </c>
-      <c r="F244">
+      <c r="F244" s="4">
         <v>37</v>
       </c>
       <c r="G244" t="s">
@@ -7173,7 +7172,7 @@
       <c r="E245" t="s">
         <v>19</v>
       </c>
-      <c r="F245">
+      <c r="F245" s="4">
         <v>24</v>
       </c>
       <c r="G245" s="2" t="s">
@@ -7199,7 +7198,7 @@
       <c r="E246" t="s">
         <v>10</v>
       </c>
-      <c r="F246">
+      <c r="F246" s="4">
         <v>39</v>
       </c>
       <c r="G246" t="s">
@@ -7225,7 +7224,7 @@
       <c r="E247" t="s">
         <v>10</v>
       </c>
-      <c r="F247">
+      <c r="F247" s="4">
         <v>26</v>
       </c>
       <c r="G247" t="s">
@@ -7251,7 +7250,7 @@
       <c r="E248" t="s">
         <v>10</v>
       </c>
-      <c r="F248">
+      <c r="F248" s="4">
         <v>34</v>
       </c>
       <c r="G248" s="2" t="s">
@@ -7277,7 +7276,7 @@
       <c r="E249" t="s">
         <v>10</v>
       </c>
-      <c r="F249">
+      <c r="F249" s="4">
         <v>28</v>
       </c>
       <c r="G249" t="s">
@@ -7303,7 +7302,7 @@
       <c r="E250" t="s">
         <v>10</v>
       </c>
-      <c r="F250">
+      <c r="F250" s="4">
         <v>32</v>
       </c>
       <c r="G250" t="s">
@@ -7329,7 +7328,7 @@
       <c r="E251" t="s">
         <v>10</v>
       </c>
-      <c r="F251">
+      <c r="F251" s="4">
         <v>39</v>
       </c>
       <c r="G251" s="2" t="s">
@@ -7355,7 +7354,7 @@
       <c r="E252" t="s">
         <v>10</v>
       </c>
-      <c r="F252">
+      <c r="F252" s="4">
         <v>29</v>
       </c>
       <c r="G252" t="s">
@@ -7381,7 +7380,7 @@
       <c r="E253" t="s">
         <v>10</v>
       </c>
-      <c r="F253">
+      <c r="F253" s="4">
         <v>32</v>
       </c>
       <c r="G253" s="2" t="s">
@@ -7407,7 +7406,7 @@
       <c r="E254" t="s">
         <v>14</v>
       </c>
-      <c r="F254">
+      <c r="F254" s="4">
         <v>25</v>
       </c>
       <c r="G254" t="s">
@@ -7433,7 +7432,7 @@
       <c r="E255" t="s">
         <v>19</v>
       </c>
-      <c r="F255">
+      <c r="F255" s="4">
         <v>36</v>
       </c>
       <c r="G255" t="s">
@@ -7459,7 +7458,7 @@
       <c r="E256" t="s">
         <v>10</v>
       </c>
-      <c r="F256">
+      <c r="F256" s="4">
         <v>25</v>
       </c>
       <c r="G256" s="2" t="s">
@@ -7485,7 +7484,7 @@
       <c r="E257" t="s">
         <v>10</v>
       </c>
-      <c r="F257">
+      <c r="F257" s="4">
         <v>58</v>
       </c>
       <c r="G257" t="s">
@@ -7511,7 +7510,7 @@
       <c r="E258" t="s">
         <v>10</v>
       </c>
-      <c r="F258">
+      <c r="F258" s="4">
         <v>24</v>
       </c>
       <c r="G258" t="s">
@@ -7537,7 +7536,7 @@
       <c r="E259" t="s">
         <v>14</v>
       </c>
-      <c r="F259">
+      <c r="F259" s="4">
         <v>56</v>
       </c>
       <c r="G259" s="2" t="s">
@@ -7563,7 +7562,7 @@
       <c r="E260" t="s">
         <v>10</v>
       </c>
-      <c r="F260">
+      <c r="F260" s="4">
         <v>27</v>
       </c>
       <c r="G260" t="s">
@@ -7589,7 +7588,7 @@
       <c r="E261" t="s">
         <v>10</v>
       </c>
-      <c r="F261">
+      <c r="F261" s="4">
         <v>40</v>
       </c>
       <c r="G261" t="s">
@@ -7615,7 +7614,7 @@
       <c r="E262" t="s">
         <v>14</v>
       </c>
-      <c r="F262">
+      <c r="F262" s="4">
         <v>28</v>
       </c>
       <c r="G262" t="s">
@@ -7641,7 +7640,7 @@
       <c r="E263" t="s">
         <v>14</v>
       </c>
-      <c r="F263">
+      <c r="F263" s="4">
         <v>39</v>
       </c>
       <c r="G263" t="s">
@@ -7667,7 +7666,7 @@
       <c r="E264" t="s">
         <v>19</v>
       </c>
-      <c r="F264">
+      <c r="F264" s="4">
         <v>38</v>
       </c>
       <c r="G264" s="2" t="s">
@@ -7693,7 +7692,7 @@
       <c r="E265" t="s">
         <v>14</v>
       </c>
-      <c r="F265">
+      <c r="F265" s="4">
         <v>32</v>
       </c>
       <c r="G265" t="s">
@@ -7719,7 +7718,7 @@
       <c r="E266" t="s">
         <v>14</v>
       </c>
-      <c r="F266">
+      <c r="F266" s="4">
         <v>26</v>
       </c>
       <c r="G266" t="s">
@@ -7745,7 +7744,7 @@
       <c r="E267" t="s">
         <v>14</v>
       </c>
-      <c r="F267">
+      <c r="F267" s="4">
         <v>31</v>
       </c>
       <c r="G267" t="s">
@@ -7771,7 +7770,7 @@
       <c r="E268" t="s">
         <v>19</v>
       </c>
-      <c r="F268">
+      <c r="F268" s="4">
         <v>24</v>
       </c>
       <c r="G268" t="s">
@@ -7797,7 +7796,7 @@
       <c r="E269" t="s">
         <v>19</v>
       </c>
-      <c r="F269">
+      <c r="F269" s="4">
         <v>39</v>
       </c>
       <c r="G269" s="2" t="s">
@@ -7823,7 +7822,7 @@
       <c r="E270" t="s">
         <v>14</v>
       </c>
-      <c r="F270">
+      <c r="F270" s="4">
         <v>28</v>
       </c>
       <c r="G270" t="s">
@@ -7849,7 +7848,7 @@
       <c r="E271" t="s">
         <v>19</v>
       </c>
-      <c r="F271">
+      <c r="F271" s="4">
         <v>26</v>
       </c>
       <c r="G271" t="s">
@@ -7875,7 +7874,7 @@
       <c r="E272" t="s">
         <v>19</v>
       </c>
-      <c r="F272">
+      <c r="F272" s="4">
         <v>46</v>
       </c>
       <c r="G272" t="s">
@@ -7901,7 +7900,7 @@
       <c r="E273" t="s">
         <v>10</v>
       </c>
-      <c r="F273">
+      <c r="F273" s="4">
         <v>37</v>
       </c>
       <c r="G273" s="2" t="s">
@@ -7927,7 +7926,7 @@
       <c r="E274" t="s">
         <v>10</v>
       </c>
-      <c r="F274">
+      <c r="F274" s="4">
         <v>52</v>
       </c>
       <c r="G274" t="s">
@@ -7953,7 +7952,7 @@
       <c r="E275" t="s">
         <v>14</v>
       </c>
-      <c r="F275">
+      <c r="F275" s="4">
         <v>46</v>
       </c>
       <c r="G275" t="s">
@@ -7979,7 +7978,7 @@
       <c r="E276" t="s">
         <v>19</v>
       </c>
-      <c r="F276">
+      <c r="F276" s="4">
         <v>42</v>
       </c>
       <c r="G276" t="s">
@@ -8005,7 +8004,7 @@
       <c r="E277" t="s">
         <v>19</v>
       </c>
-      <c r="F277">
+      <c r="F277" s="4">
         <v>21</v>
       </c>
       <c r="G277" s="2" t="s">
@@ -8031,7 +8030,7 @@
       <c r="E278" t="s">
         <v>14</v>
       </c>
-      <c r="F278">
+      <c r="F278" s="4">
         <v>28</v>
       </c>
       <c r="G278" t="s">
@@ -8057,7 +8056,7 @@
       <c r="E279" t="s">
         <v>10</v>
       </c>
-      <c r="F279">
+      <c r="F279" s="4">
         <v>29</v>
       </c>
       <c r="G279" t="s">
@@ -8083,7 +8082,7 @@
       <c r="E280" t="s">
         <v>19</v>
       </c>
-      <c r="F280">
+      <c r="F280" s="4">
         <v>23</v>
       </c>
       <c r="G280" s="2" t="s">
@@ -8109,7 +8108,7 @@
       <c r="E281" t="s">
         <v>10</v>
       </c>
-      <c r="F281">
+      <c r="F281" s="4">
         <v>41</v>
       </c>
       <c r="G281" t="s">
@@ -8135,7 +8134,7 @@
       <c r="E282" t="s">
         <v>14</v>
       </c>
-      <c r="F282">
+      <c r="F282" s="4">
         <v>28</v>
       </c>
       <c r="G282" t="s">
@@ -8161,7 +8160,7 @@
       <c r="E283" t="s">
         <v>14</v>
       </c>
-      <c r="F283">
+      <c r="F283" s="4">
         <v>37</v>
       </c>
       <c r="G283" s="2" t="s">
@@ -8187,7 +8186,7 @@
       <c r="E284" t="s">
         <v>14</v>
       </c>
-      <c r="F284">
+      <c r="F284" s="4">
         <v>34</v>
       </c>
       <c r="G284" t="s">
@@ -8213,7 +8212,7 @@
       <c r="E285" t="s">
         <v>14</v>
       </c>
-      <c r="F285">
+      <c r="F285" s="4">
         <v>26</v>
       </c>
       <c r="G285" t="s">
@@ -8239,7 +8238,7 @@
       <c r="E286" t="s">
         <v>19</v>
       </c>
-      <c r="F286">
+      <c r="F286" s="4">
         <v>35</v>
       </c>
       <c r="G286" t="s">
@@ -8265,7 +8264,7 @@
       <c r="E287" t="s">
         <v>10</v>
       </c>
-      <c r="F287">
+      <c r="F287" s="4">
         <v>36</v>
       </c>
       <c r="G287" t="s">
@@ -8291,7 +8290,7 @@
       <c r="E288" t="s">
         <v>10</v>
       </c>
-      <c r="F288">
+      <c r="F288" s="4">
         <v>29</v>
       </c>
       <c r="G288" s="2" t="s">
@@ -8317,7 +8316,7 @@
       <c r="E289" t="s">
         <v>19</v>
       </c>
-      <c r="F289">
+      <c r="F289" s="4">
         <v>27</v>
       </c>
       <c r="G289" t="s">
@@ -8343,7 +8342,7 @@
       <c r="E290" t="s">
         <v>10</v>
       </c>
-      <c r="F290">
+      <c r="F290" s="4">
         <v>25</v>
       </c>
       <c r="G290" t="s">
@@ -8369,7 +8368,7 @@
       <c r="E291" t="s">
         <v>10</v>
       </c>
-      <c r="F291">
+      <c r="F291" s="4">
         <v>36</v>
       </c>
       <c r="G291" t="s">
@@ -8395,7 +8394,7 @@
       <c r="E292" t="s">
         <v>10</v>
       </c>
-      <c r="F292">
+      <c r="F292" s="4">
         <v>37</v>
       </c>
       <c r="G292" s="2" t="s">
@@ -8421,7 +8420,7 @@
       <c r="E293" t="s">
         <v>10</v>
       </c>
-      <c r="F293">
+      <c r="F293" s="4">
         <v>26</v>
       </c>
       <c r="G293" t="s">
@@ -8447,7 +8446,7 @@
       <c r="E294" t="s">
         <v>10</v>
       </c>
-      <c r="F294">
+      <c r="F294" s="4">
         <v>37</v>
       </c>
       <c r="G294" t="s">
@@ -8473,7 +8472,7 @@
       <c r="E295" t="s">
         <v>19</v>
       </c>
-      <c r="F295">
+      <c r="F295" s="4">
         <v>24</v>
       </c>
       <c r="G295" s="2" t="s">
@@ -8499,7 +8498,7 @@
       <c r="E296" t="s">
         <v>10</v>
       </c>
-      <c r="F296">
+      <c r="F296" s="4">
         <v>39</v>
       </c>
       <c r="G296" t="s">
@@ -8525,7 +8524,7 @@
       <c r="E297" t="s">
         <v>10</v>
       </c>
-      <c r="F297">
+      <c r="F297" s="4">
         <v>26</v>
       </c>
       <c r="G297" t="s">
@@ -8551,7 +8550,7 @@
       <c r="E298" t="s">
         <v>10</v>
       </c>
-      <c r="F298">
+      <c r="F298" s="4">
         <v>34</v>
       </c>
       <c r="G298" s="2" t="s">
@@ -8577,7 +8576,7 @@
       <c r="E299" t="s">
         <v>10</v>
       </c>
-      <c r="F299">
+      <c r="F299" s="4">
         <v>28</v>
       </c>
       <c r="G299" t="s">
@@ -8603,7 +8602,7 @@
       <c r="E300" t="s">
         <v>10</v>
       </c>
-      <c r="F300">
+      <c r="F300" s="4">
         <v>32</v>
       </c>
       <c r="G300" t="s">
@@ -8629,7 +8628,7 @@
       <c r="E301" t="s">
         <v>10</v>
       </c>
-      <c r="F301">
+      <c r="F301" s="4">
         <v>39</v>
       </c>
       <c r="G301" s="2" t="s">
@@ -8655,7 +8654,7 @@
       <c r="E302" t="s">
         <v>10</v>
       </c>
-      <c r="F302">
+      <c r="F302" s="4">
         <v>29</v>
       </c>
       <c r="G302" t="s">
@@ -8681,7 +8680,7 @@
       <c r="E303" t="s">
         <v>10</v>
       </c>
-      <c r="F303">
+      <c r="F303" s="4">
         <v>32</v>
       </c>
       <c r="G303" s="2" t="s">
@@ -8707,7 +8706,7 @@
       <c r="E304" t="s">
         <v>14</v>
       </c>
-      <c r="F304">
+      <c r="F304" s="4">
         <v>25</v>
       </c>
       <c r="G304" t="s">
@@ -8733,7 +8732,7 @@
       <c r="E305" t="s">
         <v>19</v>
       </c>
-      <c r="F305">
+      <c r="F305" s="4">
         <v>36</v>
       </c>
       <c r="G305" t="s">
@@ -8759,7 +8758,7 @@
       <c r="E306" t="s">
         <v>10</v>
       </c>
-      <c r="F306">
+      <c r="F306" s="4">
         <v>25</v>
       </c>
       <c r="G306" s="2" t="s">
@@ -8785,7 +8784,7 @@
       <c r="E307" t="s">
         <v>10</v>
       </c>
-      <c r="F307">
+      <c r="F307" s="4">
         <v>58</v>
       </c>
       <c r="G307" t="s">
@@ -8811,7 +8810,7 @@
       <c r="E308" t="s">
         <v>10</v>
       </c>
-      <c r="F308">
+      <c r="F308" s="4">
         <v>24</v>
       </c>
       <c r="G308" t="s">
@@ -8837,7 +8836,7 @@
       <c r="E309" t="s">
         <v>14</v>
       </c>
-      <c r="F309">
+      <c r="F309" s="4">
         <v>56</v>
       </c>
       <c r="G309" s="2" t="s">
@@ -8863,7 +8862,7 @@
       <c r="E310" t="s">
         <v>10</v>
       </c>
-      <c r="F310">
+      <c r="F310" s="4">
         <v>27</v>
       </c>
       <c r="G310" t="s">
@@ -8889,7 +8888,7 @@
       <c r="E311" t="s">
         <v>10</v>
       </c>
-      <c r="F311">
+      <c r="F311" s="4">
         <v>40</v>
       </c>
       <c r="G311" t="s">
@@ -8915,7 +8914,7 @@
       <c r="E312" t="s">
         <v>14</v>
       </c>
-      <c r="F312">
+      <c r="F312" s="4">
         <v>28</v>
       </c>
       <c r="G312" t="s">
@@ -8941,7 +8940,7 @@
       <c r="E313" t="s">
         <v>14</v>
       </c>
-      <c r="F313">
+      <c r="F313" s="4">
         <v>39</v>
       </c>
       <c r="G313" t="s">
@@ -8967,7 +8966,7 @@
       <c r="E314" t="s">
         <v>19</v>
       </c>
-      <c r="F314">
+      <c r="F314" s="4">
         <v>38</v>
       </c>
       <c r="G314" s="2" t="s">
@@ -8993,7 +8992,7 @@
       <c r="E315" t="s">
         <v>14</v>
       </c>
-      <c r="F315">
+      <c r="F315" s="4">
         <v>32</v>
       </c>
       <c r="G315" t="s">
@@ -9019,7 +9018,7 @@
       <c r="E316" t="s">
         <v>14</v>
       </c>
-      <c r="F316">
+      <c r="F316" s="4">
         <v>26</v>
       </c>
       <c r="G316" t="s">
@@ -9045,7 +9044,7 @@
       <c r="E317" t="s">
         <v>14</v>
       </c>
-      <c r="F317">
+      <c r="F317" s="4">
         <v>31</v>
       </c>
       <c r="G317" t="s">
@@ -9071,7 +9070,7 @@
       <c r="E318" t="s">
         <v>19</v>
       </c>
-      <c r="F318">
+      <c r="F318" s="4">
         <v>24</v>
       </c>
       <c r="G318" t="s">
@@ -9097,7 +9096,7 @@
       <c r="E319" t="s">
         <v>19</v>
       </c>
-      <c r="F319">
+      <c r="F319" s="4">
         <v>39</v>
       </c>
       <c r="G319" s="2" t="s">
@@ -9123,7 +9122,7 @@
       <c r="E320" t="s">
         <v>14</v>
       </c>
-      <c r="F320">
+      <c r="F320" s="4">
         <v>28</v>
       </c>
       <c r="G320" t="s">
@@ -9149,7 +9148,7 @@
       <c r="E321" t="s">
         <v>19</v>
       </c>
-      <c r="F321">
+      <c r="F321" s="4">
         <v>26</v>
       </c>
       <c r="G321" t="s">
@@ -9175,7 +9174,7 @@
       <c r="E322" t="s">
         <v>19</v>
       </c>
-      <c r="F322">
+      <c r="F322" s="4">
         <v>46</v>
       </c>
       <c r="G322" t="s">
@@ -9201,7 +9200,7 @@
       <c r="E323" t="s">
         <v>10</v>
       </c>
-      <c r="F323">
+      <c r="F323" s="4">
         <v>37</v>
       </c>
       <c r="G323" s="2" t="s">
@@ -9227,7 +9226,7 @@
       <c r="E324" t="s">
         <v>10</v>
       </c>
-      <c r="F324">
+      <c r="F324" s="4">
         <v>52</v>
       </c>
       <c r="G324" t="s">
@@ -9253,7 +9252,7 @@
       <c r="E325" t="s">
         <v>10</v>
       </c>
-      <c r="F325">
+      <c r="F325" s="4">
         <v>52</v>
       </c>
       <c r="G325" t="s">
@@ -9279,7 +9278,7 @@
       <c r="E326" t="s">
         <v>14</v>
       </c>
-      <c r="F326">
+      <c r="F326" s="4">
         <v>46</v>
       </c>
       <c r="G326" t="s">
@@ -9305,7 +9304,7 @@
       <c r="E327" t="s">
         <v>19</v>
       </c>
-      <c r="F327">
+      <c r="F327" s="4">
         <v>42</v>
       </c>
       <c r="G327" t="s">
@@ -9331,7 +9330,7 @@
       <c r="E328" t="s">
         <v>19</v>
       </c>
-      <c r="F328">
+      <c r="F328" s="4">
         <v>21</v>
       </c>
       <c r="G328" s="2" t="s">
@@ -9357,7 +9356,7 @@
       <c r="E329" t="s">
         <v>14</v>
       </c>
-      <c r="F329">
+      <c r="F329" s="4">
         <v>28</v>
       </c>
       <c r="G329" t="s">
@@ -9383,7 +9382,7 @@
       <c r="E330" t="s">
         <v>10</v>
       </c>
-      <c r="F330">
+      <c r="F330" s="4">
         <v>29</v>
       </c>
       <c r="G330" t="s">
@@ -9409,7 +9408,7 @@
       <c r="E331" t="s">
         <v>19</v>
       </c>
-      <c r="F331">
+      <c r="F331" s="4">
         <v>23</v>
       </c>
       <c r="G331" s="2" t="s">
@@ -9435,7 +9434,7 @@
       <c r="E332" t="s">
         <v>10</v>
       </c>
-      <c r="F332">
+      <c r="F332" s="4">
         <v>41</v>
       </c>
       <c r="G332" t="s">
@@ -9461,7 +9460,7 @@
       <c r="E333" t="s">
         <v>14</v>
       </c>
-      <c r="F333">
+      <c r="F333" s="4">
         <v>28</v>
       </c>
       <c r="G333" t="s">
@@ -9487,7 +9486,7 @@
       <c r="E334" t="s">
         <v>14</v>
       </c>
-      <c r="F334">
+      <c r="F334" s="4">
         <v>37</v>
       </c>
       <c r="G334" s="2" t="s">
@@ -9513,7 +9512,7 @@
       <c r="E335" t="s">
         <v>14</v>
       </c>
-      <c r="F335">
+      <c r="F335" s="4">
         <v>34</v>
       </c>
       <c r="G335" t="s">
@@ -9539,7 +9538,7 @@
       <c r="E336" t="s">
         <v>14</v>
       </c>
-      <c r="F336">
+      <c r="F336" s="4">
         <v>26</v>
       </c>
       <c r="G336" t="s">
@@ -9565,7 +9564,7 @@
       <c r="E337" t="s">
         <v>19</v>
       </c>
-      <c r="F337">
+      <c r="F337" s="4">
         <v>35</v>
       </c>
       <c r="G337" t="s">
@@ -9591,7 +9590,7 @@
       <c r="E338" t="s">
         <v>10</v>
       </c>
-      <c r="F338">
+      <c r="F338" s="4">
         <v>36</v>
       </c>
       <c r="G338" t="s">
@@ -9617,7 +9616,7 @@
       <c r="E339" t="s">
         <v>10</v>
       </c>
-      <c r="F339">
+      <c r="F339" s="4">
         <v>29</v>
       </c>
       <c r="G339" s="2" t="s">
@@ -9643,7 +9642,7 @@
       <c r="E340" t="s">
         <v>19</v>
       </c>
-      <c r="F340">
+      <c r="F340" s="4">
         <v>27</v>
       </c>
       <c r="G340" t="s">
@@ -9669,7 +9668,7 @@
       <c r="E341" t="s">
         <v>10</v>
       </c>
-      <c r="F341">
+      <c r="F341" s="4">
         <v>25</v>
       </c>
       <c r="G341" t="s">
@@ -9695,7 +9694,7 @@
       <c r="E342" t="s">
         <v>10</v>
       </c>
-      <c r="F342">
+      <c r="F342" s="4">
         <v>36</v>
       </c>
       <c r="G342" t="s">
@@ -9721,7 +9720,7 @@
       <c r="E343" t="s">
         <v>10</v>
       </c>
-      <c r="F343">
+      <c r="F343" s="4">
         <v>37</v>
       </c>
       <c r="G343" s="2" t="s">
@@ -9747,7 +9746,7 @@
       <c r="E344" t="s">
         <v>10</v>
       </c>
-      <c r="F344">
+      <c r="F344" s="4">
         <v>26</v>
       </c>
       <c r="G344" t="s">
@@ -9773,7 +9772,7 @@
       <c r="E345" t="s">
         <v>10</v>
       </c>
-      <c r="F345">
+      <c r="F345" s="4">
         <v>37</v>
       </c>
       <c r="G345" t="s">
@@ -9799,7 +9798,7 @@
       <c r="E346" t="s">
         <v>19</v>
       </c>
-      <c r="F346">
+      <c r="F346" s="4">
         <v>24</v>
       </c>
       <c r="G346" s="2" t="s">
@@ -9825,7 +9824,7 @@
       <c r="E347" t="s">
         <v>10</v>
       </c>
-      <c r="F347">
+      <c r="F347" s="4">
         <v>39</v>
       </c>
       <c r="G347" t="s">
@@ -9851,7 +9850,7 @@
       <c r="E348" t="s">
         <v>10</v>
       </c>
-      <c r="F348">
+      <c r="F348" s="4">
         <v>26</v>
       </c>
       <c r="G348" t="s">
@@ -9877,7 +9876,7 @@
       <c r="E349" t="s">
         <v>10</v>
       </c>
-      <c r="F349">
+      <c r="F349" s="4">
         <v>34</v>
       </c>
       <c r="G349" s="2" t="s">
@@ -9903,7 +9902,7 @@
       <c r="E350" t="s">
         <v>10</v>
       </c>
-      <c r="F350">
+      <c r="F350" s="4">
         <v>28</v>
       </c>
       <c r="G350" t="s">
@@ -9929,7 +9928,7 @@
       <c r="E351" t="s">
         <v>10</v>
       </c>
-      <c r="F351">
+      <c r="F351" s="4">
         <v>32</v>
       </c>
       <c r="G351" t="s">
@@ -9955,7 +9954,7 @@
       <c r="E352" t="s">
         <v>10</v>
       </c>
-      <c r="F352">
+      <c r="F352" s="4">
         <v>39</v>
       </c>
       <c r="G352" s="2" t="s">
@@ -9981,7 +9980,7 @@
       <c r="E353" t="s">
         <v>10</v>
       </c>
-      <c r="F353">
+      <c r="F353" s="4">
         <v>29</v>
       </c>
       <c r="G353" t="s">
@@ -10007,7 +10006,7 @@
       <c r="E354" t="s">
         <v>10</v>
       </c>
-      <c r="F354">
+      <c r="F354" s="4">
         <v>32</v>
       </c>
       <c r="G354" s="2" t="s">
@@ -10033,7 +10032,7 @@
       <c r="E355" t="s">
         <v>14</v>
       </c>
-      <c r="F355">
+      <c r="F355" s="4">
         <v>25</v>
       </c>
       <c r="G355" t="s">
@@ -10059,7 +10058,7 @@
       <c r="E356" t="s">
         <v>19</v>
       </c>
-      <c r="F356">
+      <c r="F356" s="4">
         <v>36</v>
       </c>
       <c r="G356" t="s">
@@ -10085,7 +10084,7 @@
       <c r="E357" t="s">
         <v>10</v>
       </c>
-      <c r="F357">
+      <c r="F357" s="4">
         <v>25</v>
       </c>
       <c r="G357" s="2" t="s">
@@ -10111,7 +10110,7 @@
       <c r="E358" t="s">
         <v>10</v>
       </c>
-      <c r="F358">
+      <c r="F358" s="4">
         <v>58</v>
       </c>
       <c r="G358" t="s">
@@ -10137,7 +10136,7 @@
       <c r="E359" t="s">
         <v>10</v>
       </c>
-      <c r="F359">
+      <c r="F359" s="4">
         <v>24</v>
       </c>
       <c r="G359" t="s">
@@ -10163,7 +10162,7 @@
       <c r="E360" t="s">
         <v>14</v>
       </c>
-      <c r="F360">
+      <c r="F360" s="4">
         <v>56</v>
       </c>
       <c r="G360" s="2" t="s">
@@ -10189,7 +10188,7 @@
       <c r="E361" t="s">
         <v>10</v>
       </c>
-      <c r="F361">
+      <c r="F361" s="4">
         <v>27</v>
       </c>
       <c r="G361" t="s">
@@ -10215,7 +10214,7 @@
       <c r="E362" t="s">
         <v>10</v>
       </c>
-      <c r="F362">
+      <c r="F362" s="4">
         <v>40</v>
       </c>
       <c r="G362" t="s">
@@ -10241,7 +10240,7 @@
       <c r="E363" t="s">
         <v>14</v>
       </c>
-      <c r="F363">
+      <c r="F363" s="4">
         <v>28</v>
       </c>
       <c r="G363" t="s">
@@ -10267,7 +10266,7 @@
       <c r="E364" t="s">
         <v>14</v>
       </c>
-      <c r="F364">
+      <c r="F364" s="4">
         <v>39</v>
       </c>
       <c r="G364" t="s">
@@ -10293,7 +10292,7 @@
       <c r="E365" t="s">
         <v>19</v>
       </c>
-      <c r="F365">
+      <c r="F365" s="4">
         <v>38</v>
       </c>
       <c r="G365" s="2" t="s">
@@ -10319,7 +10318,7 @@
       <c r="E366" t="s">
         <v>14</v>
       </c>
-      <c r="F366">
+      <c r="F366" s="4">
         <v>32</v>
       </c>
       <c r="G366" t="s">
@@ -10345,7 +10344,7 @@
       <c r="E367" t="s">
         <v>14</v>
       </c>
-      <c r="F367">
+      <c r="F367" s="4">
         <v>26</v>
       </c>
       <c r="G367" t="s">
@@ -10371,7 +10370,7 @@
       <c r="E368" t="s">
         <v>14</v>
       </c>
-      <c r="F368">
+      <c r="F368" s="4">
         <v>31</v>
       </c>
       <c r="G368" t="s">
@@ -10397,7 +10396,7 @@
       <c r="E369" t="s">
         <v>19</v>
       </c>
-      <c r="F369">
+      <c r="F369" s="4">
         <v>24</v>
       </c>
       <c r="G369" t="s">
@@ -10423,7 +10422,7 @@
       <c r="E370" t="s">
         <v>19</v>
       </c>
-      <c r="F370">
+      <c r="F370" s="4">
         <v>39</v>
       </c>
       <c r="G370" s="2" t="s">
@@ -10449,7 +10448,7 @@
       <c r="E371" t="s">
         <v>14</v>
       </c>
-      <c r="F371">
+      <c r="F371" s="4">
         <v>28</v>
       </c>
       <c r="G371" t="s">
@@ -10475,7 +10474,7 @@
       <c r="E372" t="s">
         <v>19</v>
       </c>
-      <c r="F372">
+      <c r="F372" s="4">
         <v>26</v>
       </c>
       <c r="G372" t="s">
@@ -10501,7 +10500,7 @@
       <c r="E373" t="s">
         <v>19</v>
       </c>
-      <c r="F373">
+      <c r="F373" s="4">
         <v>46</v>
       </c>
       <c r="G373" t="s">
@@ -10527,7 +10526,7 @@
       <c r="E374" t="s">
         <v>10</v>
       </c>
-      <c r="F374">
+      <c r="F374" s="4">
         <v>37</v>
       </c>
       <c r="G374" s="2" t="s">
@@ -10553,7 +10552,7 @@
       <c r="E375" t="s">
         <v>10</v>
       </c>
-      <c r="F375">
+      <c r="F375" s="4">
         <v>52</v>
       </c>
       <c r="G375" t="s">
@@ -10579,7 +10578,7 @@
       <c r="E376" t="s">
         <v>14</v>
       </c>
-      <c r="F376">
+      <c r="F376" s="4">
         <v>46</v>
       </c>
       <c r="G376" t="s">
@@ -10605,7 +10604,7 @@
       <c r="E377" t="s">
         <v>19</v>
       </c>
-      <c r="F377">
+      <c r="F377" s="4">
         <v>42</v>
       </c>
       <c r="G377" t="s">
@@ -10631,7 +10630,7 @@
       <c r="E378" t="s">
         <v>19</v>
       </c>
-      <c r="F378">
+      <c r="F378" s="4">
         <v>21</v>
       </c>
       <c r="G378" s="2" t="s">
@@ -10657,7 +10656,7 @@
       <c r="E379" t="s">
         <v>14</v>
       </c>
-      <c r="F379">
+      <c r="F379" s="4">
         <v>28</v>
       </c>
       <c r="G379" t="s">
@@ -10683,7 +10682,7 @@
       <c r="E380" t="s">
         <v>10</v>
       </c>
-      <c r="F380">
+      <c r="F380" s="4">
         <v>29</v>
       </c>
       <c r="G380" t="s">
@@ -10709,7 +10708,7 @@
       <c r="E381" t="s">
         <v>19</v>
       </c>
-      <c r="F381">
+      <c r="F381" s="4">
         <v>23</v>
       </c>
       <c r="G381" s="2" t="s">
@@ -10735,7 +10734,7 @@
       <c r="E382" t="s">
         <v>10</v>
       </c>
-      <c r="F382">
+      <c r="F382" s="4">
         <v>41</v>
       </c>
       <c r="G382" t="s">
@@ -10761,7 +10760,7 @@
       <c r="E383" t="s">
         <v>14</v>
       </c>
-      <c r="F383">
+      <c r="F383" s="4">
         <v>28</v>
       </c>
       <c r="G383" t="s">
@@ -10787,7 +10786,7 @@
       <c r="E384" t="s">
         <v>14</v>
       </c>
-      <c r="F384">
+      <c r="F384" s="4">
         <v>37</v>
       </c>
       <c r="G384" s="2" t="s">
@@ -10813,7 +10812,7 @@
       <c r="E385" t="s">
         <v>14</v>
       </c>
-      <c r="F385">
+      <c r="F385" s="4">
         <v>34</v>
       </c>
       <c r="G385" t="s">
@@ -10839,7 +10838,7 @@
       <c r="E386" t="s">
         <v>14</v>
       </c>
-      <c r="F386">
+      <c r="F386" s="4">
         <v>26</v>
       </c>
       <c r="G386" t="s">
@@ -10865,7 +10864,7 @@
       <c r="E387" t="s">
         <v>19</v>
       </c>
-      <c r="F387">
+      <c r="F387" s="4">
         <v>35</v>
       </c>
       <c r="G387" t="s">
@@ -10891,7 +10890,7 @@
       <c r="E388" t="s">
         <v>10</v>
       </c>
-      <c r="F388">
+      <c r="F388" s="4">
         <v>36</v>
       </c>
       <c r="G388" t="s">
@@ -10917,7 +10916,7 @@
       <c r="E389" t="s">
         <v>10</v>
       </c>
-      <c r="F389">
+      <c r="F389" s="4">
         <v>29</v>
       </c>
       <c r="G389" s="2" t="s">
@@ -10943,7 +10942,7 @@
       <c r="E390" t="s">
         <v>19</v>
       </c>
-      <c r="F390">
+      <c r="F390" s="4">
         <v>27</v>
       </c>
       <c r="G390" t="s">
@@ -10969,7 +10968,7 @@
       <c r="E391" t="s">
         <v>10</v>
       </c>
-      <c r="F391">
+      <c r="F391" s="4">
         <v>25</v>
       </c>
       <c r="G391" t="s">
@@ -10995,7 +10994,7 @@
       <c r="E392" t="s">
         <v>10</v>
       </c>
-      <c r="F392">
+      <c r="F392" s="4">
         <v>36</v>
       </c>
       <c r="G392" t="s">
@@ -11021,7 +11020,7 @@
       <c r="E393" t="s">
         <v>10</v>
       </c>
-      <c r="F393">
+      <c r="F393" s="4">
         <v>37</v>
       </c>
       <c r="G393" s="2" t="s">
@@ -11047,7 +11046,7 @@
       <c r="E394" t="s">
         <v>10</v>
       </c>
-      <c r="F394">
+      <c r="F394" s="4">
         <v>26</v>
       </c>
       <c r="G394" t="s">
@@ -11073,7 +11072,7 @@
       <c r="E395" t="s">
         <v>10</v>
       </c>
-      <c r="F395">
+      <c r="F395" s="4">
         <v>37</v>
       </c>
       <c r="G395" t="s">
@@ -11099,7 +11098,7 @@
       <c r="E396" t="s">
         <v>19</v>
       </c>
-      <c r="F396">
+      <c r="F396" s="4">
         <v>24</v>
       </c>
       <c r="G396" s="2" t="s">
@@ -11125,7 +11124,7 @@
       <c r="E397" t="s">
         <v>10</v>
       </c>
-      <c r="F397">
+      <c r="F397" s="4">
         <v>39</v>
       </c>
       <c r="G397" t="s">
@@ -11151,7 +11150,7 @@
       <c r="E398" t="s">
         <v>10</v>
       </c>
-      <c r="F398">
+      <c r="F398" s="4">
         <v>26</v>
       </c>
       <c r="G398" t="s">
@@ -11177,7 +11176,7 @@
       <c r="E399" t="s">
         <v>10</v>
       </c>
-      <c r="F399">
+      <c r="F399" s="4">
         <v>34</v>
       </c>
       <c r="G399" s="2" t="s">
@@ -11203,7 +11202,7 @@
       <c r="E400" t="s">
         <v>10</v>
       </c>
-      <c r="F400">
+      <c r="F400" s="4">
         <v>28</v>
       </c>
       <c r="G400" t="s">
@@ -11229,7 +11228,7 @@
       <c r="E401" t="s">
         <v>10</v>
       </c>
-      <c r="F401">
+      <c r="F401" s="4">
         <v>32</v>
       </c>
       <c r="G401" t="s">
@@ -11255,7 +11254,7 @@
       <c r="E402" t="s">
         <v>10</v>
       </c>
-      <c r="F402">
+      <c r="F402" s="4">
         <v>39</v>
       </c>
       <c r="G402" s="2" t="s">
@@ -11281,7 +11280,7 @@
       <c r="E403" t="s">
         <v>10</v>
       </c>
-      <c r="F403">
+      <c r="F403" s="4">
         <v>29</v>
       </c>
       <c r="G403" t="s">
@@ -11307,7 +11306,7 @@
       <c r="E404" t="s">
         <v>10</v>
       </c>
-      <c r="F404">
+      <c r="F404" s="4">
         <v>32</v>
       </c>
       <c r="G404" s="2" t="s">
@@ -11333,7 +11332,7 @@
       <c r="E405" t="s">
         <v>14</v>
       </c>
-      <c r="F405">
+      <c r="F405" s="4">
         <v>25</v>
       </c>
       <c r="G405" t="s">
@@ -11359,7 +11358,7 @@
       <c r="E406" t="s">
         <v>19</v>
       </c>
-      <c r="F406">
+      <c r="F406" s="4">
         <v>36</v>
       </c>
       <c r="G406" t="s">
@@ -11385,7 +11384,7 @@
       <c r="E407" t="s">
         <v>10</v>
       </c>
-      <c r="F407">
+      <c r="F407" s="4">
         <v>25</v>
       </c>
       <c r="G407" s="2" t="s">
@@ -11411,7 +11410,7 @@
       <c r="E408" t="s">
         <v>10</v>
       </c>
-      <c r="F408">
+      <c r="F408" s="4">
         <v>58</v>
       </c>
       <c r="G408" t="s">
@@ -11437,7 +11436,7 @@
       <c r="E409" t="s">
         <v>10</v>
       </c>
-      <c r="F409">
+      <c r="F409" s="4">
         <v>24</v>
       </c>
       <c r="G409" t="s">
@@ -11463,7 +11462,7 @@
       <c r="E410" t="s">
         <v>14</v>
       </c>
-      <c r="F410">
+      <c r="F410" s="4">
         <v>56</v>
       </c>
       <c r="G410" s="2" t="s">
@@ -11489,7 +11488,7 @@
       <c r="E411" t="s">
         <v>10</v>
       </c>
-      <c r="F411">
+      <c r="F411" s="4">
         <v>27</v>
       </c>
       <c r="G411" t="s">
@@ -11515,7 +11514,7 @@
       <c r="E412" t="s">
         <v>10</v>
       </c>
-      <c r="F412">
+      <c r="F412" s="4">
         <v>40</v>
       </c>
       <c r="G412" t="s">
@@ -11541,7 +11540,7 @@
       <c r="E413" t="s">
         <v>14</v>
       </c>
-      <c r="F413">
+      <c r="F413" s="4">
         <v>28</v>
       </c>
       <c r="G413" t="s">
@@ -11567,7 +11566,7 @@
       <c r="E414" t="s">
         <v>14</v>
       </c>
-      <c r="F414">
+      <c r="F414" s="4">
         <v>39</v>
       </c>
       <c r="G414" t="s">
@@ -11593,7 +11592,7 @@
       <c r="E415" t="s">
         <v>19</v>
       </c>
-      <c r="F415">
+      <c r="F415" s="4">
         <v>38</v>
       </c>
       <c r="G415" s="2" t="s">
@@ -11619,7 +11618,7 @@
       <c r="E416" t="s">
         <v>14</v>
       </c>
-      <c r="F416">
+      <c r="F416" s="4">
         <v>32</v>
       </c>
       <c r="G416" t="s">
@@ -11645,7 +11644,7 @@
       <c r="E417" t="s">
         <v>14</v>
       </c>
-      <c r="F417">
+      <c r="F417" s="4">
         <v>26</v>
       </c>
       <c r="G417" t="s">
@@ -11671,7 +11670,7 @@
       <c r="E418" t="s">
         <v>14</v>
       </c>
-      <c r="F418">
+      <c r="F418" s="4">
         <v>31</v>
       </c>
       <c r="G418" t="s">
@@ -11697,7 +11696,7 @@
       <c r="E419" t="s">
         <v>19</v>
       </c>
-      <c r="F419">
+      <c r="F419" s="4">
         <v>24</v>
       </c>
       <c r="G419" t="s">
@@ -11723,7 +11722,7 @@
       <c r="E420" t="s">
         <v>19</v>
       </c>
-      <c r="F420">
+      <c r="F420" s="4">
         <v>39</v>
       </c>
       <c r="G420" s="2" t="s">
@@ -11749,7 +11748,7 @@
       <c r="E421" t="s">
         <v>14</v>
       </c>
-      <c r="F421">
+      <c r="F421" s="4">
         <v>28</v>
       </c>
       <c r="G421" t="s">
@@ -11775,7 +11774,7 @@
       <c r="E422" t="s">
         <v>19</v>
       </c>
-      <c r="F422">
+      <c r="F422" s="4">
         <v>26</v>
       </c>
       <c r="G422" t="s">
@@ -11801,7 +11800,7 @@
       <c r="E423" t="s">
         <v>19</v>
       </c>
-      <c r="F423">
+      <c r="F423" s="4">
         <v>46</v>
       </c>
       <c r="G423" t="s">
@@ -11827,7 +11826,7 @@
       <c r="E424" t="s">
         <v>10</v>
       </c>
-      <c r="F424">
+      <c r="F424" s="4">
         <v>37</v>
       </c>
       <c r="G424" s="2" t="s">
@@ -11853,7 +11852,7 @@
       <c r="E425" t="s">
         <v>10</v>
       </c>
-      <c r="F425">
+      <c r="F425" s="4">
         <v>52</v>
       </c>
       <c r="G425" t="s">
@@ -11879,7 +11878,7 @@
       <c r="E426" t="s">
         <v>14</v>
       </c>
-      <c r="F426">
+      <c r="F426" s="4">
         <v>46</v>
       </c>
       <c r="G426" t="s">
@@ -11905,7 +11904,7 @@
       <c r="E427" t="s">
         <v>19</v>
       </c>
-      <c r="F427">
+      <c r="F427" s="4">
         <v>42</v>
       </c>
       <c r="G427" t="s">
@@ -11931,7 +11930,7 @@
       <c r="E428" t="s">
         <v>19</v>
       </c>
-      <c r="F428">
+      <c r="F428" s="4">
         <v>21</v>
       </c>
       <c r="G428" s="2" t="s">
@@ -11957,7 +11956,7 @@
       <c r="E429" t="s">
         <v>14</v>
       </c>
-      <c r="F429">
+      <c r="F429" s="4">
         <v>28</v>
       </c>
       <c r="G429" t="s">
@@ -11983,7 +11982,7 @@
       <c r="E430" t="s">
         <v>10</v>
       </c>
-      <c r="F430">
+      <c r="F430" s="4">
         <v>29</v>
       </c>
       <c r="G430" t="s">
@@ -12009,7 +12008,7 @@
       <c r="E431" t="s">
         <v>19</v>
       </c>
-      <c r="F431">
+      <c r="F431" s="4">
         <v>23</v>
       </c>
       <c r="G431" s="2" t="s">
@@ -12035,7 +12034,7 @@
       <c r="E432" t="s">
         <v>10</v>
       </c>
-      <c r="F432">
+      <c r="F432" s="4">
         <v>41</v>
       </c>
       <c r="G432" t="s">
@@ -12061,7 +12060,7 @@
       <c r="E433" t="s">
         <v>14</v>
       </c>
-      <c r="F433">
+      <c r="F433" s="4">
         <v>28</v>
       </c>
       <c r="G433" t="s">
@@ -12087,7 +12086,7 @@
       <c r="E434" t="s">
         <v>14</v>
       </c>
-      <c r="F434">
+      <c r="F434" s="4">
         <v>37</v>
       </c>
       <c r="G434" s="2" t="s">
@@ -12113,7 +12112,7 @@
       <c r="E435" t="s">
         <v>14</v>
       </c>
-      <c r="F435">
+      <c r="F435" s="4">
         <v>34</v>
       </c>
       <c r="G435" t="s">
@@ -12139,7 +12138,7 @@
       <c r="E436" t="s">
         <v>14</v>
       </c>
-      <c r="F436">
+      <c r="F436" s="4">
         <v>26</v>
       </c>
       <c r="G436" t="s">
@@ -12165,7 +12164,7 @@
       <c r="E437" t="s">
         <v>19</v>
       </c>
-      <c r="F437">
+      <c r="F437" s="4">
         <v>35</v>
       </c>
       <c r="G437" t="s">
@@ -12191,7 +12190,7 @@
       <c r="E438" t="s">
         <v>10</v>
       </c>
-      <c r="F438">
+      <c r="F438" s="4">
         <v>36</v>
       </c>
       <c r="G438" t="s">
@@ -12217,7 +12216,7 @@
       <c r="E439" t="s">
         <v>10</v>
       </c>
-      <c r="F439">
+      <c r="F439" s="4">
         <v>29</v>
       </c>
       <c r="G439" s="2" t="s">
@@ -12243,7 +12242,7 @@
       <c r="E440" t="s">
         <v>19</v>
       </c>
-      <c r="F440">
+      <c r="F440" s="4">
         <v>27</v>
       </c>
       <c r="G440" t="s">
@@ -12269,7 +12268,7 @@
       <c r="E441" t="s">
         <v>10</v>
       </c>
-      <c r="F441">
+      <c r="F441" s="4">
         <v>25</v>
       </c>
       <c r="G441" t="s">
@@ -12295,7 +12294,7 @@
       <c r="E442" t="s">
         <v>10</v>
       </c>
-      <c r="F442">
+      <c r="F442" s="4">
         <v>36</v>
       </c>
       <c r="G442" t="s">
@@ -12321,7 +12320,7 @@
       <c r="E443" t="s">
         <v>10</v>
       </c>
-      <c r="F443">
+      <c r="F443" s="4">
         <v>37</v>
       </c>
       <c r="G443" s="2" t="s">
@@ -12347,7 +12346,7 @@
       <c r="E444" t="s">
         <v>10</v>
       </c>
-      <c r="F444">
+      <c r="F444" s="4">
         <v>26</v>
       </c>
       <c r="G444" t="s">
@@ -12373,7 +12372,7 @@
       <c r="E445" t="s">
         <v>10</v>
       </c>
-      <c r="F445">
+      <c r="F445" s="4">
         <v>37</v>
       </c>
       <c r="G445" t="s">
@@ -12399,7 +12398,7 @@
       <c r="E446" t="s">
         <v>19</v>
       </c>
-      <c r="F446">
+      <c r="F446" s="4">
         <v>24</v>
       </c>
       <c r="G446" s="2" t="s">
@@ -12425,7 +12424,7 @@
       <c r="E447" t="s">
         <v>10</v>
       </c>
-      <c r="F447">
+      <c r="F447" s="4">
         <v>39</v>
       </c>
       <c r="G447" t="s">
@@ -12451,7 +12450,7 @@
       <c r="E448" t="s">
         <v>10</v>
       </c>
-      <c r="F448">
+      <c r="F448" s="4">
         <v>26</v>
       </c>
       <c r="G448" t="s">
@@ -12477,7 +12476,7 @@
       <c r="E449" t="s">
         <v>10</v>
       </c>
-      <c r="F449">
+      <c r="F449" s="4">
         <v>34</v>
       </c>
       <c r="G449" s="2" t="s">
@@ -12503,7 +12502,7 @@
       <c r="E450" t="s">
         <v>10</v>
       </c>
-      <c r="F450">
+      <c r="F450" s="4">
         <v>28</v>
       </c>
       <c r="G450" t="s">
@@ -12529,7 +12528,7 @@
       <c r="E451" t="s">
         <v>10</v>
       </c>
-      <c r="F451">
+      <c r="F451" s="4">
         <v>32</v>
       </c>
       <c r="G451" t="s">
@@ -12555,7 +12554,7 @@
       <c r="E452" t="s">
         <v>10</v>
       </c>
-      <c r="F452">
+      <c r="F452" s="4">
         <v>39</v>
       </c>
       <c r="G452" s="2" t="s">
@@ -12581,7 +12580,7 @@
       <c r="E453" t="s">
         <v>10</v>
       </c>
-      <c r="F453">
+      <c r="F453" s="4">
         <v>29</v>
       </c>
       <c r="G453" t="s">
@@ -12607,7 +12606,7 @@
       <c r="E454" t="s">
         <v>10</v>
       </c>
-      <c r="F454">
+      <c r="F454" s="4">
         <v>32</v>
       </c>
       <c r="G454" s="2" t="s">
@@ -12633,7 +12632,7 @@
       <c r="E455" t="s">
         <v>14</v>
       </c>
-      <c r="F455">
+      <c r="F455" s="4">
         <v>25</v>
       </c>
       <c r="G455" t="s">
@@ -12659,7 +12658,7 @@
       <c r="E456" t="s">
         <v>19</v>
       </c>
-      <c r="F456">
+      <c r="F456" s="4">
         <v>36</v>
       </c>
       <c r="G456" t="s">
@@ -12685,7 +12684,7 @@
       <c r="E457" t="s">
         <v>10</v>
       </c>
-      <c r="F457">
+      <c r="F457" s="4">
         <v>25</v>
       </c>
       <c r="G457" s="2" t="s">
@@ -12711,7 +12710,7 @@
       <c r="E458" t="s">
         <v>10</v>
       </c>
-      <c r="F458">
+      <c r="F458" s="4">
         <v>58</v>
       </c>
       <c r="G458" t="s">
@@ -12737,7 +12736,7 @@
       <c r="E459" t="s">
         <v>10</v>
       </c>
-      <c r="F459">
+      <c r="F459" s="4">
         <v>24</v>
       </c>
       <c r="G459" t="s">
@@ -12763,7 +12762,7 @@
       <c r="E460" t="s">
         <v>14</v>
       </c>
-      <c r="F460">
+      <c r="F460" s="4">
         <v>56</v>
       </c>
       <c r="G460" s="2" t="s">
@@ -12789,7 +12788,7 @@
       <c r="E461" t="s">
         <v>10</v>
       </c>
-      <c r="F461">
+      <c r="F461" s="4">
         <v>27</v>
       </c>
       <c r="G461" t="s">
@@ -12815,7 +12814,7 @@
       <c r="E462" t="s">
         <v>10</v>
       </c>
-      <c r="F462">
+      <c r="F462" s="4">
         <v>40</v>
       </c>
       <c r="G462" t="s">
@@ -12841,7 +12840,7 @@
       <c r="E463" t="s">
         <v>14</v>
       </c>
-      <c r="F463">
+      <c r="F463" s="4">
         <v>28</v>
       </c>
       <c r="G463" t="s">
@@ -12867,7 +12866,7 @@
       <c r="E464" t="s">
         <v>14</v>
       </c>
-      <c r="F464">
+      <c r="F464" s="4">
         <v>39</v>
       </c>
       <c r="G464" t="s">
@@ -12893,7 +12892,7 @@
       <c r="E465" t="s">
         <v>19</v>
       </c>
-      <c r="F465">
+      <c r="F465" s="4">
         <v>38</v>
       </c>
       <c r="G465" s="2" t="s">
@@ -12919,7 +12918,7 @@
       <c r="E466" t="s">
         <v>14</v>
       </c>
-      <c r="F466">
+      <c r="F466" s="4">
         <v>32</v>
       </c>
       <c r="G466" t="s">
@@ -12945,7 +12944,7 @@
       <c r="E467" t="s">
         <v>14</v>
       </c>
-      <c r="F467">
+      <c r="F467" s="4">
         <v>26</v>
       </c>
       <c r="G467" t="s">
@@ -12971,7 +12970,7 @@
       <c r="E468" t="s">
         <v>14</v>
       </c>
-      <c r="F468">
+      <c r="F468" s="4">
         <v>31</v>
       </c>
       <c r="G468" t="s">
@@ -12997,7 +12996,7 @@
       <c r="E469" t="s">
         <v>19</v>
       </c>
-      <c r="F469">
+      <c r="F469" s="4">
         <v>24</v>
       </c>
       <c r="G469" t="s">
@@ -13023,7 +13022,7 @@
       <c r="E470" t="s">
         <v>19</v>
       </c>
-      <c r="F470">
+      <c r="F470" s="4">
         <v>39</v>
       </c>
       <c r="G470" s="2" t="s">
@@ -13049,7 +13048,7 @@
       <c r="E471" t="s">
         <v>14</v>
       </c>
-      <c r="F471">
+      <c r="F471" s="4">
         <v>28</v>
       </c>
       <c r="G471" t="s">
@@ -13075,7 +13074,7 @@
       <c r="E472" t="s">
         <v>19</v>
       </c>
-      <c r="F472">
+      <c r="F472" s="4">
         <v>26</v>
       </c>
       <c r="G472" t="s">
@@ -13101,7 +13100,7 @@
       <c r="E473" t="s">
         <v>19</v>
       </c>
-      <c r="F473">
+      <c r="F473" s="4">
         <v>46</v>
       </c>
       <c r="G473" t="s">
@@ -13127,7 +13126,7 @@
       <c r="E474" t="s">
         <v>10</v>
       </c>
-      <c r="F474">
+      <c r="F474" s="4">
         <v>37</v>
       </c>
       <c r="G474" s="2" t="s">
@@ -13153,7 +13152,7 @@
       <c r="E475" t="s">
         <v>10</v>
       </c>
-      <c r="F475">
+      <c r="F475" s="4">
         <v>52</v>
       </c>
       <c r="G475" t="s">
@@ -13179,7 +13178,7 @@
       <c r="E476" t="s">
         <v>14</v>
       </c>
-      <c r="F476">
+      <c r="F476" s="4">
         <v>46</v>
       </c>
       <c r="G476" t="s">
@@ -13205,7 +13204,7 @@
       <c r="E477" t="s">
         <v>19</v>
       </c>
-      <c r="F477">
+      <c r="F477" s="4">
         <v>42</v>
       </c>
       <c r="G477" t="s">
@@ -13231,7 +13230,7 @@
       <c r="E478" t="s">
         <v>19</v>
       </c>
-      <c r="F478">
+      <c r="F478" s="4">
         <v>21</v>
       </c>
       <c r="G478" s="2" t="s">
@@ -13257,7 +13256,7 @@
       <c r="E479" t="s">
         <v>14</v>
       </c>
-      <c r="F479">
+      <c r="F479" s="4">
         <v>28</v>
       </c>
       <c r="G479" t="s">
@@ -13283,7 +13282,7 @@
       <c r="E480" t="s">
         <v>10</v>
       </c>
-      <c r="F480">
+      <c r="F480" s="4">
         <v>29</v>
       </c>
       <c r="G480" t="s">
@@ -13309,7 +13308,7 @@
       <c r="E481" t="s">
         <v>19</v>
       </c>
-      <c r="F481">
+      <c r="F481" s="4">
         <v>23</v>
       </c>
       <c r="G481" s="2" t="s">
@@ -13335,7 +13334,7 @@
       <c r="E482" t="s">
         <v>10</v>
       </c>
-      <c r="F482">
+      <c r="F482" s="4">
         <v>41</v>
       </c>
       <c r="G482" t="s">
@@ -13361,7 +13360,7 @@
       <c r="E483" t="s">
         <v>14</v>
       </c>
-      <c r="F483">
+      <c r="F483" s="4">
         <v>28</v>
       </c>
       <c r="G483" t="s">
@@ -13387,7 +13386,7 @@
       <c r="E484" t="s">
         <v>14</v>
       </c>
-      <c r="F484">
+      <c r="F484" s="4">
         <v>37</v>
       </c>
       <c r="G484" s="2" t="s">
@@ -13413,7 +13412,7 @@
       <c r="E485" t="s">
         <v>14</v>
       </c>
-      <c r="F485">
+      <c r="F485" s="4">
         <v>34</v>
       </c>
       <c r="G485" t="s">
@@ -13439,7 +13438,7 @@
       <c r="E486" t="s">
         <v>14</v>
       </c>
-      <c r="F486">
+      <c r="F486" s="4">
         <v>26</v>
       </c>
       <c r="G486" t="s">
@@ -13465,7 +13464,7 @@
       <c r="E487" t="s">
         <v>19</v>
       </c>
-      <c r="F487">
+      <c r="F487" s="4">
         <v>35</v>
       </c>
       <c r="G487" t="s">
@@ -13491,7 +13490,7 @@
       <c r="E488" t="s">
         <v>10</v>
       </c>
-      <c r="F488">
+      <c r="F488" s="4">
         <v>36</v>
       </c>
       <c r="G488" t="s">
@@ -13517,7 +13516,7 @@
       <c r="E489" t="s">
         <v>10</v>
       </c>
-      <c r="F489">
+      <c r="F489" s="4">
         <v>29</v>
       </c>
       <c r="G489" s="2" t="s">
@@ -13543,7 +13542,7 @@
       <c r="E490" t="s">
         <v>19</v>
       </c>
-      <c r="F490">
+      <c r="F490" s="4">
         <v>27</v>
       </c>
       <c r="G490" t="s">
@@ -13569,7 +13568,7 @@
       <c r="E491" t="s">
         <v>10</v>
       </c>
-      <c r="F491">
+      <c r="F491" s="4">
         <v>25</v>
       </c>
       <c r="G491" t="s">
@@ -13595,7 +13594,7 @@
       <c r="E492" t="s">
         <v>10</v>
       </c>
-      <c r="F492">
+      <c r="F492" s="4">
         <v>36</v>
       </c>
       <c r="G492" t="s">
@@ -13621,7 +13620,7 @@
       <c r="E493" t="s">
         <v>10</v>
       </c>
-      <c r="F493">
+      <c r="F493" s="4">
         <v>37</v>
       </c>
       <c r="G493" s="2" t="s">
@@ -13647,7 +13646,7 @@
       <c r="E494" t="s">
         <v>10</v>
       </c>
-      <c r="F494">
+      <c r="F494" s="4">
         <v>26</v>
       </c>
       <c r="G494" t="s">
@@ -13673,7 +13672,7 @@
       <c r="E495" t="s">
         <v>10</v>
       </c>
-      <c r="F495">
+      <c r="F495" s="4">
         <v>37</v>
       </c>
       <c r="G495" t="s">
@@ -13699,7 +13698,7 @@
       <c r="E496" t="s">
         <v>19</v>
       </c>
-      <c r="F496">
+      <c r="F496" s="4">
         <v>24</v>
       </c>
       <c r="G496" s="2" t="s">
@@ -13725,7 +13724,7 @@
       <c r="E497" t="s">
         <v>10</v>
       </c>
-      <c r="F497">
+      <c r="F497" s="4">
         <v>39</v>
       </c>
       <c r="G497" t="s">
@@ -13751,7 +13750,7 @@
       <c r="E498" t="s">
         <v>10</v>
       </c>
-      <c r="F498">
+      <c r="F498" s="4">
         <v>26</v>
       </c>
       <c r="G498" t="s">
@@ -13777,7 +13776,7 @@
       <c r="E499" t="s">
         <v>10</v>
       </c>
-      <c r="F499">
+      <c r="F499" s="4">
         <v>34</v>
       </c>
       <c r="G499" s="2" t="s">
@@ -13803,7 +13802,7 @@
       <c r="E500" t="s">
         <v>10</v>
       </c>
-      <c r="F500">
+      <c r="F500" s="4">
         <v>28</v>
       </c>
       <c r="G500" t="s">
@@ -13829,7 +13828,7 @@
       <c r="E501" t="s">
         <v>10</v>
       </c>
-      <c r="F501">
+      <c r="F501" s="4">
         <v>32</v>
       </c>
       <c r="G501" t="s">
@@ -13855,7 +13854,7 @@
       <c r="E502" t="s">
         <v>10</v>
       </c>
-      <c r="F502">
+      <c r="F502" s="4">
         <v>39</v>
       </c>
       <c r="G502" s="2" t="s">
@@ -13881,7 +13880,7 @@
       <c r="E503" t="s">
         <v>10</v>
       </c>
-      <c r="F503">
+      <c r="F503" s="4">
         <v>29</v>
       </c>
       <c r="G503" t="s">
@@ -13907,7 +13906,7 @@
       <c r="E504" t="s">
         <v>10</v>
       </c>
-      <c r="F504">
+      <c r="F504" s="4">
         <v>32</v>
       </c>
       <c r="G504" s="2" t="s">
@@ -13933,7 +13932,7 @@
       <c r="E505" t="s">
         <v>14</v>
       </c>
-      <c r="F505">
+      <c r="F505" s="4">
         <v>25</v>
       </c>
       <c r="G505" t="s">
@@ -13959,7 +13958,7 @@
       <c r="E506" t="s">
         <v>19</v>
       </c>
-      <c r="F506">
+      <c r="F506" s="4">
         <v>36</v>
       </c>
       <c r="G506" t="s">
@@ -13985,7 +13984,7 @@
       <c r="E507" t="s">
         <v>10</v>
       </c>
-      <c r="F507">
+      <c r="F507" s="4">
         <v>25</v>
       </c>
       <c r="G507" s="2" t="s">
@@ -14011,7 +14010,7 @@
       <c r="E508" t="s">
         <v>10</v>
       </c>
-      <c r="F508">
+      <c r="F508" s="4">
         <v>58</v>
       </c>
       <c r="G508" t="s">
@@ -14037,7 +14036,7 @@
       <c r="E509" t="s">
         <v>10</v>
       </c>
-      <c r="F509">
+      <c r="F509" s="4">
         <v>24</v>
       </c>
       <c r="G509" t="s">
@@ -14063,7 +14062,7 @@
       <c r="E510" t="s">
         <v>14</v>
       </c>
-      <c r="F510">
+      <c r="F510" s="4">
         <v>56</v>
       </c>
       <c r="G510" s="2" t="s">
@@ -14089,7 +14088,7 @@
       <c r="E511" t="s">
         <v>10</v>
       </c>
-      <c r="F511">
+      <c r="F511" s="4">
         <v>27</v>
       </c>
       <c r="G511" t="s">
@@ -14115,7 +14114,7 @@
       <c r="E512" t="s">
         <v>10</v>
       </c>
-      <c r="F512">
+      <c r="F512" s="4">
         <v>40</v>
       </c>
       <c r="G512" t="s">
@@ -14141,7 +14140,7 @@
       <c r="E513" t="s">
         <v>14</v>
       </c>
-      <c r="F513">
+      <c r="F513" s="4">
         <v>28</v>
       </c>
       <c r="G513" t="s">
@@ -14167,7 +14166,7 @@
       <c r="E514" t="s">
         <v>14</v>
       </c>
-      <c r="F514">
+      <c r="F514" s="4">
         <v>39</v>
       </c>
       <c r="G514" t="s">
@@ -14193,7 +14192,7 @@
       <c r="E515" t="s">
         <v>19</v>
       </c>
-      <c r="F515">
+      <c r="F515" s="4">
         <v>38</v>
       </c>
       <c r="G515" s="2" t="s">
@@ -14219,7 +14218,7 @@
       <c r="E516" t="s">
         <v>14</v>
       </c>
-      <c r="F516">
+      <c r="F516" s="4">
         <v>32</v>
       </c>
       <c r="G516" t="s">
@@ -14245,7 +14244,7 @@
       <c r="E517" t="s">
         <v>14</v>
       </c>
-      <c r="F517">
+      <c r="F517" s="4">
         <v>26</v>
       </c>
       <c r="G517" t="s">
@@ -14271,7 +14270,7 @@
       <c r="E518" t="s">
         <v>14</v>
       </c>
-      <c r="F518">
+      <c r="F518" s="4">
         <v>31</v>
       </c>
       <c r="G518" t="s">
@@ -14297,7 +14296,7 @@
       <c r="E519" t="s">
         <v>19</v>
       </c>
-      <c r="F519">
+      <c r="F519" s="4">
         <v>24</v>
       </c>
       <c r="G519" t="s">
@@ -14323,7 +14322,7 @@
       <c r="E520" t="s">
         <v>19</v>
       </c>
-      <c r="F520">
+      <c r="F520" s="4">
         <v>39</v>
       </c>
       <c r="G520" s="2" t="s">
@@ -14349,7 +14348,7 @@
       <c r="E521" t="s">
         <v>14</v>
       </c>
-      <c r="F521">
+      <c r="F521" s="4">
         <v>28</v>
       </c>
       <c r="G521" t="s">
@@ -14375,7 +14374,7 @@
       <c r="E522" t="s">
         <v>19</v>
       </c>
-      <c r="F522">
+      <c r="F522" s="4">
         <v>26</v>
       </c>
       <c r="G522" t="s">
@@ -14401,7 +14400,7 @@
       <c r="E523" t="s">
         <v>19</v>
       </c>
-      <c r="F523">
+      <c r="F523" s="4">
         <v>46</v>
       </c>
       <c r="G523" t="s">
@@ -14427,7 +14426,7 @@
       <c r="E524" t="s">
         <v>10</v>
       </c>
-      <c r="F524">
+      <c r="F524" s="4">
         <v>37</v>
       </c>
       <c r="G524" s="2" t="s">
@@ -14453,7 +14452,7 @@
       <c r="E525" t="s">
         <v>10</v>
       </c>
-      <c r="F525">
+      <c r="F525" s="4">
         <v>52</v>
       </c>
       <c r="G525" t="s">
@@ -14479,7 +14478,7 @@
       <c r="E526" t="s">
         <v>14</v>
       </c>
-      <c r="F526">
+      <c r="F526" s="4">
         <v>46</v>
       </c>
       <c r="G526" t="s">
@@ -14505,7 +14504,7 @@
       <c r="E527" t="s">
         <v>19</v>
       </c>
-      <c r="F527">
+      <c r="F527" s="4">
         <v>42</v>
       </c>
       <c r="G527" t="s">
@@ -14531,7 +14530,7 @@
       <c r="E528" t="s">
         <v>19</v>
       </c>
-      <c r="F528">
+      <c r="F528" s="4">
         <v>21</v>
       </c>
       <c r="G528" s="2" t="s">
@@ -14557,7 +14556,7 @@
       <c r="E529" t="s">
         <v>14</v>
       </c>
-      <c r="F529">
+      <c r="F529" s="4">
         <v>28</v>
       </c>
       <c r="G529" t="s">
@@ -14583,7 +14582,7 @@
       <c r="E530" t="s">
         <v>10</v>
       </c>
-      <c r="F530">
+      <c r="F530" s="4">
         <v>29</v>
       </c>
       <c r="G530" t="s">
@@ -14609,7 +14608,7 @@
       <c r="E531" t="s">
         <v>19</v>
       </c>
-      <c r="F531">
+      <c r="F531" s="4">
         <v>23</v>
       </c>
       <c r="G531" s="2" t="s">
@@ -14635,7 +14634,7 @@
       <c r="E532" t="s">
         <v>10</v>
       </c>
-      <c r="F532">
+      <c r="F532" s="4">
         <v>41</v>
       </c>
       <c r="G532" t="s">
@@ -14661,7 +14660,7 @@
       <c r="E533" t="s">
         <v>14</v>
       </c>
-      <c r="F533">
+      <c r="F533" s="4">
         <v>28</v>
       </c>
       <c r="G533" t="s">
@@ -14687,7 +14686,7 @@
       <c r="E534" t="s">
         <v>14</v>
       </c>
-      <c r="F534">
+      <c r="F534" s="4">
         <v>37</v>
       </c>
       <c r="G534" s="2" t="s">
@@ -14713,7 +14712,7 @@
       <c r="E535" t="s">
         <v>14</v>
       </c>
-      <c r="F535">
+      <c r="F535" s="4">
         <v>34</v>
       </c>
       <c r="G535" t="s">
@@ -14739,7 +14738,7 @@
       <c r="E536" t="s">
         <v>14</v>
       </c>
-      <c r="F536">
+      <c r="F536" s="4">
         <v>26</v>
       </c>
       <c r="G536" t="s">
@@ -14765,7 +14764,7 @@
       <c r="E537" t="s">
         <v>19</v>
       </c>
-      <c r="F537">
+      <c r="F537" s="4">
         <v>35</v>
       </c>
       <c r="G537" t="s">
@@ -14791,7 +14790,7 @@
       <c r="E538" t="s">
         <v>10</v>
       </c>
-      <c r="F538">
+      <c r="F538" s="4">
         <v>36</v>
       </c>
       <c r="G538" t="s">
@@ -14817,7 +14816,7 @@
       <c r="E539" t="s">
         <v>10</v>
       </c>
-      <c r="F539">
+      <c r="F539" s="4">
         <v>29</v>
       </c>
       <c r="G539" s="2" t="s">
@@ -14843,7 +14842,7 @@
       <c r="E540" t="s">
         <v>19</v>
       </c>
-      <c r="F540">
+      <c r="F540" s="4">
         <v>27</v>
       </c>
       <c r="G540" t="s">
@@ -14869,7 +14868,7 @@
       <c r="E541" t="s">
         <v>10</v>
       </c>
-      <c r="F541">
+      <c r="F541" s="4">
         <v>25</v>
       </c>
       <c r="G541" t="s">
@@ -14895,7 +14894,7 @@
       <c r="E542" t="s">
         <v>10</v>
       </c>
-      <c r="F542">
+      <c r="F542" s="4">
         <v>36</v>
       </c>
       <c r="G542" t="s">
@@ -14921,7 +14920,7 @@
       <c r="E543" t="s">
         <v>10</v>
       </c>
-      <c r="F543">
+      <c r="F543" s="4">
         <v>37</v>
       </c>
       <c r="G543" s="2" t="s">
@@ -14947,7 +14946,7 @@
       <c r="E544" t="s">
         <v>10</v>
       </c>
-      <c r="F544">
+      <c r="F544" s="4">
         <v>26</v>
       </c>
       <c r="G544" t="s">
@@ -14973,7 +14972,7 @@
       <c r="E545" t="s">
         <v>10</v>
       </c>
-      <c r="F545">
+      <c r="F545" s="4">
         <v>37</v>
       </c>
       <c r="G545" t="s">
@@ -14999,7 +14998,7 @@
       <c r="E546" t="s">
         <v>19</v>
       </c>
-      <c r="F546">
+      <c r="F546" s="4">
         <v>24</v>
       </c>
       <c r="G546" s="2" t="s">
@@ -15025,7 +15024,7 @@
       <c r="E547" t="s">
         <v>10</v>
       </c>
-      <c r="F547">
+      <c r="F547" s="4">
         <v>39</v>
       </c>
       <c r="G547" t="s">
@@ -15051,7 +15050,7 @@
       <c r="E548" t="s">
         <v>10</v>
       </c>
-      <c r="F548">
+      <c r="F548" s="4">
         <v>26</v>
       </c>
       <c r="G548" t="s">
@@ -15077,7 +15076,7 @@
       <c r="E549" t="s">
         <v>10</v>
       </c>
-      <c r="F549">
+      <c r="F549" s="4">
         <v>34</v>
       </c>
       <c r="G549" s="2" t="s">
@@ -15103,7 +15102,7 @@
       <c r="E550" t="s">
         <v>10</v>
       </c>
-      <c r="F550">
+      <c r="F550" s="4">
         <v>28</v>
       </c>
       <c r="G550" t="s">
@@ -15129,7 +15128,7 @@
       <c r="E551" t="s">
         <v>10</v>
       </c>
-      <c r="F551">
+      <c r="F551" s="4">
         <v>32</v>
       </c>
       <c r="G551" t="s">
@@ -15155,7 +15154,7 @@
       <c r="E552" t="s">
         <v>10</v>
       </c>
-      <c r="F552">
+      <c r="F552" s="4">
         <v>39</v>
       </c>
       <c r="G552" s="2" t="s">
@@ -15181,7 +15180,7 @@
       <c r="E553" t="s">
         <v>10</v>
       </c>
-      <c r="F553">
+      <c r="F553" s="4">
         <v>29</v>
       </c>
       <c r="G553" t="s">
@@ -15207,7 +15206,7 @@
       <c r="E554" t="s">
         <v>10</v>
       </c>
-      <c r="F554">
+      <c r="F554" s="4">
         <v>32</v>
       </c>
       <c r="G554" s="2" t="s">
@@ -15233,7 +15232,7 @@
       <c r="E555" t="s">
         <v>14</v>
       </c>
-      <c r="F555">
+      <c r="F555" s="4">
         <v>25</v>
       </c>
       <c r="G555" t="s">
@@ -15259,7 +15258,7 @@
       <c r="E556" t="s">
         <v>19</v>
       </c>
-      <c r="F556">
+      <c r="F556" s="4">
         <v>36</v>
       </c>
       <c r="G556" t="s">
@@ -15285,7 +15284,7 @@
       <c r="E557" t="s">
         <v>10</v>
       </c>
-      <c r="F557">
+      <c r="F557" s="4">
         <v>25</v>
       </c>
       <c r="G557" s="2" t="s">
@@ -15311,7 +15310,7 @@
       <c r="E558" t="s">
         <v>10</v>
       </c>
-      <c r="F558">
+      <c r="F558" s="4">
         <v>58</v>
       </c>
       <c r="G558" t="s">
@@ -15337,7 +15336,7 @@
       <c r="E559" t="s">
         <v>10</v>
       </c>
-      <c r="F559">
+      <c r="F559" s="4">
         <v>24</v>
       </c>
       <c r="G559" t="s">
@@ -15363,7 +15362,7 @@
       <c r="E560" t="s">
         <v>14</v>
       </c>
-      <c r="F560">
+      <c r="F560" s="4">
         <v>56</v>
       </c>
       <c r="G560" s="2" t="s">
@@ -15389,7 +15388,7 @@
       <c r="E561" t="s">
         <v>10</v>
       </c>
-      <c r="F561">
+      <c r="F561" s="4">
         <v>27</v>
       </c>
       <c r="G561" t="s">
@@ -15415,7 +15414,7 @@
       <c r="E562" t="s">
         <v>10</v>
       </c>
-      <c r="F562">
+      <c r="F562" s="4">
         <v>40</v>
       </c>
       <c r="G562" t="s">
@@ -15441,7 +15440,7 @@
       <c r="E563" t="s">
         <v>14</v>
       </c>
-      <c r="F563">
+      <c r="F563" s="4">
         <v>28</v>
       </c>
       <c r="G563" t="s">
@@ -15467,7 +15466,7 @@
       <c r="E564" t="s">
         <v>14</v>
       </c>
-      <c r="F564">
+      <c r="F564" s="4">
         <v>39</v>
       </c>
       <c r="G564" t="s">
@@ -15493,7 +15492,7 @@
       <c r="E565" t="s">
         <v>19</v>
       </c>
-      <c r="F565">
+      <c r="F565" s="4">
         <v>38</v>
       </c>
       <c r="G565" s="2" t="s">
@@ -15519,7 +15518,7 @@
       <c r="E566" t="s">
         <v>14</v>
       </c>
-      <c r="F566">
+      <c r="F566" s="4">
         <v>32</v>
       </c>
       <c r="G566" t="s">
@@ -15545,7 +15544,7 @@
       <c r="E567" t="s">
         <v>14</v>
       </c>
-      <c r="F567">
+      <c r="F567" s="4">
         <v>26</v>
       </c>
       <c r="G567" t="s">
@@ -15571,7 +15570,7 @@
       <c r="E568" t="s">
         <v>14</v>
       </c>
-      <c r="F568">
+      <c r="F568" s="4">
         <v>31</v>
       </c>
       <c r="G568" t="s">
@@ -15597,7 +15596,7 @@
       <c r="E569" t="s">
         <v>19</v>
       </c>
-      <c r="F569">
+      <c r="F569" s="4">
         <v>24</v>
       </c>
       <c r="G569" t="s">
@@ -15623,7 +15622,7 @@
       <c r="E570" t="s">
         <v>19</v>
       </c>
-      <c r="F570">
+      <c r="F570" s="4">
         <v>39</v>
       </c>
       <c r="G570" s="2" t="s">
@@ -15649,7 +15648,7 @@
       <c r="E571" t="s">
         <v>14</v>
       </c>
-      <c r="F571">
+      <c r="F571" s="4">
         <v>28</v>
       </c>
       <c r="G571" t="s">
@@ -15675,7 +15674,7 @@
       <c r="E572" t="s">
         <v>19</v>
       </c>
-      <c r="F572">
+      <c r="F572" s="4">
         <v>26</v>
       </c>
       <c r="G572" t="s">
@@ -15701,7 +15700,7 @@
       <c r="E573" t="s">
         <v>19</v>
       </c>
-      <c r="F573">
+      <c r="F573" s="4">
         <v>46</v>
       </c>
       <c r="G573" t="s">
@@ -15727,7 +15726,7 @@
       <c r="E574" t="s">
         <v>10</v>
       </c>
-      <c r="F574">
+      <c r="F574" s="4">
         <v>37</v>
       </c>
       <c r="G574" s="2" t="s">
@@ -15753,7 +15752,7 @@
       <c r="E575" t="s">
         <v>10</v>
       </c>
-      <c r="F575">
+      <c r="F575" s="4">
         <v>52</v>
       </c>
       <c r="G575" t="s">
@@ -15779,7 +15778,7 @@
       <c r="E576" t="s">
         <v>14</v>
       </c>
-      <c r="F576">
+      <c r="F576" s="4">
         <v>46</v>
       </c>
       <c r="G576" t="s">
@@ -15805,7 +15804,7 @@
       <c r="E577" t="s">
         <v>19</v>
       </c>
-      <c r="F577">
+      <c r="F577" s="4">
         <v>42</v>
       </c>
       <c r="G577" t="s">
@@ -15831,7 +15830,7 @@
       <c r="E578" t="s">
         <v>19</v>
       </c>
-      <c r="F578">
+      <c r="F578" s="4">
         <v>21</v>
       </c>
       <c r="G578" s="2" t="s">
@@ -15857,7 +15856,7 @@
       <c r="E579" t="s">
         <v>14</v>
       </c>
-      <c r="F579">
+      <c r="F579" s="4">
         <v>28</v>
       </c>
       <c r="G579" t="s">
@@ -15883,7 +15882,7 @@
       <c r="E580" t="s">
         <v>10</v>
       </c>
-      <c r="F580">
+      <c r="F580" s="4">
         <v>29</v>
       </c>
       <c r="G580" t="s">
@@ -15909,7 +15908,7 @@
       <c r="E581" t="s">
         <v>19</v>
       </c>
-      <c r="F581">
+      <c r="F581" s="4">
         <v>23</v>
       </c>
       <c r="G581" s="2" t="s">
@@ -15935,7 +15934,7 @@
       <c r="E582" t="s">
         <v>10</v>
       </c>
-      <c r="F582">
+      <c r="F582" s="4">
         <v>41</v>
       </c>
       <c r="G582" t="s">
@@ -15961,7 +15960,7 @@
       <c r="E583" t="s">
         <v>14</v>
       </c>
-      <c r="F583">
+      <c r="F583" s="4">
         <v>28</v>
       </c>
       <c r="G583" t="s">
@@ -15987,7 +15986,7 @@
       <c r="E584" t="s">
         <v>14</v>
       </c>
-      <c r="F584">
+      <c r="F584" s="4">
         <v>37</v>
       </c>
       <c r="G584" s="2" t="s">
@@ -16013,7 +16012,7 @@
       <c r="E585" t="s">
         <v>14</v>
       </c>
-      <c r="F585">
+      <c r="F585" s="4">
         <v>34</v>
       </c>
       <c r="G585" t="s">
@@ -16039,7 +16038,7 @@
       <c r="E586" t="s">
         <v>14</v>
       </c>
-      <c r="F586">
+      <c r="F586" s="4">
         <v>26</v>
       </c>
       <c r="G586" t="s">
@@ -16065,7 +16064,7 @@
       <c r="E587" t="s">
         <v>19</v>
       </c>
-      <c r="F587">
+      <c r="F587" s="4">
         <v>35</v>
       </c>
       <c r="G587" t="s">
@@ -16091,7 +16090,7 @@
       <c r="E588" t="s">
         <v>10</v>
       </c>
-      <c r="F588">
+      <c r="F588" s="4">
         <v>36</v>
       </c>
       <c r="G588" t="s">
@@ -16117,7 +16116,7 @@
       <c r="E589" t="s">
         <v>10</v>
       </c>
-      <c r="F589">
+      <c r="F589" s="4">
         <v>29</v>
       </c>
       <c r="G589" s="2" t="s">
@@ -16143,7 +16142,7 @@
       <c r="E590" t="s">
         <v>19</v>
       </c>
-      <c r="F590">
+      <c r="F590" s="4">
         <v>27</v>
       </c>
       <c r="G590" t="s">
@@ -16169,7 +16168,7 @@
       <c r="E591" t="s">
         <v>10</v>
       </c>
-      <c r="F591">
+      <c r="F591" s="4">
         <v>25</v>
       </c>
       <c r="G591" t="s">
@@ -16195,7 +16194,7 @@
       <c r="E592" t="s">
         <v>10</v>
       </c>
-      <c r="F592">
+      <c r="F592" s="4">
         <v>36</v>
       </c>
       <c r="G592" t="s">
@@ -16221,7 +16220,7 @@
       <c r="E593" t="s">
         <v>10</v>
       </c>
-      <c r="F593">
+      <c r="F593" s="4">
         <v>37</v>
       </c>
       <c r="G593" s="2" t="s">
@@ -16247,7 +16246,7 @@
       <c r="E594" t="s">
         <v>10</v>
       </c>
-      <c r="F594">
+      <c r="F594" s="4">
         <v>26</v>
       </c>
       <c r="G594" t="s">
@@ -16273,7 +16272,7 @@
       <c r="E595" t="s">
         <v>10</v>
       </c>
-      <c r="F595">
+      <c r="F595" s="4">
         <v>37</v>
       </c>
       <c r="G595" t="s">
@@ -16299,7 +16298,7 @@
       <c r="E596" t="s">
         <v>19</v>
       </c>
-      <c r="F596">
+      <c r="F596" s="4">
         <v>24</v>
       </c>
       <c r="G596" s="2" t="s">
@@ -16325,7 +16324,7 @@
       <c r="E597" t="s">
         <v>10</v>
       </c>
-      <c r="F597">
+      <c r="F597" s="4">
         <v>39</v>
       </c>
       <c r="G597" t="s">
@@ -16351,7 +16350,7 @@
       <c r="E598" t="s">
         <v>10</v>
       </c>
-      <c r="F598">
+      <c r="F598" s="4">
         <v>26</v>
       </c>
       <c r="G598" t="s">
@@ -16377,7 +16376,7 @@
       <c r="E599" t="s">
         <v>10</v>
       </c>
-      <c r="F599">
+      <c r="F599" s="4">
         <v>34</v>
       </c>
       <c r="G599" s="2" t="s">
@@ -16403,7 +16402,7 @@
       <c r="E600" t="s">
         <v>10</v>
       </c>
-      <c r="F600">
+      <c r="F600" s="4">
         <v>28</v>
       </c>
       <c r="G600" t="s">
@@ -16429,7 +16428,7 @@
       <c r="E601" t="s">
         <v>10</v>
       </c>
-      <c r="F601">
+      <c r="F601" s="4">
         <v>32</v>
       </c>
       <c r="G601" t="s">
@@ -16455,7 +16454,7 @@
       <c r="E602" t="s">
         <v>10</v>
       </c>
-      <c r="F602">
+      <c r="F602" s="4">
         <v>39</v>
       </c>
       <c r="G602" s="2" t="s">
@@ -16481,7 +16480,7 @@
       <c r="E603" t="s">
         <v>10</v>
       </c>
-      <c r="F603">
+      <c r="F603" s="4">
         <v>29</v>
       </c>
       <c r="G603" t="s">
@@ -16507,7 +16506,7 @@
       <c r="E604" t="s">
         <v>10</v>
       </c>
-      <c r="F604">
+      <c r="F604" s="4">
         <v>32</v>
       </c>
       <c r="G604" s="2" t="s">
@@ -16533,7 +16532,7 @@
       <c r="E605" t="s">
         <v>14</v>
       </c>
-      <c r="F605">
+      <c r="F605" s="4">
         <v>25</v>
       </c>
       <c r="G605" t="s">
@@ -16559,7 +16558,7 @@
       <c r="E606" t="s">
         <v>19</v>
       </c>
-      <c r="F606">
+      <c r="F606" s="4">
         <v>36</v>
       </c>
       <c r="G606" t="s">
@@ -16585,7 +16584,7 @@
       <c r="E607" t="s">
         <v>10</v>
       </c>
-      <c r="F607">
+      <c r="F607" s="4">
         <v>25</v>
       </c>
       <c r="G607" s="2" t="s">
@@ -16611,7 +16610,7 @@
       <c r="E608" t="s">
         <v>10</v>
       </c>
-      <c r="F608">
+      <c r="F608" s="4">
         <v>58</v>
       </c>
       <c r="G608" t="s">
@@ -16637,7 +16636,7 @@
       <c r="E609" t="s">
         <v>10</v>
       </c>
-      <c r="F609">
+      <c r="F609" s="4">
         <v>24</v>
       </c>
       <c r="G609" t="s">
@@ -16663,7 +16662,7 @@
       <c r="E610" t="s">
         <v>14</v>
       </c>
-      <c r="F610">
+      <c r="F610" s="4">
         <v>56</v>
       </c>
       <c r="G610" s="2" t="s">
@@ -16689,7 +16688,7 @@
       <c r="E611" t="s">
         <v>10</v>
       </c>
-      <c r="F611">
+      <c r="F611" s="4">
         <v>27</v>
       </c>
       <c r="G611" t="s">
@@ -16715,7 +16714,7 @@
       <c r="E612" t="s">
         <v>10</v>
       </c>
-      <c r="F612">
+      <c r="F612" s="4">
         <v>40</v>
       </c>
       <c r="G612" t="s">
@@ -16741,7 +16740,7 @@
       <c r="E613" t="s">
         <v>14</v>
       </c>
-      <c r="F613">
+      <c r="F613" s="4">
         <v>28</v>
       </c>
       <c r="G613" t="s">
@@ -16767,7 +16766,7 @@
       <c r="E614" t="s">
         <v>14</v>
       </c>
-      <c r="F614">
+      <c r="F614" s="4">
         <v>39</v>
       </c>
       <c r="G614" t="s">
@@ -16793,7 +16792,7 @@
       <c r="E615" t="s">
         <v>19</v>
       </c>
-      <c r="F615">
+      <c r="F615" s="4">
         <v>38</v>
       </c>
       <c r="G615" s="2" t="s">
@@ -16819,7 +16818,7 @@
       <c r="E616" t="s">
         <v>14</v>
       </c>
-      <c r="F616">
+      <c r="F616" s="4">
         <v>32</v>
       </c>
       <c r="G616" t="s">
@@ -16845,7 +16844,7 @@
       <c r="E617" t="s">
         <v>14</v>
       </c>
-      <c r="F617">
+      <c r="F617" s="4">
         <v>26</v>
       </c>
       <c r="G617" t="s">
@@ -16871,7 +16870,7 @@
       <c r="E618" t="s">
         <v>14</v>
       </c>
-      <c r="F618">
+      <c r="F618" s="4">
         <v>31</v>
       </c>
       <c r="G618" t="s">
@@ -16897,7 +16896,7 @@
       <c r="E619" t="s">
         <v>19</v>
       </c>
-      <c r="F619">
+      <c r="F619" s="4">
         <v>24</v>
       </c>
       <c r="G619" t="s">
@@ -16923,7 +16922,7 @@
       <c r="E620" t="s">
         <v>19</v>
       </c>
-      <c r="F620">
+      <c r="F620" s="4">
         <v>39</v>
       </c>
       <c r="G620" s="2" t="s">
@@ -16949,7 +16948,7 @@
       <c r="E621" t="s">
         <v>14</v>
       </c>
-      <c r="F621">
+      <c r="F621" s="4">
         <v>28</v>
       </c>
       <c r="G621" t="s">
@@ -16975,7 +16974,7 @@
       <c r="E622" t="s">
         <v>19</v>
       </c>
-      <c r="F622">
+      <c r="F622" s="4">
         <v>26</v>
       </c>
       <c r="G622" t="s">
@@ -17001,7 +17000,7 @@
       <c r="E623" t="s">
         <v>19</v>
       </c>
-      <c r="F623">
+      <c r="F623" s="4">
         <v>46</v>
       </c>
       <c r="G623" t="s">
@@ -17027,7 +17026,7 @@
       <c r="E624" t="s">
         <v>10</v>
       </c>
-      <c r="F624">
+      <c r="F624" s="4">
         <v>37</v>
       </c>
       <c r="G624" s="2" t="s">
@@ -17053,7 +17052,7 @@
       <c r="E625" t="s">
         <v>10</v>
       </c>
-      <c r="F625">
+      <c r="F625" s="4">
         <v>52</v>
       </c>
       <c r="G625" t="s">
@@ -17079,7 +17078,7 @@
       <c r="E626" t="s">
         <v>14</v>
       </c>
-      <c r="F626">
+      <c r="F626" s="4">
         <v>46</v>
       </c>
       <c r="G626" t="s">
@@ -17105,7 +17104,7 @@
       <c r="E627" t="s">
         <v>19</v>
       </c>
-      <c r="F627">
+      <c r="F627" s="4">
         <v>42</v>
       </c>
       <c r="G627" t="s">
@@ -17131,7 +17130,7 @@
       <c r="E628" t="s">
         <v>19</v>
       </c>
-      <c r="F628">
+      <c r="F628" s="4">
         <v>21</v>
       </c>
       <c r="G628" s="2" t="s">
@@ -17157,7 +17156,7 @@
       <c r="E629" t="s">
         <v>14</v>
       </c>
-      <c r="F629">
+      <c r="F629" s="4">
         <v>28</v>
       </c>
       <c r="G629" t="s">
@@ -17183,7 +17182,7 @@
       <c r="E630" t="s">
         <v>10</v>
       </c>
-      <c r="F630">
+      <c r="F630" s="4">
         <v>29</v>
       </c>
       <c r="G630" t="s">
@@ -17209,7 +17208,7 @@
       <c r="E631" t="s">
         <v>19</v>
       </c>
-      <c r="F631">
+      <c r="F631" s="4">
         <v>23</v>
       </c>
       <c r="G631" s="2" t="s">
@@ -17235,7 +17234,7 @@
       <c r="E632" t="s">
         <v>10</v>
       </c>
-      <c r="F632">
+      <c r="F632" s="4">
         <v>41</v>
       </c>
       <c r="G632" t="s">
@@ -17261,7 +17260,7 @@
       <c r="E633" t="s">
         <v>14</v>
       </c>
-      <c r="F633">
+      <c r="F633" s="4">
         <v>28</v>
       </c>
       <c r="G633" t="s">
@@ -17287,7 +17286,7 @@
       <c r="E634" t="s">
         <v>14</v>
       </c>
-      <c r="F634">
+      <c r="F634" s="4">
         <v>37</v>
       </c>
       <c r="G634" s="2" t="s">
@@ -17313,7 +17312,7 @@
       <c r="E635" t="s">
         <v>14</v>
       </c>
-      <c r="F635">
+      <c r="F635" s="4">
         <v>34</v>
       </c>
       <c r="G635" t="s">
@@ -17339,7 +17338,7 @@
       <c r="E636" t="s">
         <v>14</v>
       </c>
-      <c r="F636">
+      <c r="F636" s="4">
         <v>26</v>
       </c>
       <c r="G636" t="s">
@@ -17365,7 +17364,7 @@
       <c r="E637" t="s">
         <v>19</v>
       </c>
-      <c r="F637">
+      <c r="F637" s="4">
         <v>35</v>
       </c>
       <c r="G637" t="s">
@@ -17391,7 +17390,7 @@
       <c r="E638" t="s">
         <v>10</v>
       </c>
-      <c r="F638">
+      <c r="F638" s="4">
         <v>36</v>
       </c>
       <c r="G638" t="s">
@@ -17417,7 +17416,7 @@
       <c r="E639" t="s">
         <v>10</v>
       </c>
-      <c r="F639">
+      <c r="F639" s="4">
         <v>29</v>
       </c>
       <c r="G639" s="2" t="s">
@@ -17443,7 +17442,7 @@
       <c r="E640" t="s">
         <v>19</v>
       </c>
-      <c r="F640">
+      <c r="F640" s="4">
         <v>27</v>
       </c>
       <c r="G640" t="s">
@@ -17469,7 +17468,7 @@
       <c r="E641" t="s">
         <v>10</v>
       </c>
-      <c r="F641">
+      <c r="F641" s="4">
         <v>25</v>
       </c>
       <c r="G641" t="s">
@@ -17495,7 +17494,7 @@
       <c r="E642" t="s">
         <v>10</v>
       </c>
-      <c r="F642">
+      <c r="F642" s="4">
         <v>36</v>
       </c>
       <c r="G642" t="s">
@@ -17521,7 +17520,7 @@
       <c r="E643" t="s">
         <v>10</v>
       </c>
-      <c r="F643">
+      <c r="F643" s="4">
         <v>37</v>
       </c>
       <c r="G643" s="2" t="s">
@@ -17547,7 +17546,7 @@
       <c r="E644" t="s">
         <v>10</v>
       </c>
-      <c r="F644">
+      <c r="F644" s="4">
         <v>26</v>
       </c>
       <c r="G644" t="s">
@@ -17573,7 +17572,7 @@
       <c r="E645" t="s">
         <v>10</v>
       </c>
-      <c r="F645">
+      <c r="F645" s="4">
         <v>37</v>
       </c>
       <c r="G645" t="s">
@@ -17599,7 +17598,7 @@
       <c r="E646" t="s">
         <v>19</v>
       </c>
-      <c r="F646">
+      <c r="F646" s="4">
         <v>24</v>
       </c>
       <c r="G646" s="2" t="s">
@@ -17625,7 +17624,7 @@
       <c r="E647" t="s">
         <v>10</v>
       </c>
-      <c r="F647">
+      <c r="F647" s="4">
         <v>39</v>
       </c>
       <c r="G647" t="s">
@@ -17651,7 +17650,7 @@
       <c r="E648" t="s">
         <v>10</v>
       </c>
-      <c r="F648">
+      <c r="F648" s="4">
         <v>26</v>
       </c>
       <c r="G648" t="s">
@@ -17677,7 +17676,7 @@
       <c r="E649" t="s">
         <v>10</v>
       </c>
-      <c r="F649">
+      <c r="F649" s="4">
         <v>34</v>
       </c>
       <c r="G649" s="2" t="s">
@@ -17703,7 +17702,7 @@
       <c r="E650" t="s">
         <v>10</v>
       </c>
-      <c r="F650">
+      <c r="F650" s="4">
         <v>28</v>
       </c>
       <c r="G650" t="s">
@@ -17729,7 +17728,7 @@
       <c r="E651" t="s">
         <v>10</v>
       </c>
-      <c r="F651">
+      <c r="F651" s="4">
         <v>32</v>
       </c>
       <c r="G651" t="s">
@@ -17755,7 +17754,7 @@
       <c r="E652" t="s">
         <v>10</v>
       </c>
-      <c r="F652">
+      <c r="F652" s="4">
         <v>39</v>
       </c>
       <c r="G652" s="2" t="s">
@@ -17781,7 +17780,7 @@
       <c r="E653" t="s">
         <v>10</v>
       </c>
-      <c r="F653">
+      <c r="F653" s="4">
         <v>39</v>
       </c>
       <c r="G653" s="2" t="s">
@@ -17807,7 +17806,7 @@
       <c r="E654" t="s">
         <v>10</v>
       </c>
-      <c r="F654">
+      <c r="F654" s="4">
         <v>29</v>
       </c>
       <c r="G654" t="s">
@@ -17833,7 +17832,7 @@
       <c r="E655" t="s">
         <v>10</v>
       </c>
-      <c r="F655">
+      <c r="F655" s="4">
         <v>32</v>
       </c>
       <c r="G655" s="2" t="s">
@@ -17859,7 +17858,7 @@
       <c r="E656" t="s">
         <v>14</v>
       </c>
-      <c r="F656">
+      <c r="F656" s="4">
         <v>25</v>
       </c>
       <c r="G656" t="s">
@@ -17885,7 +17884,7 @@
       <c r="E657" t="s">
         <v>19</v>
       </c>
-      <c r="F657">
+      <c r="F657" s="4">
         <v>36</v>
       </c>
       <c r="G657" t="s">
@@ -17911,7 +17910,7 @@
       <c r="E658" t="s">
         <v>10</v>
       </c>
-      <c r="F658">
+      <c r="F658" s="4">
         <v>25</v>
       </c>
       <c r="G658" s="2" t="s">
@@ -17937,7 +17936,7 @@
       <c r="E659" t="s">
         <v>10</v>
       </c>
-      <c r="F659">
+      <c r="F659" s="4">
         <v>58</v>
       </c>
       <c r="G659" t="s">
@@ -17963,7 +17962,7 @@
       <c r="E660" t="s">
         <v>10</v>
       </c>
-      <c r="F660">
+      <c r="F660" s="4">
         <v>24</v>
       </c>
       <c r="G660" t="s">
@@ -17989,7 +17988,7 @@
       <c r="E661" t="s">
         <v>14</v>
       </c>
-      <c r="F661">
+      <c r="F661" s="4">
         <v>56</v>
       </c>
       <c r="G661" s="2" t="s">
@@ -18015,7 +18014,7 @@
       <c r="E662" t="s">
         <v>10</v>
       </c>
-      <c r="F662">
+      <c r="F662" s="4">
         <v>27</v>
       </c>
       <c r="G662" t="s">
@@ -18041,7 +18040,7 @@
       <c r="E663" t="s">
         <v>10</v>
       </c>
-      <c r="F663">
+      <c r="F663" s="4">
         <v>40</v>
       </c>
       <c r="G663" t="s">
@@ -18067,7 +18066,7 @@
       <c r="E664" t="s">
         <v>14</v>
       </c>
-      <c r="F664">
+      <c r="F664" s="4">
         <v>28</v>
       </c>
       <c r="G664" t="s">
@@ -18093,7 +18092,7 @@
       <c r="E665" t="s">
         <v>14</v>
       </c>
-      <c r="F665">
+      <c r="F665" s="4">
         <v>39</v>
       </c>
       <c r="G665" t="s">
@@ -18119,7 +18118,7 @@
       <c r="E666" t="s">
         <v>19</v>
       </c>
-      <c r="F666">
+      <c r="F666" s="4">
         <v>38</v>
       </c>
       <c r="G666" s="2" t="s">
@@ -18145,7 +18144,7 @@
       <c r="E667" t="s">
         <v>14</v>
       </c>
-      <c r="F667">
+      <c r="F667" s="4">
         <v>32</v>
       </c>
       <c r="G667" t="s">
@@ -18171,7 +18170,7 @@
       <c r="E668" t="s">
         <v>14</v>
       </c>
-      <c r="F668">
+      <c r="F668" s="4">
         <v>26</v>
       </c>
       <c r="G668" t="s">
@@ -18197,7 +18196,7 @@
       <c r="E669" t="s">
         <v>14</v>
       </c>
-      <c r="F669">
+      <c r="F669" s="4">
         <v>31</v>
       </c>
       <c r="G669" t="s">
@@ -18223,7 +18222,7 @@
       <c r="E670" t="s">
         <v>19</v>
       </c>
-      <c r="F670">
+      <c r="F670" s="4">
         <v>24</v>
       </c>
       <c r="G670" t="s">
@@ -18249,7 +18248,7 @@
       <c r="E671" t="s">
         <v>19</v>
       </c>
-      <c r="F671">
+      <c r="F671" s="4">
         <v>39</v>
       </c>
       <c r="G671" s="2" t="s">
@@ -18275,7 +18274,7 @@
       <c r="E672" t="s">
         <v>14</v>
       </c>
-      <c r="F672">
+      <c r="F672" s="4">
         <v>28</v>
       </c>
       <c r="G672" t="s">
@@ -18301,7 +18300,7 @@
       <c r="E673" t="s">
         <v>19</v>
       </c>
-      <c r="F673">
+      <c r="F673" s="4">
         <v>26</v>
       </c>
       <c r="G673" t="s">
@@ -18327,7 +18326,7 @@
       <c r="E674" t="s">
         <v>19</v>
       </c>
-      <c r="F674">
+      <c r="F674" s="4">
         <v>46</v>
       </c>
       <c r="G674" t="s">
@@ -18353,7 +18352,7 @@
       <c r="E675" t="s">
         <v>10</v>
       </c>
-      <c r="F675">
+      <c r="F675" s="4">
         <v>37</v>
       </c>
       <c r="G675" s="2" t="s">
@@ -18379,7 +18378,7 @@
       <c r="E676" t="s">
         <v>10</v>
       </c>
-      <c r="F676">
+      <c r="F676" s="4">
         <v>52</v>
       </c>
       <c r="G676" t="s">
@@ -18405,7 +18404,7 @@
       <c r="E677" t="s">
         <v>14</v>
       </c>
-      <c r="F677">
+      <c r="F677" s="4">
         <v>46</v>
       </c>
       <c r="G677" t="s">
@@ -18431,7 +18430,7 @@
       <c r="E678" t="s">
         <v>19</v>
       </c>
-      <c r="F678">
+      <c r="F678" s="4">
         <v>42</v>
       </c>
       <c r="G678" t="s">
@@ -18457,7 +18456,7 @@
       <c r="E679" t="s">
         <v>19</v>
       </c>
-      <c r="F679">
+      <c r="F679" s="4">
         <v>21</v>
       </c>
       <c r="G679" s="2" t="s">
@@ -18483,7 +18482,7 @@
       <c r="E680" t="s">
         <v>14</v>
       </c>
-      <c r="F680">
+      <c r="F680" s="4">
         <v>28</v>
       </c>
       <c r="G680" t="s">
@@ -18509,7 +18508,7 @@
       <c r="E681" t="s">
         <v>10</v>
       </c>
-      <c r="F681">
+      <c r="F681" s="4">
         <v>29</v>
       </c>
       <c r="G681" t="s">
@@ -18535,7 +18534,7 @@
       <c r="E682" t="s">
         <v>19</v>
       </c>
-      <c r="F682">
+      <c r="F682" s="4">
         <v>23</v>
       </c>
       <c r="G682" s="2" t="s">
@@ -18561,7 +18560,7 @@
       <c r="E683" t="s">
         <v>10</v>
       </c>
-      <c r="F683">
+      <c r="F683" s="4">
         <v>41</v>
       </c>
       <c r="G683" t="s">
@@ -18587,7 +18586,7 @@
       <c r="E684" t="s">
         <v>14</v>
       </c>
-      <c r="F684">
+      <c r="F684" s="4">
         <v>28</v>
       </c>
       <c r="G684" t="s">
@@ -18613,7 +18612,7 @@
       <c r="E685" t="s">
         <v>14</v>
       </c>
-      <c r="F685">
+      <c r="F685" s="4">
         <v>37</v>
       </c>
       <c r="G685" s="2" t="s">
@@ -18639,7 +18638,7 @@
       <c r="E686" t="s">
         <v>14</v>
       </c>
-      <c r="F686">
+      <c r="F686" s="4">
         <v>34</v>
       </c>
       <c r="G686" t="s">
@@ -18665,7 +18664,7 @@
       <c r="E687" t="s">
         <v>14</v>
       </c>
-      <c r="F687">
+      <c r="F687" s="4">
         <v>26</v>
       </c>
       <c r="G687" t="s">
@@ -18691,7 +18690,7 @@
       <c r="E688" t="s">
         <v>19</v>
       </c>
-      <c r="F688">
+      <c r="F688" s="4">
         <v>35</v>
       </c>
       <c r="G688" t="s">
@@ -18717,7 +18716,7 @@
       <c r="E689" t="s">
         <v>10</v>
       </c>
-      <c r="F689">
+      <c r="F689" s="4">
         <v>36</v>
       </c>
       <c r="G689" t="s">
@@ -18743,7 +18742,7 @@
       <c r="E690" t="s">
         <v>10</v>
       </c>
-      <c r="F690">
+      <c r="F690" s="4">
         <v>29</v>
       </c>
       <c r="G690" s="2" t="s">
@@ -18769,7 +18768,7 @@
       <c r="E691" t="s">
         <v>19</v>
       </c>
-      <c r="F691">
+      <c r="F691" s="4">
         <v>27</v>
       </c>
       <c r="G691" t="s">
@@ -18795,7 +18794,7 @@
       <c r="E692" t="s">
         <v>10</v>
       </c>
-      <c r="F692">
+      <c r="F692" s="4">
         <v>25</v>
       </c>
       <c r="G692" t="s">
@@ -18821,7 +18820,7 @@
       <c r="E693" t="s">
         <v>10</v>
       </c>
-      <c r="F693">
+      <c r="F693" s="4">
         <v>36</v>
       </c>
       <c r="G693" t="s">
@@ -18847,7 +18846,7 @@
       <c r="E694" t="s">
         <v>10</v>
       </c>
-      <c r="F694">
+      <c r="F694" s="4">
         <v>37</v>
       </c>
       <c r="G694" s="2" t="s">
@@ -18873,7 +18872,7 @@
       <c r="E695" t="s">
         <v>10</v>
       </c>
-      <c r="F695">
+      <c r="F695" s="4">
         <v>26</v>
       </c>
       <c r="G695" t="s">
@@ -18899,7 +18898,7 @@
       <c r="E696" t="s">
         <v>10</v>
       </c>
-      <c r="F696">
+      <c r="F696" s="4">
         <v>37</v>
       </c>
       <c r="G696" t="s">
@@ -18925,7 +18924,7 @@
       <c r="E697" t="s">
         <v>19</v>
       </c>
-      <c r="F697">
+      <c r="F697" s="4">
         <v>24</v>
       </c>
       <c r="G697" s="2" t="s">
@@ -18951,7 +18950,7 @@
       <c r="E698" t="s">
         <v>10</v>
       </c>
-      <c r="F698">
+      <c r="F698" s="4">
         <v>39</v>
       </c>
       <c r="G698" t="s">
@@ -18977,7 +18976,7 @@
       <c r="E699" t="s">
         <v>10</v>
       </c>
-      <c r="F699">
+      <c r="F699" s="4">
         <v>26</v>
       </c>
       <c r="G699" t="s">
@@ -19003,7 +19002,7 @@
       <c r="E700" t="s">
         <v>10</v>
       </c>
-      <c r="F700">
+      <c r="F700" s="4">
         <v>34</v>
       </c>
       <c r="G700" s="2" t="s">
@@ -19029,7 +19028,7 @@
       <c r="E701" t="s">
         <v>10</v>
       </c>
-      <c r="F701">
+      <c r="F701" s="4">
         <v>28</v>
       </c>
       <c r="G701" t="s">
@@ -19055,7 +19054,7 @@
       <c r="E702" t="s">
         <v>10</v>
       </c>
-      <c r="F702">
+      <c r="F702" s="4">
         <v>32</v>
       </c>
       <c r="G702" t="s">
@@ -19081,7 +19080,7 @@
       <c r="E703" t="s">
         <v>10</v>
       </c>
-      <c r="F703">
+      <c r="F703" s="4">
         <v>39</v>
       </c>
       <c r="G703" s="2" t="s">
@@ -19107,7 +19106,7 @@
       <c r="E704" t="s">
         <v>10</v>
       </c>
-      <c r="F704">
+      <c r="F704" s="4">
         <v>29</v>
       </c>
       <c r="G704" t="s">
@@ -19133,7 +19132,7 @@
       <c r="E705" t="s">
         <v>10</v>
       </c>
-      <c r="F705">
+      <c r="F705" s="4">
         <v>32</v>
       </c>
       <c r="G705" s="2" t="s">
@@ -19159,7 +19158,7 @@
       <c r="E706" t="s">
         <v>14</v>
       </c>
-      <c r="F706">
+      <c r="F706" s="4">
         <v>25</v>
       </c>
       <c r="G706" t="s">
@@ -19185,7 +19184,7 @@
       <c r="E707" t="s">
         <v>19</v>
       </c>
-      <c r="F707">
+      <c r="F707" s="4">
         <v>36</v>
       </c>
       <c r="G707" t="s">
@@ -19211,7 +19210,7 @@
       <c r="E708" t="s">
         <v>10</v>
       </c>
-      <c r="F708">
+      <c r="F708" s="4">
         <v>25</v>
       </c>
       <c r="G708" s="2" t="s">
@@ -19237,7 +19236,7 @@
       <c r="E709" t="s">
         <v>10</v>
       </c>
-      <c r="F709">
+      <c r="F709" s="4">
         <v>58</v>
       </c>
       <c r="G709" t="s">
@@ -19263,7 +19262,7 @@
       <c r="E710" t="s">
         <v>10</v>
       </c>
-      <c r="F710">
+      <c r="F710" s="4">
         <v>24</v>
       </c>
       <c r="G710" t="s">
@@ -19289,7 +19288,7 @@
       <c r="E711" t="s">
         <v>14</v>
       </c>
-      <c r="F711">
+      <c r="F711" s="4">
         <v>56</v>
       </c>
       <c r="G711" s="2" t="s">
@@ -19315,7 +19314,7 @@
       <c r="E712" t="s">
         <v>10</v>
       </c>
-      <c r="F712">
+      <c r="F712" s="4">
         <v>27</v>
       </c>
       <c r="G712" t="s">
@@ -19341,7 +19340,7 @@
       <c r="E713" t="s">
         <v>10</v>
       </c>
-      <c r="F713">
+      <c r="F713" s="4">
         <v>40</v>
       </c>
       <c r="G713" t="s">
@@ -19367,7 +19366,7 @@
       <c r="E714" t="s">
         <v>14</v>
       </c>
-      <c r="F714">
+      <c r="F714" s="4">
         <v>28</v>
       </c>
       <c r="G714" t="s">
@@ -19393,7 +19392,7 @@
       <c r="E715" t="s">
         <v>14</v>
       </c>
-      <c r="F715">
+      <c r="F715" s="4">
         <v>39</v>
       </c>
       <c r="G715" t="s">
@@ -19419,7 +19418,7 @@
       <c r="E716" t="s">
         <v>19</v>
       </c>
-      <c r="F716">
+      <c r="F716" s="4">
         <v>38</v>
       </c>
       <c r="G716" s="2" t="s">
@@ -19445,7 +19444,7 @@
       <c r="E717" t="s">
         <v>14</v>
       </c>
-      <c r="F717">
+      <c r="F717" s="4">
         <v>32</v>
       </c>
       <c r="G717" t="s">
@@ -19471,7 +19470,7 @@
       <c r="E718" t="s">
         <v>14</v>
       </c>
-      <c r="F718">
+      <c r="F718" s="4">
         <v>26</v>
       </c>
       <c r="G718" t="s">
@@ -19497,7 +19496,7 @@
       <c r="E719" t="s">
         <v>14</v>
       </c>
-      <c r="F719">
+      <c r="F719" s="4">
         <v>31</v>
       </c>
       <c r="G719" t="s">
@@ -19523,7 +19522,7 @@
       <c r="E720" t="s">
         <v>19</v>
       </c>
-      <c r="F720">
+      <c r="F720" s="4">
         <v>24</v>
       </c>
       <c r="G720" t="s">
@@ -19549,7 +19548,7 @@
       <c r="E721" t="s">
         <v>19</v>
       </c>
-      <c r="F721">
+      <c r="F721" s="4">
         <v>39</v>
       </c>
       <c r="G721" s="2" t="s">
@@ -19575,7 +19574,7 @@
       <c r="E722" t="s">
         <v>14</v>
       </c>
-      <c r="F722">
+      <c r="F722" s="4">
         <v>28</v>
       </c>
       <c r="G722" t="s">
@@ -19601,7 +19600,7 @@
       <c r="E723" t="s">
         <v>19</v>
       </c>
-      <c r="F723">
+      <c r="F723" s="4">
         <v>26</v>
       </c>
       <c r="G723" t="s">
@@ -19627,7 +19626,7 @@
       <c r="E724" t="s">
         <v>19</v>
       </c>
-      <c r="F724">
+      <c r="F724" s="4">
         <v>46</v>
       </c>
       <c r="G724" t="s">
@@ -19653,7 +19652,7 @@
       <c r="E725" t="s">
         <v>10</v>
       </c>
-      <c r="F725">
+      <c r="F725" s="4">
         <v>37</v>
       </c>
       <c r="G725" s="2" t="s">
@@ -19679,7 +19678,7 @@
       <c r="E726" t="s">
         <v>10</v>
       </c>
-      <c r="F726">
+      <c r="F726" s="4">
         <v>52</v>
       </c>
       <c r="G726" t="s">
@@ -19705,7 +19704,7 @@
       <c r="E727" t="s">
         <v>14</v>
       </c>
-      <c r="F727">
+      <c r="F727" s="4">
         <v>46</v>
       </c>
       <c r="G727" t="s">
@@ -19731,7 +19730,7 @@
       <c r="E728" t="s">
         <v>19</v>
       </c>
-      <c r="F728">
+      <c r="F728" s="4">
         <v>42</v>
       </c>
       <c r="G728" t="s">
@@ -19757,7 +19756,7 @@
       <c r="E729" t="s">
         <v>19</v>
       </c>
-      <c r="F729">
+      <c r="F729" s="4">
         <v>21</v>
       </c>
       <c r="G729" s="2" t="s">
@@ -19783,7 +19782,7 @@
       <c r="E730" t="s">
         <v>14</v>
       </c>
-      <c r="F730">
+      <c r="F730" s="4">
         <v>28</v>
       </c>
       <c r="G730" t="s">
@@ -19809,7 +19808,7 @@
       <c r="E731" t="s">
         <v>10</v>
       </c>
-      <c r="F731">
+      <c r="F731" s="4">
         <v>29</v>
       </c>
       <c r="G731" t="s">
@@ -19835,7 +19834,7 @@
       <c r="E732" t="s">
         <v>19</v>
       </c>
-      <c r="F732">
+      <c r="F732" s="4">
         <v>23</v>
       </c>
       <c r="G732" s="2" t="s">
@@ -19861,7 +19860,7 @@
       <c r="E733" t="s">
         <v>10</v>
       </c>
-      <c r="F733">
+      <c r="F733" s="4">
         <v>41</v>
       </c>
       <c r="G733" t="s">
@@ -19887,7 +19886,7 @@
       <c r="E734" t="s">
         <v>14</v>
       </c>
-      <c r="F734">
+      <c r="F734" s="4">
         <v>28</v>
       </c>
       <c r="G734" t="s">
@@ -19913,7 +19912,7 @@
       <c r="E735" t="s">
         <v>14</v>
       </c>
-      <c r="F735">
+      <c r="F735" s="4">
         <v>37</v>
       </c>
       <c r="G735" s="2" t="s">
@@ -19939,7 +19938,7 @@
       <c r="E736" t="s">
         <v>14</v>
       </c>
-      <c r="F736">
+      <c r="F736" s="4">
         <v>34</v>
       </c>
       <c r="G736" t="s">
@@ -19965,7 +19964,7 @@
       <c r="E737" t="s">
         <v>14</v>
       </c>
-      <c r="F737">
+      <c r="F737" s="4">
         <v>26</v>
       </c>
       <c r="G737" t="s">
@@ -19991,7 +19990,7 @@
       <c r="E738" t="s">
         <v>19</v>
       </c>
-      <c r="F738">
+      <c r="F738" s="4">
         <v>35</v>
       </c>
       <c r="G738" t="s">
@@ -20017,7 +20016,7 @@
       <c r="E739" t="s">
         <v>10</v>
       </c>
-      <c r="F739">
+      <c r="F739" s="4">
         <v>36</v>
       </c>
       <c r="G739" t="s">
@@ -20043,7 +20042,7 @@
       <c r="E740" t="s">
         <v>10</v>
       </c>
-      <c r="F740">
+      <c r="F740" s="4">
         <v>29</v>
       </c>
       <c r="G740" s="2" t="s">
@@ -20069,7 +20068,7 @@
       <c r="E741" t="s">
         <v>19</v>
       </c>
-      <c r="F741">
+      <c r="F741" s="4">
         <v>27</v>
       </c>
       <c r="G741" t="s">
@@ -20095,7 +20094,7 @@
       <c r="E742" t="s">
         <v>10</v>
       </c>
-      <c r="F742">
+      <c r="F742" s="4">
         <v>25</v>
       </c>
       <c r="G742" t="s">
@@ -20121,7 +20120,7 @@
       <c r="E743" t="s">
         <v>10</v>
       </c>
-      <c r="F743">
+      <c r="F743" s="4">
         <v>36</v>
       </c>
       <c r="G743" t="s">
@@ -20147,7 +20146,7 @@
       <c r="E744" t="s">
         <v>10</v>
       </c>
-      <c r="F744">
+      <c r="F744" s="4">
         <v>37</v>
       </c>
       <c r="G744" s="2" t="s">
@@ -20173,7 +20172,7 @@
       <c r="E745" t="s">
         <v>10</v>
       </c>
-      <c r="F745">
+      <c r="F745" s="4">
         <v>26</v>
       </c>
       <c r="G745" t="s">
@@ -20199,7 +20198,7 @@
       <c r="E746" t="s">
         <v>10</v>
       </c>
-      <c r="F746">
+      <c r="F746" s="4">
         <v>37</v>
       </c>
       <c r="G746" t="s">
@@ -20225,7 +20224,7 @@
       <c r="E747" t="s">
         <v>19</v>
       </c>
-      <c r="F747">
+      <c r="F747" s="4">
         <v>24</v>
       </c>
       <c r="G747" s="2" t="s">
@@ -20251,7 +20250,7 @@
       <c r="E748" t="s">
         <v>10</v>
       </c>
-      <c r="F748">
+      <c r="F748" s="4">
         <v>39</v>
       </c>
       <c r="G748" t="s">
@@ -20277,7 +20276,7 @@
       <c r="E749" t="s">
         <v>10</v>
       </c>
-      <c r="F749">
+      <c r="F749" s="4">
         <v>26</v>
       </c>
       <c r="G749" t="s">
@@ -20303,7 +20302,7 @@
       <c r="E750" t="s">
         <v>10</v>
       </c>
-      <c r="F750">
+      <c r="F750" s="4">
         <v>34</v>
       </c>
       <c r="G750" s="2" t="s">
@@ -20329,7 +20328,7 @@
       <c r="E751" t="s">
         <v>10</v>
       </c>
-      <c r="F751">
+      <c r="F751" s="4">
         <v>28</v>
       </c>
       <c r="G751" t="s">
@@ -20355,7 +20354,7 @@
       <c r="E752" t="s">
         <v>10</v>
       </c>
-      <c r="F752">
+      <c r="F752" s="4">
         <v>32</v>
       </c>
       <c r="G752" t="s">
@@ -20381,7 +20380,7 @@
       <c r="E753" t="s">
         <v>10</v>
       </c>
-      <c r="F753">
+      <c r="F753" s="4">
         <v>39</v>
       </c>
       <c r="G753" s="2" t="s">
@@ -20407,7 +20406,7 @@
       <c r="E754" t="s">
         <v>10</v>
       </c>
-      <c r="F754">
+      <c r="F754" s="4">
         <v>29</v>
       </c>
       <c r="G754" t="s">
@@ -20433,7 +20432,7 @@
       <c r="E755" t="s">
         <v>10</v>
       </c>
-      <c r="F755">
+      <c r="F755" s="4">
         <v>32</v>
       </c>
       <c r="G755" s="2" t="s">
@@ -20459,7 +20458,7 @@
       <c r="E756" t="s">
         <v>14</v>
       </c>
-      <c r="F756">
+      <c r="F756" s="4">
         <v>25</v>
       </c>
       <c r="G756" t="s">
@@ -20485,7 +20484,7 @@
       <c r="E757" t="s">
         <v>19</v>
       </c>
-      <c r="F757">
+      <c r="F757" s="4">
         <v>36</v>
       </c>
       <c r="G757" t="s">
@@ -20511,7 +20510,7 @@
       <c r="E758" t="s">
         <v>10</v>
       </c>
-      <c r="F758">
+      <c r="F758" s="4">
         <v>25</v>
       </c>
       <c r="G758" s="2" t="s">
@@ -20537,7 +20536,7 @@
       <c r="E759" t="s">
         <v>10</v>
       </c>
-      <c r="F759">
+      <c r="F759" s="4">
         <v>58</v>
       </c>
       <c r="G759" t="s">
@@ -20563,7 +20562,7 @@
       <c r="E760" t="s">
         <v>10</v>
       </c>
-      <c r="F760">
+      <c r="F760" s="4">
         <v>24</v>
       </c>
       <c r="G760" t="s">
@@ -20589,7 +20588,7 @@
       <c r="E761" t="s">
         <v>14</v>
       </c>
-      <c r="F761">
+      <c r="F761" s="4">
         <v>56</v>
       </c>
       <c r="G761" s="2" t="s">
@@ -20615,7 +20614,7 @@
       <c r="E762" t="s">
         <v>10</v>
       </c>
-      <c r="F762">
+      <c r="F762" s="4">
         <v>27</v>
       </c>
       <c r="G762" t="s">
@@ -20641,7 +20640,7 @@
       <c r="E763" t="s">
         <v>10</v>
       </c>
-      <c r="F763">
+      <c r="F763" s="4">
         <v>40</v>
       </c>
       <c r="G763" t="s">
@@ -20667,7 +20666,7 @@
       <c r="E764" t="s">
         <v>14</v>
       </c>
-      <c r="F764">
+      <c r="F764" s="4">
         <v>28</v>
       </c>
       <c r="G764" t="s">
@@ -20693,7 +20692,7 @@
       <c r="E765" t="s">
         <v>14</v>
       </c>
-      <c r="F765">
+      <c r="F765" s="4">
         <v>39</v>
       </c>
       <c r="G765" t="s">
@@ -20719,7 +20718,7 @@
       <c r="E766" t="s">
         <v>19</v>
       </c>
-      <c r="F766">
+      <c r="F766" s="4">
         <v>38</v>
       </c>
       <c r="G766" s="2" t="s">
@@ -20745,7 +20744,7 @@
       <c r="E767" t="s">
         <v>14</v>
       </c>
-      <c r="F767">
+      <c r="F767" s="4">
         <v>32</v>
       </c>
       <c r="G767" t="s">
@@ -20771,7 +20770,7 @@
       <c r="E768" t="s">
         <v>14</v>
       </c>
-      <c r="F768">
+      <c r="F768" s="4">
         <v>26</v>
       </c>
       <c r="G768" t="s">
@@ -20797,7 +20796,7 @@
       <c r="E769" t="s">
         <v>14</v>
       </c>
-      <c r="F769">
+      <c r="F769" s="4">
         <v>31</v>
       </c>
       <c r="G769" t="s">
@@ -20823,7 +20822,7 @@
       <c r="E770" t="s">
         <v>19</v>
       </c>
-      <c r="F770">
+      <c r="F770" s="4">
         <v>24</v>
       </c>
       <c r="G770" t="s">
@@ -20849,7 +20848,7 @@
       <c r="E771" t="s">
         <v>19</v>
       </c>
-      <c r="F771">
+      <c r="F771" s="4">
         <v>39</v>
       </c>
       <c r="G771" s="2" t="s">
@@ -20875,7 +20874,7 @@
       <c r="E772" t="s">
         <v>14</v>
       </c>
-      <c r="F772">
+      <c r="F772" s="4">
         <v>28</v>
       </c>
       <c r="G772" t="s">
@@ -20901,7 +20900,7 @@
       <c r="E773" t="s">
         <v>19</v>
       </c>
-      <c r="F773">
+      <c r="F773" s="4">
         <v>26</v>
       </c>
       <c r="G773" t="s">
@@ -20927,7 +20926,7 @@
       <c r="E774" t="s">
         <v>19</v>
       </c>
-      <c r="F774">
+      <c r="F774" s="4">
         <v>46</v>
       </c>
       <c r="G774" t="s">
@@ -20953,7 +20952,7 @@
       <c r="E775" t="s">
         <v>10</v>
       </c>
-      <c r="F775">
+      <c r="F775" s="4">
         <v>37</v>
       </c>
       <c r="G775" s="2" t="s">
@@ -20979,7 +20978,7 @@
       <c r="E776" t="s">
         <v>10</v>
       </c>
-      <c r="F776">
+      <c r="F776" s="4">
         <v>52</v>
       </c>
       <c r="G776" t="s">
@@ -21005,7 +21004,7 @@
       <c r="E777" t="s">
         <v>14</v>
       </c>
-      <c r="F777">
+      <c r="F777" s="4">
         <v>46</v>
       </c>
       <c r="G777" t="s">
@@ -21031,7 +21030,7 @@
       <c r="E778" t="s">
         <v>19</v>
       </c>
-      <c r="F778">
+      <c r="F778" s="4">
         <v>42</v>
       </c>
       <c r="G778" t="s">
@@ -21057,7 +21056,7 @@
       <c r="E779" t="s">
         <v>19</v>
       </c>
-      <c r="F779">
+      <c r="F779" s="4">
         <v>21</v>
       </c>
       <c r="G779" s="2" t="s">
@@ -21083,7 +21082,7 @@
       <c r="E780" t="s">
         <v>14</v>
       </c>
-      <c r="F780">
+      <c r="F780" s="4">
         <v>28</v>
       </c>
       <c r="G780" t="s">
@@ -21109,7 +21108,7 @@
       <c r="E781" t="s">
         <v>10</v>
       </c>
-      <c r="F781">
+      <c r="F781" s="4">
         <v>29</v>
       </c>
       <c r="G781" t="s">
@@ -21135,7 +21134,7 @@
       <c r="E782" t="s">
         <v>19</v>
       </c>
-      <c r="F782">
+      <c r="F782" s="4">
         <v>23</v>
       </c>
       <c r="G782" s="2" t="s">
@@ -21161,7 +21160,7 @@
       <c r="E783" t="s">
         <v>10</v>
       </c>
-      <c r="F783">
+      <c r="F783" s="4">
         <v>41</v>
       </c>
       <c r="G783" t="s">
@@ -21187,7 +21186,7 @@
       <c r="E784" t="s">
         <v>14</v>
       </c>
-      <c r="F784">
+      <c r="F784" s="4">
         <v>28</v>
       </c>
       <c r="G784" t="s">
@@ -21213,7 +21212,7 @@
       <c r="E785" t="s">
         <v>14</v>
       </c>
-      <c r="F785">
+      <c r="F785" s="4">
         <v>37</v>
       </c>
       <c r="G785" s="2" t="s">
@@ -21239,7 +21238,7 @@
       <c r="E786" t="s">
         <v>14</v>
       </c>
-      <c r="F786">
+      <c r="F786" s="4">
         <v>34</v>
       </c>
       <c r="G786" t="s">
@@ -21265,7 +21264,7 @@
       <c r="E787" t="s">
         <v>14</v>
       </c>
-      <c r="F787">
+      <c r="F787" s="4">
         <v>26</v>
       </c>
       <c r="G787" t="s">
@@ -21291,7 +21290,7 @@
       <c r="E788" t="s">
         <v>19</v>
       </c>
-      <c r="F788">
+      <c r="F788" s="4">
         <v>35</v>
       </c>
       <c r="G788" t="s">
@@ -21317,7 +21316,7 @@
       <c r="E789" t="s">
         <v>10</v>
       </c>
-      <c r="F789">
+      <c r="F789" s="4">
         <v>36</v>
       </c>
       <c r="G789" t="s">
@@ -21343,7 +21342,7 @@
       <c r="E790" t="s">
         <v>10</v>
       </c>
-      <c r="F790">
+      <c r="F790" s="4">
         <v>29</v>
       </c>
       <c r="G790" s="2" t="s">
@@ -21369,7 +21368,7 @@
       <c r="E791" t="s">
         <v>19</v>
       </c>
-      <c r="F791">
+      <c r="F791" s="4">
         <v>27</v>
       </c>
       <c r="G791" t="s">
@@ -21395,7 +21394,7 @@
       <c r="E792" t="s">
         <v>10</v>
       </c>
-      <c r="F792">
+      <c r="F792" s="4">
         <v>25</v>
       </c>
       <c r="G792" t="s">
@@ -21421,7 +21420,7 @@
       <c r="E793" t="s">
         <v>10</v>
       </c>
-      <c r="F793">
+      <c r="F793" s="4">
         <v>36</v>
       </c>
       <c r="G793" t="s">
@@ -21447,7 +21446,7 @@
       <c r="E794" t="s">
         <v>10</v>
       </c>
-      <c r="F794">
+      <c r="F794" s="4">
         <v>37</v>
       </c>
       <c r="G794" s="2" t="s">
@@ -21473,7 +21472,7 @@
       <c r="E795" t="s">
         <v>10</v>
       </c>
-      <c r="F795">
+      <c r="F795" s="4">
         <v>26</v>
       </c>
       <c r="G795" t="s">
@@ -21499,7 +21498,7 @@
       <c r="E796" t="s">
         <v>10</v>
       </c>
-      <c r="F796">
+      <c r="F796" s="4">
         <v>37</v>
       </c>
       <c r="G796" t="s">
@@ -21525,7 +21524,7 @@
       <c r="E797" t="s">
         <v>19</v>
       </c>
-      <c r="F797">
+      <c r="F797" s="4">
         <v>24</v>
       </c>
       <c r="G797" s="2" t="s">
@@ -21551,7 +21550,7 @@
       <c r="E798" t="s">
         <v>10</v>
       </c>
-      <c r="F798">
+      <c r="F798" s="4">
         <v>39</v>
       </c>
       <c r="G798" t="s">
@@ -21577,7 +21576,7 @@
       <c r="E799" t="s">
         <v>10</v>
       </c>
-      <c r="F799">
+      <c r="F799" s="4">
         <v>26</v>
       </c>
       <c r="G799" t="s">
@@ -21603,7 +21602,7 @@
       <c r="E800" t="s">
         <v>10</v>
       </c>
-      <c r="F800">
+      <c r="F800" s="4">
         <v>34</v>
       </c>
       <c r="G800" s="2" t="s">
@@ -21629,7 +21628,7 @@
       <c r="E801" t="s">
         <v>10</v>
       </c>
-      <c r="F801">
+      <c r="F801" s="4">
         <v>28</v>
       </c>
       <c r="G801" t="s">
@@ -21655,7 +21654,7 @@
       <c r="E802" t="s">
         <v>10</v>
       </c>
-      <c r="F802">
+      <c r="F802" s="4">
         <v>32</v>
       </c>
       <c r="G802" t="s">
@@ -21681,7 +21680,7 @@
       <c r="E803" t="s">
         <v>10</v>
       </c>
-      <c r="F803">
+      <c r="F803" s="4">
         <v>39</v>
       </c>
       <c r="G803" s="2" t="s">
@@ -21707,7 +21706,7 @@
       <c r="E804" t="s">
         <v>10</v>
       </c>
-      <c r="F804">
+      <c r="F804" s="4">
         <v>29</v>
       </c>
       <c r="G804" t="s">
@@ -21733,7 +21732,7 @@
       <c r="E805" t="s">
         <v>10</v>
       </c>
-      <c r="F805">
+      <c r="F805" s="4">
         <v>32</v>
       </c>
       <c r="G805" s="2" t="s">
@@ -21759,7 +21758,7 @@
       <c r="E806" t="s">
         <v>14</v>
       </c>
-      <c r="F806">
+      <c r="F806" s="4">
         <v>25</v>
       </c>
       <c r="G806" t="s">
@@ -21785,7 +21784,7 @@
       <c r="E807" t="s">
         <v>19</v>
       </c>
-      <c r="F807">
+      <c r="F807" s="4">
         <v>36</v>
       </c>
       <c r="G807" t="s">
@@ -21811,7 +21810,7 @@
       <c r="E808" t="s">
         <v>10</v>
       </c>
-      <c r="F808">
+      <c r="F808" s="4">
         <v>25</v>
       </c>
       <c r="G808" s="2" t="s">
@@ -21837,7 +21836,7 @@
       <c r="E809" t="s">
         <v>10</v>
       </c>
-      <c r="F809">
+      <c r="F809" s="4">
         <v>58</v>
       </c>
       <c r="G809" t="s">
@@ -21863,7 +21862,7 @@
       <c r="E810" t="s">
         <v>10</v>
       </c>
-      <c r="F810">
+      <c r="F810" s="4">
         <v>24</v>
       </c>
       <c r="G810" t="s">
@@ -21889,7 +21888,7 @@
       <c r="E811" t="s">
         <v>14</v>
       </c>
-      <c r="F811">
+      <c r="F811" s="4">
         <v>56</v>
       </c>
       <c r="G811" s="2" t="s">
@@ -21915,7 +21914,7 @@
       <c r="E812" t="s">
         <v>10</v>
       </c>
-      <c r="F812">
+      <c r="F812" s="4">
         <v>27</v>
       </c>
       <c r="G812" t="s">
@@ -21941,7 +21940,7 @@
       <c r="E813" t="s">
         <v>10</v>
       </c>
-      <c r="F813">
+      <c r="F813" s="4">
         <v>40</v>
       </c>
       <c r="G813" t="s">
@@ -21967,7 +21966,7 @@
       <c r="E814" t="s">
         <v>14</v>
       </c>
-      <c r="F814">
+      <c r="F814" s="4">
         <v>28</v>
       </c>
       <c r="G814" t="s">
@@ -21993,7 +21992,7 @@
       <c r="E815" t="s">
         <v>14</v>
       </c>
-      <c r="F815">
+      <c r="F815" s="4">
         <v>39</v>
       </c>
       <c r="G815" t="s">
@@ -22019,7 +22018,7 @@
       <c r="E816" t="s">
         <v>19</v>
       </c>
-      <c r="F816">
+      <c r="F816" s="4">
         <v>38</v>
       </c>
       <c r="G816" s="2" t="s">
@@ -22045,7 +22044,7 @@
       <c r="E817" t="s">
         <v>14</v>
       </c>
-      <c r="F817">
+      <c r="F817" s="4">
         <v>32</v>
       </c>
       <c r="G817" t="s">
@@ -22071,7 +22070,7 @@
       <c r="E818" t="s">
         <v>14</v>
       </c>
-      <c r="F818">
+      <c r="F818" s="4">
         <v>26</v>
       </c>
       <c r="G818" t="s">
@@ -22097,7 +22096,7 @@
       <c r="E819" t="s">
         <v>14</v>
       </c>
-      <c r="F819">
+      <c r="F819" s="4">
         <v>31</v>
       </c>
       <c r="G819" t="s">
@@ -22123,7 +22122,7 @@
       <c r="E820" t="s">
         <v>19</v>
       </c>
-      <c r="F820">
+      <c r="F820" s="4">
         <v>24</v>
       </c>
       <c r="G820" t="s">
@@ -22149,7 +22148,7 @@
       <c r="E821" t="s">
         <v>19</v>
       </c>
-      <c r="F821">
+      <c r="F821" s="4">
         <v>39</v>
       </c>
       <c r="G821" s="2" t="s">
@@ -22175,7 +22174,7 @@
       <c r="E822" t="s">
         <v>14</v>
       </c>
-      <c r="F822">
+      <c r="F822" s="4">
         <v>28</v>
       </c>
       <c r="G822" t="s">
@@ -22201,7 +22200,7 @@
       <c r="E823" t="s">
         <v>19</v>
       </c>
-      <c r="F823">
+      <c r="F823" s="4">
         <v>26</v>
       </c>
       <c r="G823" t="s">
@@ -22227,7 +22226,7 @@
       <c r="E824" t="s">
         <v>19</v>
       </c>
-      <c r="F824">
+      <c r="F824" s="4">
         <v>46</v>
       </c>
       <c r="G824" t="s">
@@ -22253,7 +22252,7 @@
       <c r="E825" t="s">
         <v>10</v>
       </c>
-      <c r="F825">
+      <c r="F825" s="4">
         <v>37</v>
       </c>
       <c r="G825" s="2" t="s">
@@ -22279,7 +22278,7 @@
       <c r="E826" t="s">
         <v>10</v>
       </c>
-      <c r="F826">
+      <c r="F826" s="4">
         <v>52</v>
       </c>
       <c r="G826" t="s">
@@ -22305,7 +22304,7 @@
       <c r="E827" t="s">
         <v>14</v>
       </c>
-      <c r="F827">
+      <c r="F827" s="4">
         <v>46</v>
       </c>
       <c r="G827" t="s">
@@ -22331,7 +22330,7 @@
       <c r="E828" t="s">
         <v>19</v>
       </c>
-      <c r="F828">
+      <c r="F828" s="4">
         <v>42</v>
       </c>
       <c r="G828" t="s">
@@ -22357,7 +22356,7 @@
       <c r="E829" t="s">
         <v>19</v>
       </c>
-      <c r="F829">
+      <c r="F829" s="4">
         <v>21</v>
       </c>
       <c r="G829" s="2" t="s">
@@ -22383,7 +22382,7 @@
       <c r="E830" t="s">
         <v>14</v>
       </c>
-      <c r="F830">
+      <c r="F830" s="4">
         <v>28</v>
       </c>
       <c r="G830" t="s">
@@ -22409,7 +22408,7 @@
       <c r="E831" t="s">
         <v>10</v>
       </c>
-      <c r="F831">
+      <c r="F831" s="4">
         <v>29</v>
       </c>
       <c r="G831" t="s">
@@ -22435,7 +22434,7 @@
       <c r="E832" t="s">
         <v>19</v>
       </c>
-      <c r="F832">
+      <c r="F832" s="4">
         <v>23</v>
       </c>
       <c r="G832" s="2" t="s">
@@ -22461,7 +22460,7 @@
       <c r="E833" t="s">
         <v>10</v>
       </c>
-      <c r="F833">
+      <c r="F833" s="4">
         <v>41</v>
       </c>
       <c r="G833" t="s">
@@ -22487,7 +22486,7 @@
       <c r="E834" t="s">
         <v>14</v>
       </c>
-      <c r="F834">
+      <c r="F834" s="4">
         <v>28</v>
       </c>
       <c r="G834" t="s">
@@ -22513,7 +22512,7 @@
       <c r="E835" t="s">
         <v>14</v>
       </c>
-      <c r="F835">
+      <c r="F835" s="4">
         <v>37</v>
       </c>
       <c r="G835" s="2" t="s">
@@ -22539,7 +22538,7 @@
       <c r="E836" t="s">
         <v>14</v>
       </c>
-      <c r="F836">
+      <c r="F836" s="4">
         <v>34</v>
       </c>
       <c r="G836" t="s">
@@ -22565,7 +22564,7 @@
       <c r="E837" t="s">
         <v>14</v>
       </c>
-      <c r="F837">
+      <c r="F837" s="4">
         <v>26</v>
       </c>
       <c r="G837" t="s">
@@ -22591,7 +22590,7 @@
       <c r="E838" t="s">
         <v>19</v>
       </c>
-      <c r="F838">
+      <c r="F838" s="4">
         <v>35</v>
       </c>
       <c r="G838" t="s">
@@ -22617,7 +22616,7 @@
       <c r="E839" t="s">
         <v>10</v>
       </c>
-      <c r="F839">
+      <c r="F839" s="4">
         <v>36</v>
       </c>
       <c r="G839" t="s">
@@ -22643,7 +22642,7 @@
       <c r="E840" t="s">
         <v>10</v>
       </c>
-      <c r="F840">
+      <c r="F840" s="4">
         <v>29</v>
       </c>
       <c r="G840" s="2" t="s">
@@ -22669,7 +22668,7 @@
       <c r="E841" t="s">
         <v>19</v>
       </c>
-      <c r="F841">
+      <c r="F841" s="4">
         <v>27</v>
       </c>
       <c r="G841" t="s">
@@ -22695,7 +22694,7 @@
       <c r="E842" t="s">
         <v>10</v>
       </c>
-      <c r="F842">
+      <c r="F842" s="4">
         <v>25</v>
       </c>
       <c r="G842" t="s">
@@ -22721,7 +22720,7 @@
       <c r="E843" t="s">
         <v>10</v>
       </c>
-      <c r="F843">
+      <c r="F843" s="4">
         <v>36</v>
       </c>
       <c r="G843" t="s">
@@ -22747,7 +22746,7 @@
       <c r="E844" t="s">
         <v>10</v>
       </c>
-      <c r="F844">
+      <c r="F844" s="4">
         <v>37</v>
       </c>
       <c r="G844" s="2" t="s">
@@ -22773,7 +22772,7 @@
       <c r="E845" t="s">
         <v>10</v>
       </c>
-      <c r="F845">
+      <c r="F845" s="4">
         <v>26</v>
       </c>
       <c r="G845" t="s">
@@ -22799,7 +22798,7 @@
       <c r="E846" t="s">
         <v>10</v>
       </c>
-      <c r="F846">
+      <c r="F846" s="4">
         <v>37</v>
       </c>
       <c r="G846" t="s">
@@ -22825,7 +22824,7 @@
       <c r="E847" t="s">
         <v>19</v>
       </c>
-      <c r="F847">
+      <c r="F847" s="4">
         <v>24</v>
       </c>
       <c r="G847" s="2" t="s">
@@ -22851,7 +22850,7 @@
       <c r="E848" t="s">
         <v>10</v>
       </c>
-      <c r="F848">
+      <c r="F848" s="4">
         <v>39</v>
       </c>
       <c r="G848" t="s">
@@ -22877,7 +22876,7 @@
       <c r="E849" t="s">
         <v>10</v>
       </c>
-      <c r="F849">
+      <c r="F849" s="4">
         <v>26</v>
       </c>
       <c r="G849" t="s">
@@ -22903,7 +22902,7 @@
       <c r="E850" t="s">
         <v>10</v>
       </c>
-      <c r="F850">
+      <c r="F850" s="4">
         <v>34</v>
       </c>
       <c r="G850" s="2" t="s">
@@ -22929,7 +22928,7 @@
       <c r="E851" t="s">
         <v>10</v>
       </c>
-      <c r="F851">
+      <c r="F851" s="4">
         <v>28</v>
       </c>
       <c r="G851" t="s">
@@ -22955,7 +22954,7 @@
       <c r="E852" t="s">
         <v>10</v>
       </c>
-      <c r="F852">
+      <c r="F852" s="4">
         <v>32</v>
       </c>
       <c r="G852" t="s">
@@ -22981,7 +22980,7 @@
       <c r="E853" t="s">
         <v>10</v>
       </c>
-      <c r="F853">
+      <c r="F853" s="4">
         <v>39</v>
       </c>
       <c r="G853" s="2" t="s">
@@ -23007,7 +23006,7 @@
       <c r="E854" t="s">
         <v>10</v>
       </c>
-      <c r="F854">
+      <c r="F854" s="4">
         <v>29</v>
       </c>
       <c r="G854" t="s">
@@ -23033,7 +23032,7 @@
       <c r="E855" t="s">
         <v>10</v>
       </c>
-      <c r="F855">
+      <c r="F855" s="4">
         <v>32</v>
       </c>
       <c r="G855" s="2" t="s">
@@ -23059,7 +23058,7 @@
       <c r="E856" t="s">
         <v>14</v>
       </c>
-      <c r="F856">
+      <c r="F856" s="4">
         <v>25</v>
       </c>
       <c r="G856" t="s">
@@ -23085,7 +23084,7 @@
       <c r="E857" t="s">
         <v>19</v>
       </c>
-      <c r="F857">
+      <c r="F857" s="4">
         <v>36</v>
       </c>
       <c r="G857" t="s">
@@ -23111,7 +23110,7 @@
       <c r="E858" t="s">
         <v>10</v>
       </c>
-      <c r="F858">
+      <c r="F858" s="4">
         <v>25</v>
       </c>
       <c r="G858" s="2" t="s">
@@ -23137,7 +23136,7 @@
       <c r="E859" t="s">
         <v>10</v>
       </c>
-      <c r="F859">
+      <c r="F859" s="4">
         <v>58</v>
       </c>
       <c r="G859" t="s">
@@ -23163,7 +23162,7 @@
       <c r="E860" t="s">
         <v>10</v>
       </c>
-      <c r="F860">
+      <c r="F860" s="4">
         <v>24</v>
       </c>
       <c r="G860" t="s">
@@ -23189,7 +23188,7 @@
       <c r="E861" t="s">
         <v>14</v>
       </c>
-      <c r="F861">
+      <c r="F861" s="4">
         <v>56</v>
       </c>
       <c r="G861" s="2" t="s">
@@ -23215,7 +23214,7 @@
       <c r="E862" t="s">
         <v>10</v>
       </c>
-      <c r="F862">
+      <c r="F862" s="4">
         <v>27</v>
       </c>
       <c r="G862" t="s">
@@ -23241,7 +23240,7 @@
       <c r="E863" t="s">
         <v>10</v>
       </c>
-      <c r="F863">
+      <c r="F863" s="4">
         <v>40</v>
       </c>
       <c r="G863" t="s">
@@ -23267,7 +23266,7 @@
       <c r="E864" t="s">
         <v>14</v>
       </c>
-      <c r="F864">
+      <c r="F864" s="4">
         <v>28</v>
       </c>
       <c r="G864" t="s">
@@ -23293,7 +23292,7 @@
       <c r="E865" t="s">
         <v>14</v>
       </c>
-      <c r="F865">
+      <c r="F865" s="4">
         <v>39</v>
       </c>
       <c r="G865" t="s">
@@ -23319,7 +23318,7 @@
       <c r="E866" t="s">
         <v>19</v>
       </c>
-      <c r="F866">
+      <c r="F866" s="4">
         <v>38</v>
       </c>
       <c r="G866" s="2" t="s">
@@ -23345,7 +23344,7 @@
       <c r="E867" t="s">
         <v>14</v>
       </c>
-      <c r="F867">
+      <c r="F867" s="4">
         <v>32</v>
       </c>
       <c r="G867" t="s">
@@ -23371,7 +23370,7 @@
       <c r="E868" t="s">
         <v>14</v>
       </c>
-      <c r="F868">
+      <c r="F868" s="4">
         <v>26</v>
       </c>
       <c r="G868" t="s">
@@ -23397,7 +23396,7 @@
       <c r="E869" t="s">
         <v>14</v>
       </c>
-      <c r="F869">
+      <c r="F869" s="4">
         <v>31</v>
       </c>
       <c r="G869" t="s">
@@ -23423,7 +23422,7 @@
       <c r="E870" t="s">
         <v>19</v>
       </c>
-      <c r="F870">
+      <c r="F870" s="4">
         <v>24</v>
       </c>
       <c r="G870" t="s">
@@ -23449,7 +23448,7 @@
       <c r="E871" t="s">
         <v>19</v>
       </c>
-      <c r="F871">
+      <c r="F871" s="4">
         <v>39</v>
       </c>
       <c r="G871" s="2" t="s">
@@ -23475,7 +23474,7 @@
       <c r="E872" t="s">
         <v>14</v>
       </c>
-      <c r="F872">
+      <c r="F872" s="4">
         <v>28</v>
       </c>
       <c r="G872" t="s">
@@ -23501,7 +23500,7 @@
       <c r="E873" t="s">
         <v>19</v>
       </c>
-      <c r="F873">
+      <c r="F873" s="4">
         <v>26</v>
       </c>
       <c r="G873" t="s">
@@ -23527,7 +23526,7 @@
       <c r="E874" t="s">
         <v>19</v>
       </c>
-      <c r="F874">
+      <c r="F874" s="4">
         <v>46</v>
       </c>
       <c r="G874" t="s">
@@ -23553,7 +23552,7 @@
       <c r="E875" t="s">
         <v>10</v>
       </c>
-      <c r="F875">
+      <c r="F875" s="4">
         <v>37</v>
       </c>
       <c r="G875" s="2" t="s">
@@ -23579,7 +23578,7 @@
       <c r="E876" t="s">
         <v>10</v>
       </c>
-      <c r="F876">
+      <c r="F876" s="4">
         <v>52</v>
       </c>
       <c r="G876" t="s">
@@ -23605,7 +23604,7 @@
       <c r="E877" t="s">
         <v>14</v>
       </c>
-      <c r="F877">
+      <c r="F877" s="4">
         <v>46</v>
       </c>
       <c r="G877" t="s">
@@ -23631,7 +23630,7 @@
       <c r="E878" t="s">
         <v>19</v>
       </c>
-      <c r="F878">
+      <c r="F878" s="4">
         <v>42</v>
       </c>
       <c r="G878" t="s">
@@ -23657,7 +23656,7 @@
       <c r="E879" t="s">
         <v>19</v>
       </c>
-      <c r="F879">
+      <c r="F879" s="4">
         <v>21</v>
       </c>
       <c r="G879" s="2" t="s">
@@ -23683,7 +23682,7 @@
       <c r="E880" t="s">
         <v>14</v>
       </c>
-      <c r="F880">
+      <c r="F880" s="4">
         <v>28</v>
       </c>
       <c r="G880" t="s">
@@ -23709,7 +23708,7 @@
       <c r="E881" t="s">
         <v>10</v>
       </c>
-      <c r="F881">
+      <c r="F881" s="4">
         <v>29</v>
       </c>
       <c r="G881" t="s">
@@ -23735,7 +23734,7 @@
       <c r="E882" t="s">
         <v>19</v>
       </c>
-      <c r="F882">
+      <c r="F882" s="4">
         <v>23</v>
       </c>
       <c r="G882" s="2" t="s">
@@ -23761,7 +23760,7 @@
       <c r="E883" t="s">
         <v>10</v>
       </c>
-      <c r="F883">
+      <c r="F883" s="4">
         <v>41</v>
       </c>
       <c r="G883" t="s">
@@ -23787,7 +23786,7 @@
       <c r="E884" t="s">
         <v>14</v>
       </c>
-      <c r="F884">
+      <c r="F884" s="4">
         <v>28</v>
       </c>
       <c r="G884" t="s">
@@ -23813,7 +23812,7 @@
       <c r="E885" t="s">
         <v>14</v>
       </c>
-      <c r="F885">
+      <c r="F885" s="4">
         <v>37</v>
       </c>
       <c r="G885" s="2" t="s">
@@ -23839,7 +23838,7 @@
       <c r="E886" t="s">
         <v>14</v>
       </c>
-      <c r="F886">
+      <c r="F886" s="4">
         <v>34</v>
       </c>
       <c r="G886" t="s">
@@ -23865,7 +23864,7 @@
       <c r="E887" t="s">
         <v>14</v>
       </c>
-      <c r="F887">
+      <c r="F887" s="4">
         <v>26</v>
       </c>
       <c r="G887" t="s">
@@ -23891,7 +23890,7 @@
       <c r="E888" t="s">
         <v>19</v>
       </c>
-      <c r="F888">
+      <c r="F888" s="4">
         <v>35</v>
       </c>
       <c r="G888" t="s">
@@ -23917,7 +23916,7 @@
       <c r="E889" t="s">
         <v>10</v>
       </c>
-      <c r="F889">
+      <c r="F889" s="4">
         <v>36</v>
       </c>
       <c r="G889" t="s">
@@ -23943,7 +23942,7 @@
       <c r="E890" t="s">
         <v>10</v>
       </c>
-      <c r="F890">
+      <c r="F890" s="4">
         <v>29</v>
       </c>
       <c r="G890" s="2" t="s">
@@ -23969,7 +23968,7 @@
       <c r="E891" t="s">
         <v>19</v>
       </c>
-      <c r="F891">
+      <c r="F891" s="4">
         <v>27</v>
       </c>
       <c r="G891" t="s">
@@ -23995,7 +23994,7 @@
       <c r="E892" t="s">
         <v>10</v>
       </c>
-      <c r="F892">
+      <c r="F892" s="4">
         <v>25</v>
       </c>
       <c r="G892" t="s">
@@ -24021,7 +24020,7 @@
       <c r="E893" t="s">
         <v>10</v>
       </c>
-      <c r="F893">
+      <c r="F893" s="4">
         <v>36</v>
       </c>
       <c r="G893" t="s">
@@ -24047,7 +24046,7 @@
       <c r="E894" t="s">
         <v>10</v>
       </c>
-      <c r="F894">
+      <c r="F894" s="4">
         <v>37</v>
       </c>
       <c r="G894" s="2" t="s">
@@ -24073,7 +24072,7 @@
       <c r="E895" t="s">
         <v>10</v>
       </c>
-      <c r="F895">
+      <c r="F895" s="4">
         <v>26</v>
       </c>
       <c r="G895" t="s">
@@ -24099,7 +24098,7 @@
       <c r="E896" t="s">
         <v>10</v>
       </c>
-      <c r="F896">
+      <c r="F896" s="4">
         <v>37</v>
       </c>
       <c r="G896" t="s">
@@ -24125,7 +24124,7 @@
       <c r="E897" t="s">
         <v>19</v>
       </c>
-      <c r="F897">
+      <c r="F897" s="4">
         <v>24</v>
       </c>
       <c r="G897" s="2" t="s">
@@ -24151,7 +24150,7 @@
       <c r="E898" t="s">
         <v>10</v>
       </c>
-      <c r="F898">
+      <c r="F898" s="4">
         <v>39</v>
       </c>
       <c r="G898" t="s">
@@ -24177,7 +24176,7 @@
       <c r="E899" t="s">
         <v>10</v>
       </c>
-      <c r="F899">
+      <c r="F899" s="4">
         <v>26</v>
       </c>
       <c r="G899" t="s">
@@ -24203,7 +24202,7 @@
       <c r="E900" t="s">
         <v>10</v>
       </c>
-      <c r="F900">
+      <c r="F900" s="4">
         <v>34</v>
       </c>
       <c r="G900" s="2" t="s">
@@ -24229,7 +24228,7 @@
       <c r="E901" t="s">
         <v>10</v>
       </c>
-      <c r="F901">
+      <c r="F901" s="4">
         <v>28</v>
       </c>
       <c r="G901" t="s">
@@ -24255,7 +24254,7 @@
       <c r="E902" t="s">
         <v>10</v>
       </c>
-      <c r="F902">
+      <c r="F902" s="4">
         <v>32</v>
       </c>
       <c r="G902" t="s">
@@ -24281,7 +24280,7 @@
       <c r="E903" t="s">
         <v>10</v>
       </c>
-      <c r="F903">
+      <c r="F903" s="4">
         <v>39</v>
       </c>
       <c r="G903" s="2" t="s">
@@ -24307,7 +24306,7 @@
       <c r="E904" t="s">
         <v>10</v>
       </c>
-      <c r="F904">
+      <c r="F904" s="4">
         <v>29</v>
       </c>
       <c r="G904" t="s">
@@ -24333,7 +24332,7 @@
       <c r="E905" t="s">
         <v>10</v>
       </c>
-      <c r="F905">
+      <c r="F905" s="4">
         <v>32</v>
       </c>
       <c r="G905" s="2" t="s">
@@ -24359,7 +24358,7 @@
       <c r="E906" t="s">
         <v>14</v>
       </c>
-      <c r="F906">
+      <c r="F906" s="4">
         <v>25</v>
       </c>
       <c r="G906" t="s">
@@ -24385,7 +24384,7 @@
       <c r="E907" t="s">
         <v>19</v>
       </c>
-      <c r="F907">
+      <c r="F907" s="4">
         <v>36</v>
       </c>
       <c r="G907" t="s">
@@ -24411,7 +24410,7 @@
       <c r="E908" t="s">
         <v>10</v>
       </c>
-      <c r="F908">
+      <c r="F908" s="4">
         <v>25</v>
       </c>
       <c r="G908" s="2" t="s">
@@ -24437,7 +24436,7 @@
       <c r="E909" t="s">
         <v>10</v>
       </c>
-      <c r="F909">
+      <c r="F909" s="4">
         <v>58</v>
       </c>
       <c r="G909" t="s">
@@ -24463,7 +24462,7 @@
       <c r="E910" t="s">
         <v>10</v>
       </c>
-      <c r="F910">
+      <c r="F910" s="4">
         <v>24</v>
       </c>
       <c r="G910" t="s">
@@ -24489,7 +24488,7 @@
       <c r="E911" t="s">
         <v>14</v>
       </c>
-      <c r="F911">
+      <c r="F911" s="4">
         <v>56</v>
       </c>
       <c r="G911" s="2" t="s">
@@ -24515,7 +24514,7 @@
       <c r="E912" t="s">
         <v>10</v>
       </c>
-      <c r="F912">
+      <c r="F912" s="4">
         <v>27</v>
       </c>
       <c r="G912" t="s">
@@ -24541,7 +24540,7 @@
       <c r="E913" t="s">
         <v>10</v>
       </c>
-      <c r="F913">
+      <c r="F913" s="4">
         <v>40</v>
       </c>
       <c r="G913" t="s">
@@ -24567,7 +24566,7 @@
       <c r="E914" t="s">
         <v>14</v>
       </c>
-      <c r="F914">
+      <c r="F914" s="4">
         <v>28</v>
       </c>
       <c r="G914" t="s">
@@ -24593,7 +24592,7 @@
       <c r="E915" t="s">
         <v>14</v>
       </c>
-      <c r="F915">
+      <c r="F915" s="4">
         <v>39</v>
       </c>
       <c r="G915" t="s">
@@ -24619,7 +24618,7 @@
       <c r="E916" t="s">
         <v>19</v>
       </c>
-      <c r="F916">
+      <c r="F916" s="4">
         <v>38</v>
       </c>
       <c r="G916" s="2" t="s">
@@ -24645,7 +24644,7 @@
       <c r="E917" t="s">
         <v>14</v>
       </c>
-      <c r="F917">
+      <c r="F917" s="4">
         <v>32</v>
       </c>
       <c r="G917" t="s">
@@ -24671,7 +24670,7 @@
       <c r="E918" t="s">
         <v>14</v>
       </c>
-      <c r="F918">
+      <c r="F918" s="4">
         <v>26</v>
       </c>
       <c r="G918" t="s">
@@ -24697,7 +24696,7 @@
       <c r="E919" t="s">
         <v>14</v>
       </c>
-      <c r="F919">
+      <c r="F919" s="4">
         <v>31</v>
       </c>
       <c r="G919" t="s">
@@ -24723,7 +24722,7 @@
       <c r="E920" t="s">
         <v>19</v>
       </c>
-      <c r="F920">
+      <c r="F920" s="4">
         <v>24</v>
       </c>
       <c r="G920" t="s">
@@ -24749,7 +24748,7 @@
       <c r="E921" t="s">
         <v>19</v>
       </c>
-      <c r="F921">
+      <c r="F921" s="4">
         <v>39</v>
       </c>
       <c r="G921" s="2" t="s">
@@ -24775,7 +24774,7 @@
       <c r="E922" t="s">
         <v>14</v>
       </c>
-      <c r="F922">
+      <c r="F922" s="4">
         <v>28</v>
       </c>
       <c r="G922" t="s">
@@ -24801,7 +24800,7 @@
       <c r="E923" t="s">
         <v>19</v>
       </c>
-      <c r="F923">
+      <c r="F923" s="4">
         <v>26</v>
       </c>
       <c r="G923" t="s">
@@ -24827,7 +24826,7 @@
       <c r="E924" t="s">
         <v>19</v>
       </c>
-      <c r="F924">
+      <c r="F924" s="4">
         <v>46</v>
       </c>
       <c r="G924" t="s">
@@ -24853,7 +24852,7 @@
       <c r="E925" t="s">
         <v>10</v>
       </c>
-      <c r="F925">
+      <c r="F925" s="4">
         <v>37</v>
       </c>
       <c r="G925" s="2" t="s">
@@ -24879,7 +24878,7 @@
       <c r="E926" t="s">
         <v>10</v>
       </c>
-      <c r="F926">
+      <c r="F926" s="4">
         <v>52</v>
       </c>
       <c r="G926" t="s">
@@ -24905,7 +24904,7 @@
       <c r="E927" t="s">
         <v>14</v>
       </c>
-      <c r="F927">
+      <c r="F927" s="4">
         <v>46</v>
       </c>
       <c r="G927" t="s">
@@ -24931,7 +24930,7 @@
       <c r="E928" t="s">
         <v>19</v>
       </c>
-      <c r="F928">
+      <c r="F928" s="4">
         <v>42</v>
       </c>
       <c r="G928" t="s">
@@ -24957,7 +24956,7 @@
       <c r="E929" t="s">
         <v>19</v>
       </c>
-      <c r="F929">
+      <c r="F929" s="4">
         <v>21</v>
       </c>
       <c r="G929" s="2" t="s">
@@ -24983,7 +24982,7 @@
       <c r="E930" t="s">
         <v>14</v>
       </c>
-      <c r="F930">
+      <c r="F930" s="4">
         <v>28</v>
       </c>
       <c r="G930" t="s">
@@ -25009,7 +25008,7 @@
       <c r="E931" t="s">
         <v>10</v>
       </c>
-      <c r="F931">
+      <c r="F931" s="4">
         <v>29</v>
       </c>
       <c r="G931" t="s">
@@ -25035,7 +25034,7 @@
       <c r="E932" t="s">
         <v>19</v>
       </c>
-      <c r="F932">
+      <c r="F932" s="4">
         <v>23</v>
       </c>
       <c r="G932" s="2" t="s">
@@ -25061,7 +25060,7 @@
       <c r="E933" t="s">
         <v>10</v>
       </c>
-      <c r="F933">
+      <c r="F933" s="4">
         <v>41</v>
       </c>
       <c r="G933" t="s">
@@ -25087,7 +25086,7 @@
       <c r="E934" t="s">
         <v>14</v>
       </c>
-      <c r="F934">
+      <c r="F934" s="4">
         <v>28</v>
       </c>
       <c r="G934" t="s">
@@ -25113,7 +25112,7 @@
       <c r="E935" t="s">
         <v>14</v>
       </c>
-      <c r="F935">
+      <c r="F935" s="4">
         <v>37</v>
       </c>
       <c r="G935" s="2" t="s">
@@ -25139,7 +25138,7 @@
       <c r="E936" t="s">
         <v>14</v>
       </c>
-      <c r="F936">
+      <c r="F936" s="4">
         <v>34</v>
       </c>
       <c r="G936" t="s">
@@ -25165,7 +25164,7 @@
       <c r="E937" t="s">
         <v>14</v>
       </c>
-      <c r="F937">
+      <c r="F937" s="4">
         <v>26</v>
       </c>
       <c r="G937" t="s">
@@ -25191,7 +25190,7 @@
       <c r="E938" t="s">
         <v>19</v>
       </c>
-      <c r="F938">
+      <c r="F938" s="4">
         <v>35</v>
       </c>
       <c r="G938" t="s">
@@ -25217,7 +25216,7 @@
       <c r="E939" t="s">
         <v>10</v>
       </c>
-      <c r="F939">
+      <c r="F939" s="4">
         <v>36</v>
       </c>
       <c r="G939" t="s">
@@ -25243,7 +25242,7 @@
       <c r="E940" t="s">
         <v>10</v>
       </c>
-      <c r="F940">
+      <c r="F940" s="4">
         <v>29</v>
       </c>
       <c r="G940" s="2" t="s">
@@ -25269,7 +25268,7 @@
       <c r="E941" t="s">
         <v>19</v>
       </c>
-      <c r="F941">
+      <c r="F941" s="4">
         <v>27</v>
       </c>
       <c r="G941" t="s">
@@ -25295,7 +25294,7 @@
       <c r="E942" t="s">
         <v>10</v>
       </c>
-      <c r="F942">
+      <c r="F942" s="4">
         <v>25</v>
       </c>
       <c r="G942" t="s">
@@ -25321,7 +25320,7 @@
       <c r="E943" t="s">
         <v>10</v>
       </c>
-      <c r="F943">
+      <c r="F943" s="4">
         <v>36</v>
       </c>
       <c r="G943" t="s">
@@ -25347,7 +25346,7 @@
       <c r="E944" t="s">
         <v>10</v>
       </c>
-      <c r="F944">
+      <c r="F944" s="4">
         <v>37</v>
       </c>
       <c r="G944" s="2" t="s">
@@ -25373,7 +25372,7 @@
       <c r="E945" t="s">
         <v>10</v>
       </c>
-      <c r="F945">
+      <c r="F945" s="4">
         <v>26</v>
       </c>
       <c r="G945" t="s">
@@ -25399,7 +25398,7 @@
       <c r="E946" t="s">
         <v>10</v>
       </c>
-      <c r="F946">
+      <c r="F946" s="4">
         <v>37</v>
       </c>
       <c r="G946" t="s">
@@ -25425,7 +25424,7 @@
       <c r="E947" t="s">
         <v>19</v>
       </c>
-      <c r="F947">
+      <c r="F947" s="4">
         <v>24</v>
       </c>
       <c r="G947" s="2" t="s">
@@ -25451,7 +25450,7 @@
       <c r="E948" t="s">
         <v>10</v>
       </c>
-      <c r="F948">
+      <c r="F948" s="4">
         <v>39</v>
       </c>
       <c r="G948" t="s">
@@ -25477,7 +25476,7 @@
       <c r="E949" t="s">
         <v>10</v>
       </c>
-      <c r="F949">
+      <c r="F949" s="4">
         <v>26</v>
       </c>
       <c r="G949" t="s">
@@ -25503,7 +25502,7 @@
       <c r="E950" t="s">
         <v>10</v>
       </c>
-      <c r="F950">
+      <c r="F950" s="4">
         <v>34</v>
       </c>
       <c r="G950" s="2" t="s">
@@ -25529,7 +25528,7 @@
       <c r="E951" t="s">
         <v>10</v>
       </c>
-      <c r="F951">
+      <c r="F951" s="4">
         <v>28</v>
       </c>
       <c r="G951" t="s">
@@ -25555,7 +25554,7 @@
       <c r="E952" t="s">
         <v>10</v>
       </c>
-      <c r="F952">
+      <c r="F952" s="4">
         <v>32</v>
       </c>
       <c r="G952" t="s">
@@ -25581,7 +25580,7 @@
       <c r="E953" t="s">
         <v>10</v>
       </c>
-      <c r="F953">
+      <c r="F953" s="4">
         <v>39</v>
       </c>
       <c r="G953" s="2" t="s">
@@ -25607,7 +25606,7 @@
       <c r="E954" t="s">
         <v>10</v>
       </c>
-      <c r="F954">
+      <c r="F954" s="4">
         <v>29</v>
       </c>
       <c r="G954" t="s">
@@ -25633,7 +25632,7 @@
       <c r="E955" t="s">
         <v>10</v>
       </c>
-      <c r="F955">
+      <c r="F955" s="4">
         <v>32</v>
       </c>
       <c r="G955" s="2" t="s">
@@ -25659,7 +25658,7 @@
       <c r="E956" t="s">
         <v>14</v>
       </c>
-      <c r="F956">
+      <c r="F956" s="4">
         <v>25</v>
       </c>
       <c r="G956" t="s">
@@ -25685,7 +25684,7 @@
       <c r="E957" t="s">
         <v>19</v>
       </c>
-      <c r="F957">
+      <c r="F957" s="4">
         <v>36</v>
       </c>
       <c r="G957" t="s">
@@ -25711,7 +25710,7 @@
       <c r="E958" t="s">
         <v>10</v>
       </c>
-      <c r="F958">
+      <c r="F958" s="4">
         <v>25</v>
       </c>
       <c r="G958" s="2" t="s">
@@ -25737,7 +25736,7 @@
       <c r="E959" t="s">
         <v>10</v>
       </c>
-      <c r="F959">
+      <c r="F959" s="4">
         <v>58</v>
       </c>
       <c r="G959" t="s">
@@ -25763,7 +25762,7 @@
       <c r="E960" t="s">
         <v>10</v>
       </c>
-      <c r="F960">
+      <c r="F960" s="4">
         <v>24</v>
       </c>
       <c r="G960" t="s">
@@ -25789,7 +25788,7 @@
       <c r="E961" t="s">
         <v>14</v>
       </c>
-      <c r="F961">
+      <c r="F961" s="4">
         <v>56</v>
       </c>
       <c r="G961" s="2" t="s">
@@ -25815,7 +25814,7 @@
       <c r="E962" t="s">
         <v>10</v>
       </c>
-      <c r="F962">
+      <c r="F962" s="4">
         <v>27</v>
       </c>
       <c r="G962" t="s">
@@ -25841,7 +25840,7 @@
       <c r="E963" t="s">
         <v>10</v>
       </c>
-      <c r="F963">
+      <c r="F963" s="4">
         <v>40</v>
       </c>
       <c r="G963" t="s">
@@ -25867,7 +25866,7 @@
       <c r="E964" t="s">
         <v>14</v>
       </c>
-      <c r="F964">
+      <c r="F964" s="4">
         <v>28</v>
       </c>
       <c r="G964" t="s">
@@ -25893,7 +25892,7 @@
       <c r="E965" t="s">
         <v>14</v>
       </c>
-      <c r="F965">
+      <c r="F965" s="4">
         <v>39</v>
       </c>
       <c r="G965" t="s">
@@ -25919,7 +25918,7 @@
       <c r="E966" t="s">
         <v>19</v>
       </c>
-      <c r="F966">
+      <c r="F966" s="4">
         <v>38</v>
       </c>
       <c r="G966" s="2" t="s">
@@ -25945,7 +25944,7 @@
       <c r="E967" t="s">
         <v>14</v>
       </c>
-      <c r="F967">
+      <c r="F967" s="4">
         <v>32</v>
       </c>
       <c r="G967" t="s">
@@ -25971,7 +25970,7 @@
       <c r="E968" t="s">
         <v>14</v>
       </c>
-      <c r="F968">
+      <c r="F968" s="4">
         <v>26</v>
       </c>
       <c r="G968" t="s">
@@ -25997,7 +25996,7 @@
       <c r="E969" t="s">
         <v>14</v>
       </c>
-      <c r="F969">
+      <c r="F969" s="4">
         <v>31</v>
       </c>
       <c r="G969" t="s">
@@ -26023,7 +26022,7 @@
       <c r="E970" t="s">
         <v>19</v>
       </c>
-      <c r="F970">
+      <c r="F970" s="4">
         <v>24</v>
       </c>
       <c r="G970" t="s">
@@ -26049,7 +26048,7 @@
       <c r="E971" t="s">
         <v>19</v>
       </c>
-      <c r="F971">
+      <c r="F971" s="4">
         <v>39</v>
       </c>
       <c r="G971" s="2" t="s">
@@ -26075,7 +26074,7 @@
       <c r="E972" t="s">
         <v>14</v>
       </c>
-      <c r="F972">
+      <c r="F972" s="4">
         <v>28</v>
       </c>
       <c r="G972" t="s">
@@ -26101,7 +26100,7 @@
       <c r="E973" t="s">
         <v>19</v>
       </c>
-      <c r="F973">
+      <c r="F973" s="4">
         <v>26</v>
       </c>
       <c r="G973" t="s">
@@ -26127,7 +26126,7 @@
       <c r="E974" t="s">
         <v>19</v>
       </c>
-      <c r="F974">
+      <c r="F974" s="4">
         <v>46</v>
       </c>
       <c r="G974" t="s">
@@ -26153,7 +26152,7 @@
       <c r="E975" t="s">
         <v>10</v>
       </c>
-      <c r="F975">
+      <c r="F975" s="4">
         <v>37</v>
       </c>
       <c r="G975" s="2" t="s">
@@ -26179,7 +26178,7 @@
       <c r="E976" t="s">
         <v>10</v>
       </c>
-      <c r="F976">
+      <c r="F976" s="4">
         <v>52</v>
       </c>
       <c r="G976" t="s">
@@ -26205,7 +26204,7 @@
       <c r="E977" t="s">
         <v>14</v>
       </c>
-      <c r="F977">
+      <c r="F977" s="4">
         <v>46</v>
       </c>
       <c r="G977" t="s">
@@ -26231,7 +26230,7 @@
       <c r="E978" t="s">
         <v>19</v>
       </c>
-      <c r="F978">
+      <c r="F978" s="4">
         <v>42</v>
       </c>
       <c r="G978" t="s">
@@ -26257,7 +26256,7 @@
       <c r="E979" t="s">
         <v>19</v>
       </c>
-      <c r="F979">
+      <c r="F979" s="4">
         <v>21</v>
       </c>
       <c r="G979" s="2" t="s">
@@ -26283,7 +26282,7 @@
       <c r="E980" t="s">
         <v>14</v>
       </c>
-      <c r="F980">
+      <c r="F980" s="4">
         <v>28</v>
       </c>
       <c r="G980" t="s">
@@ -26309,7 +26308,7 @@
       <c r="E981" t="s">
         <v>10</v>
       </c>
-      <c r="F981">
+      <c r="F981" s="4">
         <v>29</v>
       </c>
       <c r="G981" t="s">
@@ -26335,7 +26334,7 @@
       <c r="E982" t="s">
         <v>19</v>
       </c>
-      <c r="F982">
+      <c r="F982" s="4">
         <v>23</v>
       </c>
       <c r="G982" s="2" t="s">
@@ -26361,7 +26360,7 @@
       <c r="E983" t="s">
         <v>10</v>
       </c>
-      <c r="F983">
+      <c r="F983" s="4">
         <v>41</v>
       </c>
       <c r="G983" t="s">
@@ -26387,7 +26386,7 @@
       <c r="E984" t="s">
         <v>14</v>
       </c>
-      <c r="F984">
+      <c r="F984" s="4">
         <v>28</v>
       </c>
       <c r="G984" t="s">
@@ -26413,7 +26412,7 @@
       <c r="E985" t="s">
         <v>14</v>
       </c>
-      <c r="F985">
+      <c r="F985" s="4">
         <v>37</v>
       </c>
       <c r="G985" s="2" t="s">
@@ -26439,7 +26438,7 @@
       <c r="E986" t="s">
         <v>14</v>
       </c>
-      <c r="F986">
+      <c r="F986" s="4">
         <v>34</v>
       </c>
       <c r="G986" t="s">
@@ -26465,7 +26464,7 @@
       <c r="E987" t="s">
         <v>14</v>
       </c>
-      <c r="F987">
+      <c r="F987" s="4">
         <v>26</v>
       </c>
       <c r="G987" t="s">
@@ -26491,7 +26490,7 @@
       <c r="E988" t="s">
         <v>19</v>
       </c>
-      <c r="F988">
+      <c r="F988" s="4">
         <v>35</v>
       </c>
       <c r="G988" t="s">
@@ -26517,7 +26516,7 @@
       <c r="E989" t="s">
         <v>10</v>
       </c>
-      <c r="F989">
+      <c r="F989" s="4">
         <v>36</v>
       </c>
       <c r="G989" t="s">
@@ -26543,7 +26542,7 @@
       <c r="E990" t="s">
         <v>10</v>
       </c>
-      <c r="F990">
+      <c r="F990" s="4">
         <v>29</v>
       </c>
       <c r="G990" s="2" t="s">
@@ -26569,7 +26568,7 @@
       <c r="E991" t="s">
         <v>19</v>
       </c>
-      <c r="F991">
+      <c r="F991" s="4">
         <v>27</v>
       </c>
       <c r="G991" t="s">
@@ -26595,7 +26594,7 @@
       <c r="E992" t="s">
         <v>10</v>
       </c>
-      <c r="F992">
+      <c r="F992" s="4">
         <v>25</v>
       </c>
       <c r="G992" t="s">
@@ -26621,7 +26620,7 @@
       <c r="E993" t="s">
         <v>10</v>
       </c>
-      <c r="F993">
+      <c r="F993" s="4">
         <v>36</v>
       </c>
       <c r="G993" t="s">
@@ -26647,7 +26646,7 @@
       <c r="E994" t="s">
         <v>10</v>
       </c>
-      <c r="F994">
+      <c r="F994" s="4">
         <v>37</v>
       </c>
       <c r="G994" s="2" t="s">
@@ -26673,7 +26672,7 @@
       <c r="E995" t="s">
         <v>10</v>
       </c>
-      <c r="F995">
+      <c r="F995" s="4">
         <v>26</v>
       </c>
       <c r="G995" t="s">
@@ -26699,7 +26698,7 @@
       <c r="E996" t="s">
         <v>10</v>
       </c>
-      <c r="F996">
+      <c r="F996" s="4">
         <v>37</v>
       </c>
       <c r="G996" t="s">
@@ -26725,7 +26724,7 @@
       <c r="E997" t="s">
         <v>19</v>
       </c>
-      <c r="F997">
+      <c r="F997" s="4">
         <v>24</v>
       </c>
       <c r="G997" s="2" t="s">
@@ -26751,7 +26750,7 @@
       <c r="E998" t="s">
         <v>10</v>
       </c>
-      <c r="F998">
+      <c r="F998" s="4">
         <v>39</v>
       </c>
       <c r="G998" t="s">
@@ -26777,7 +26776,7 @@
       <c r="E999" t="s">
         <v>10</v>
       </c>
-      <c r="F999">
+      <c r="F999" s="4">
         <v>26</v>
       </c>
       <c r="G999" t="s">
@@ -26803,7 +26802,7 @@
       <c r="E1000" t="s">
         <v>10</v>
       </c>
-      <c r="F1000">
+      <c r="F1000" s="4">
         <v>34</v>
       </c>
       <c r="G1000" s="2" t="s">
@@ -26829,7 +26828,7 @@
       <c r="E1001" t="s">
         <v>10</v>
       </c>
-      <c r="F1001">
+      <c r="F1001" s="4">
         <v>28</v>
       </c>
       <c r="G1001" t="s">
@@ -26855,7 +26854,7 @@
       <c r="E1002" t="s">
         <v>10</v>
       </c>
-      <c r="F1002">
+      <c r="F1002" s="4">
         <v>32</v>
       </c>
       <c r="G1002" t="s">
@@ -26881,7 +26880,7 @@
       <c r="E1003" t="s">
         <v>10</v>
       </c>
-      <c r="F1003">
+      <c r="F1003" s="4">
         <v>39</v>
       </c>
       <c r="G1003" s="2" t="s">
@@ -26907,7 +26906,7 @@
       <c r="E1004" t="s">
         <v>10</v>
       </c>
-      <c r="F1004">
+      <c r="F1004" s="4">
         <v>29</v>
       </c>
       <c r="G1004" t="s">
